--- a/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
+++ b/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0;;"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -110,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -127,6 +129,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -557,27 +560,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Mes/Año</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -807,23 +817,23 @@
       <c r="AE7" s="7" t="n"/>
       <c r="AF7" s="7" t="n"/>
       <c r="AG7" s="7" t="n"/>
-      <c r="AH7" s="6">
+      <c r="AH7" s="8">
         <f>COUNTIF(C7:AG7,"A")</f>
         <v/>
       </c>
-      <c r="AI7" s="6">
+      <c r="AI7" s="8">
         <f>COUNTIF(C7:AG7,"F")</f>
         <v/>
       </c>
-      <c r="AJ7" s="6">
+      <c r="AJ7" s="8">
         <f>COUNTIF(C7:AG7,"R")</f>
         <v/>
       </c>
-      <c r="AK7" s="6">
+      <c r="AK7" s="8">
         <f>COUNTIF(C7:AG7,"V")</f>
         <v/>
       </c>
-      <c r="AL7" s="6">
+      <c r="AL7" s="8">
         <f>COUNTIF(C7:AG7,"I")</f>
         <v/>
       </c>
@@ -864,23 +874,23 @@
       <c r="AE8" s="7" t="n"/>
       <c r="AF8" s="7" t="n"/>
       <c r="AG8" s="7" t="n"/>
-      <c r="AH8" s="6">
+      <c r="AH8" s="8">
         <f>COUNTIF(C8:AG8,"A")</f>
         <v/>
       </c>
-      <c r="AI8" s="6">
+      <c r="AI8" s="8">
         <f>COUNTIF(C8:AG8,"F")</f>
         <v/>
       </c>
-      <c r="AJ8" s="6">
+      <c r="AJ8" s="8">
         <f>COUNTIF(C8:AG8,"R")</f>
         <v/>
       </c>
-      <c r="AK8" s="6">
+      <c r="AK8" s="8">
         <f>COUNTIF(C8:AG8,"V")</f>
         <v/>
       </c>
-      <c r="AL8" s="6">
+      <c r="AL8" s="8">
         <f>COUNTIF(C8:AG8,"I")</f>
         <v/>
       </c>
@@ -921,23 +931,23 @@
       <c r="AE9" s="7" t="n"/>
       <c r="AF9" s="7" t="n"/>
       <c r="AG9" s="7" t="n"/>
-      <c r="AH9" s="6">
+      <c r="AH9" s="8">
         <f>COUNTIF(C9:AG9,"A")</f>
         <v/>
       </c>
-      <c r="AI9" s="6">
+      <c r="AI9" s="8">
         <f>COUNTIF(C9:AG9,"F")</f>
         <v/>
       </c>
-      <c r="AJ9" s="6">
+      <c r="AJ9" s="8">
         <f>COUNTIF(C9:AG9,"R")</f>
         <v/>
       </c>
-      <c r="AK9" s="6">
+      <c r="AK9" s="8">
         <f>COUNTIF(C9:AG9,"V")</f>
         <v/>
       </c>
-      <c r="AL9" s="6">
+      <c r="AL9" s="8">
         <f>COUNTIF(C9:AG9,"I")</f>
         <v/>
       </c>
@@ -978,23 +988,23 @@
       <c r="AE10" s="7" t="n"/>
       <c r="AF10" s="7" t="n"/>
       <c r="AG10" s="7" t="n"/>
-      <c r="AH10" s="6">
+      <c r="AH10" s="8">
         <f>COUNTIF(C10:AG10,"A")</f>
         <v/>
       </c>
-      <c r="AI10" s="6">
+      <c r="AI10" s="8">
         <f>COUNTIF(C10:AG10,"F")</f>
         <v/>
       </c>
-      <c r="AJ10" s="6">
+      <c r="AJ10" s="8">
         <f>COUNTIF(C10:AG10,"R")</f>
         <v/>
       </c>
-      <c r="AK10" s="6">
+      <c r="AK10" s="8">
         <f>COUNTIF(C10:AG10,"V")</f>
         <v/>
       </c>
-      <c r="AL10" s="6">
+      <c r="AL10" s="8">
         <f>COUNTIF(C10:AG10,"I")</f>
         <v/>
       </c>
@@ -1035,23 +1045,23 @@
       <c r="AE11" s="7" t="n"/>
       <c r="AF11" s="7" t="n"/>
       <c r="AG11" s="7" t="n"/>
-      <c r="AH11" s="6">
+      <c r="AH11" s="8">
         <f>COUNTIF(C11:AG11,"A")</f>
         <v/>
       </c>
-      <c r="AI11" s="6">
+      <c r="AI11" s="8">
         <f>COUNTIF(C11:AG11,"F")</f>
         <v/>
       </c>
-      <c r="AJ11" s="6">
+      <c r="AJ11" s="8">
         <f>COUNTIF(C11:AG11,"R")</f>
         <v/>
       </c>
-      <c r="AK11" s="6">
+      <c r="AK11" s="8">
         <f>COUNTIF(C11:AG11,"V")</f>
         <v/>
       </c>
-      <c r="AL11" s="6">
+      <c r="AL11" s="8">
         <f>COUNTIF(C11:AG11,"I")</f>
         <v/>
       </c>
@@ -1092,23 +1102,23 @@
       <c r="AE12" s="7" t="n"/>
       <c r="AF12" s="7" t="n"/>
       <c r="AG12" s="7" t="n"/>
-      <c r="AH12" s="6">
+      <c r="AH12" s="8">
         <f>COUNTIF(C12:AG12,"A")</f>
         <v/>
       </c>
-      <c r="AI12" s="6">
+      <c r="AI12" s="8">
         <f>COUNTIF(C12:AG12,"F")</f>
         <v/>
       </c>
-      <c r="AJ12" s="6">
+      <c r="AJ12" s="8">
         <f>COUNTIF(C12:AG12,"R")</f>
         <v/>
       </c>
-      <c r="AK12" s="6">
+      <c r="AK12" s="8">
         <f>COUNTIF(C12:AG12,"V")</f>
         <v/>
       </c>
-      <c r="AL12" s="6">
+      <c r="AL12" s="8">
         <f>COUNTIF(C12:AG12,"I")</f>
         <v/>
       </c>
@@ -1149,23 +1159,23 @@
       <c r="AE13" s="7" t="n"/>
       <c r="AF13" s="7" t="n"/>
       <c r="AG13" s="7" t="n"/>
-      <c r="AH13" s="6">
+      <c r="AH13" s="8">
         <f>COUNTIF(C13:AG13,"A")</f>
         <v/>
       </c>
-      <c r="AI13" s="6">
+      <c r="AI13" s="8">
         <f>COUNTIF(C13:AG13,"F")</f>
         <v/>
       </c>
-      <c r="AJ13" s="6">
+      <c r="AJ13" s="8">
         <f>COUNTIF(C13:AG13,"R")</f>
         <v/>
       </c>
-      <c r="AK13" s="6">
+      <c r="AK13" s="8">
         <f>COUNTIF(C13:AG13,"V")</f>
         <v/>
       </c>
-      <c r="AL13" s="6">
+      <c r="AL13" s="8">
         <f>COUNTIF(C13:AG13,"I")</f>
         <v/>
       </c>
@@ -1206,23 +1216,23 @@
       <c r="AE14" s="7" t="n"/>
       <c r="AF14" s="7" t="n"/>
       <c r="AG14" s="7" t="n"/>
-      <c r="AH14" s="6">
+      <c r="AH14" s="8">
         <f>COUNTIF(C14:AG14,"A")</f>
         <v/>
       </c>
-      <c r="AI14" s="6">
+      <c r="AI14" s="8">
         <f>COUNTIF(C14:AG14,"F")</f>
         <v/>
       </c>
-      <c r="AJ14" s="6">
+      <c r="AJ14" s="8">
         <f>COUNTIF(C14:AG14,"R")</f>
         <v/>
       </c>
-      <c r="AK14" s="6">
+      <c r="AK14" s="8">
         <f>COUNTIF(C14:AG14,"V")</f>
         <v/>
       </c>
-      <c r="AL14" s="6">
+      <c r="AL14" s="8">
         <f>COUNTIF(C14:AG14,"I")</f>
         <v/>
       </c>
@@ -1263,23 +1273,23 @@
       <c r="AE15" s="7" t="n"/>
       <c r="AF15" s="7" t="n"/>
       <c r="AG15" s="7" t="n"/>
-      <c r="AH15" s="6">
+      <c r="AH15" s="8">
         <f>COUNTIF(C15:AG15,"A")</f>
         <v/>
       </c>
-      <c r="AI15" s="6">
+      <c r="AI15" s="8">
         <f>COUNTIF(C15:AG15,"F")</f>
         <v/>
       </c>
-      <c r="AJ15" s="6">
+      <c r="AJ15" s="8">
         <f>COUNTIF(C15:AG15,"R")</f>
         <v/>
       </c>
-      <c r="AK15" s="6">
+      <c r="AK15" s="8">
         <f>COUNTIF(C15:AG15,"V")</f>
         <v/>
       </c>
-      <c r="AL15" s="6">
+      <c r="AL15" s="8">
         <f>COUNTIF(C15:AG15,"I")</f>
         <v/>
       </c>
@@ -1320,23 +1330,23 @@
       <c r="AE16" s="7" t="n"/>
       <c r="AF16" s="7" t="n"/>
       <c r="AG16" s="7" t="n"/>
-      <c r="AH16" s="6">
+      <c r="AH16" s="8">
         <f>COUNTIF(C16:AG16,"A")</f>
         <v/>
       </c>
-      <c r="AI16" s="6">
+      <c r="AI16" s="8">
         <f>COUNTIF(C16:AG16,"F")</f>
         <v/>
       </c>
-      <c r="AJ16" s="6">
+      <c r="AJ16" s="8">
         <f>COUNTIF(C16:AG16,"R")</f>
         <v/>
       </c>
-      <c r="AK16" s="6">
+      <c r="AK16" s="8">
         <f>COUNTIF(C16:AG16,"V")</f>
         <v/>
       </c>
-      <c r="AL16" s="6">
+      <c r="AL16" s="8">
         <f>COUNTIF(C16:AG16,"I")</f>
         <v/>
       </c>
@@ -1377,23 +1387,23 @@
       <c r="AE17" s="7" t="n"/>
       <c r="AF17" s="7" t="n"/>
       <c r="AG17" s="7" t="n"/>
-      <c r="AH17" s="6">
+      <c r="AH17" s="8">
         <f>COUNTIF(C17:AG17,"A")</f>
         <v/>
       </c>
-      <c r="AI17" s="6">
+      <c r="AI17" s="8">
         <f>COUNTIF(C17:AG17,"F")</f>
         <v/>
       </c>
-      <c r="AJ17" s="6">
+      <c r="AJ17" s="8">
         <f>COUNTIF(C17:AG17,"R")</f>
         <v/>
       </c>
-      <c r="AK17" s="6">
+      <c r="AK17" s="8">
         <f>COUNTIF(C17:AG17,"V")</f>
         <v/>
       </c>
-      <c r="AL17" s="6">
+      <c r="AL17" s="8">
         <f>COUNTIF(C17:AG17,"I")</f>
         <v/>
       </c>
@@ -1434,23 +1444,23 @@
       <c r="AE18" s="7" t="n"/>
       <c r="AF18" s="7" t="n"/>
       <c r="AG18" s="7" t="n"/>
-      <c r="AH18" s="6">
+      <c r="AH18" s="8">
         <f>COUNTIF(C18:AG18,"A")</f>
         <v/>
       </c>
-      <c r="AI18" s="6">
+      <c r="AI18" s="8">
         <f>COUNTIF(C18:AG18,"F")</f>
         <v/>
       </c>
-      <c r="AJ18" s="6">
+      <c r="AJ18" s="8">
         <f>COUNTIF(C18:AG18,"R")</f>
         <v/>
       </c>
-      <c r="AK18" s="6">
+      <c r="AK18" s="8">
         <f>COUNTIF(C18:AG18,"V")</f>
         <v/>
       </c>
-      <c r="AL18" s="6">
+      <c r="AL18" s="8">
         <f>COUNTIF(C18:AG18,"I")</f>
         <v/>
       </c>
@@ -1491,23 +1501,23 @@
       <c r="AE19" s="7" t="n"/>
       <c r="AF19" s="7" t="n"/>
       <c r="AG19" s="7" t="n"/>
-      <c r="AH19" s="6">
+      <c r="AH19" s="8">
         <f>COUNTIF(C19:AG19,"A")</f>
         <v/>
       </c>
-      <c r="AI19" s="6">
+      <c r="AI19" s="8">
         <f>COUNTIF(C19:AG19,"F")</f>
         <v/>
       </c>
-      <c r="AJ19" s="6">
+      <c r="AJ19" s="8">
         <f>COUNTIF(C19:AG19,"R")</f>
         <v/>
       </c>
-      <c r="AK19" s="6">
+      <c r="AK19" s="8">
         <f>COUNTIF(C19:AG19,"V")</f>
         <v/>
       </c>
-      <c r="AL19" s="6">
+      <c r="AL19" s="8">
         <f>COUNTIF(C19:AG19,"I")</f>
         <v/>
       </c>
@@ -1548,23 +1558,23 @@
       <c r="AE20" s="7" t="n"/>
       <c r="AF20" s="7" t="n"/>
       <c r="AG20" s="7" t="n"/>
-      <c r="AH20" s="6">
+      <c r="AH20" s="8">
         <f>COUNTIF(C20:AG20,"A")</f>
         <v/>
       </c>
-      <c r="AI20" s="6">
+      <c r="AI20" s="8">
         <f>COUNTIF(C20:AG20,"F")</f>
         <v/>
       </c>
-      <c r="AJ20" s="6">
+      <c r="AJ20" s="8">
         <f>COUNTIF(C20:AG20,"R")</f>
         <v/>
       </c>
-      <c r="AK20" s="6">
+      <c r="AK20" s="8">
         <f>COUNTIF(C20:AG20,"V")</f>
         <v/>
       </c>
-      <c r="AL20" s="6">
+      <c r="AL20" s="8">
         <f>COUNTIF(C20:AG20,"I")</f>
         <v/>
       </c>
@@ -1605,23 +1615,23 @@
       <c r="AE21" s="7" t="n"/>
       <c r="AF21" s="7" t="n"/>
       <c r="AG21" s="7" t="n"/>
-      <c r="AH21" s="6">
+      <c r="AH21" s="8">
         <f>COUNTIF(C21:AG21,"A")</f>
         <v/>
       </c>
-      <c r="AI21" s="6">
+      <c r="AI21" s="8">
         <f>COUNTIF(C21:AG21,"F")</f>
         <v/>
       </c>
-      <c r="AJ21" s="6">
+      <c r="AJ21" s="8">
         <f>COUNTIF(C21:AG21,"R")</f>
         <v/>
       </c>
-      <c r="AK21" s="6">
+      <c r="AK21" s="8">
         <f>COUNTIF(C21:AG21,"V")</f>
         <v/>
       </c>
-      <c r="AL21" s="6">
+      <c r="AL21" s="8">
         <f>COUNTIF(C21:AG21,"I")</f>
         <v/>
       </c>
@@ -1662,23 +1672,23 @@
       <c r="AE22" s="7" t="n"/>
       <c r="AF22" s="7" t="n"/>
       <c r="AG22" s="7" t="n"/>
-      <c r="AH22" s="6">
+      <c r="AH22" s="8">
         <f>COUNTIF(C22:AG22,"A")</f>
         <v/>
       </c>
-      <c r="AI22" s="6">
+      <c r="AI22" s="8">
         <f>COUNTIF(C22:AG22,"F")</f>
         <v/>
       </c>
-      <c r="AJ22" s="6">
+      <c r="AJ22" s="8">
         <f>COUNTIF(C22:AG22,"R")</f>
         <v/>
       </c>
-      <c r="AK22" s="6">
+      <c r="AK22" s="8">
         <f>COUNTIF(C22:AG22,"V")</f>
         <v/>
       </c>
-      <c r="AL22" s="6">
+      <c r="AL22" s="8">
         <f>COUNTIF(C22:AG22,"I")</f>
         <v/>
       </c>
@@ -1719,23 +1729,23 @@
       <c r="AE23" s="7" t="n"/>
       <c r="AF23" s="7" t="n"/>
       <c r="AG23" s="7" t="n"/>
-      <c r="AH23" s="6">
+      <c r="AH23" s="8">
         <f>COUNTIF(C23:AG23,"A")</f>
         <v/>
       </c>
-      <c r="AI23" s="6">
+      <c r="AI23" s="8">
         <f>COUNTIF(C23:AG23,"F")</f>
         <v/>
       </c>
-      <c r="AJ23" s="6">
+      <c r="AJ23" s="8">
         <f>COUNTIF(C23:AG23,"R")</f>
         <v/>
       </c>
-      <c r="AK23" s="6">
+      <c r="AK23" s="8">
         <f>COUNTIF(C23:AG23,"V")</f>
         <v/>
       </c>
-      <c r="AL23" s="6">
+      <c r="AL23" s="8">
         <f>COUNTIF(C23:AG23,"I")</f>
         <v/>
       </c>
@@ -1776,23 +1786,23 @@
       <c r="AE24" s="7" t="n"/>
       <c r="AF24" s="7" t="n"/>
       <c r="AG24" s="7" t="n"/>
-      <c r="AH24" s="6">
+      <c r="AH24" s="8">
         <f>COUNTIF(C24:AG24,"A")</f>
         <v/>
       </c>
-      <c r="AI24" s="6">
+      <c r="AI24" s="8">
         <f>COUNTIF(C24:AG24,"F")</f>
         <v/>
       </c>
-      <c r="AJ24" s="6">
+      <c r="AJ24" s="8">
         <f>COUNTIF(C24:AG24,"R")</f>
         <v/>
       </c>
-      <c r="AK24" s="6">
+      <c r="AK24" s="8">
         <f>COUNTIF(C24:AG24,"V")</f>
         <v/>
       </c>
-      <c r="AL24" s="6">
+      <c r="AL24" s="8">
         <f>COUNTIF(C24:AG24,"I")</f>
         <v/>
       </c>
@@ -1833,23 +1843,23 @@
       <c r="AE25" s="7" t="n"/>
       <c r="AF25" s="7" t="n"/>
       <c r="AG25" s="7" t="n"/>
-      <c r="AH25" s="6">
+      <c r="AH25" s="8">
         <f>COUNTIF(C25:AG25,"A")</f>
         <v/>
       </c>
-      <c r="AI25" s="6">
+      <c r="AI25" s="8">
         <f>COUNTIF(C25:AG25,"F")</f>
         <v/>
       </c>
-      <c r="AJ25" s="6">
+      <c r="AJ25" s="8">
         <f>COUNTIF(C25:AG25,"R")</f>
         <v/>
       </c>
-      <c r="AK25" s="6">
+      <c r="AK25" s="8">
         <f>COUNTIF(C25:AG25,"V")</f>
         <v/>
       </c>
-      <c r="AL25" s="6">
+      <c r="AL25" s="8">
         <f>COUNTIF(C25:AG25,"I")</f>
         <v/>
       </c>
@@ -1890,23 +1900,23 @@
       <c r="AE26" s="7" t="n"/>
       <c r="AF26" s="7" t="n"/>
       <c r="AG26" s="7" t="n"/>
-      <c r="AH26" s="6">
+      <c r="AH26" s="8">
         <f>COUNTIF(C26:AG26,"A")</f>
         <v/>
       </c>
-      <c r="AI26" s="6">
+      <c r="AI26" s="8">
         <f>COUNTIF(C26:AG26,"F")</f>
         <v/>
       </c>
-      <c r="AJ26" s="6">
+      <c r="AJ26" s="8">
         <f>COUNTIF(C26:AG26,"R")</f>
         <v/>
       </c>
-      <c r="AK26" s="6">
+      <c r="AK26" s="8">
         <f>COUNTIF(C26:AG26,"V")</f>
         <v/>
       </c>
-      <c r="AL26" s="6">
+      <c r="AL26" s="8">
         <f>COUNTIF(C26:AG26,"I")</f>
         <v/>
       </c>
@@ -1947,23 +1957,23 @@
       <c r="AE27" s="7" t="n"/>
       <c r="AF27" s="7" t="n"/>
       <c r="AG27" s="7" t="n"/>
-      <c r="AH27" s="6">
+      <c r="AH27" s="8">
         <f>COUNTIF(C27:AG27,"A")</f>
         <v/>
       </c>
-      <c r="AI27" s="6">
+      <c r="AI27" s="8">
         <f>COUNTIF(C27:AG27,"F")</f>
         <v/>
       </c>
-      <c r="AJ27" s="6">
+      <c r="AJ27" s="8">
         <f>COUNTIF(C27:AG27,"R")</f>
         <v/>
       </c>
-      <c r="AK27" s="6">
+      <c r="AK27" s="8">
         <f>COUNTIF(C27:AG27,"V")</f>
         <v/>
       </c>
-      <c r="AL27" s="6">
+      <c r="AL27" s="8">
         <f>COUNTIF(C27:AG27,"I")</f>
         <v/>
       </c>
@@ -2004,23 +2014,23 @@
       <c r="AE28" s="7" t="n"/>
       <c r="AF28" s="7" t="n"/>
       <c r="AG28" s="7" t="n"/>
-      <c r="AH28" s="6">
+      <c r="AH28" s="8">
         <f>COUNTIF(C28:AG28,"A")</f>
         <v/>
       </c>
-      <c r="AI28" s="6">
+      <c r="AI28" s="8">
         <f>COUNTIF(C28:AG28,"F")</f>
         <v/>
       </c>
-      <c r="AJ28" s="6">
+      <c r="AJ28" s="8">
         <f>COUNTIF(C28:AG28,"R")</f>
         <v/>
       </c>
-      <c r="AK28" s="6">
+      <c r="AK28" s="8">
         <f>COUNTIF(C28:AG28,"V")</f>
         <v/>
       </c>
-      <c r="AL28" s="6">
+      <c r="AL28" s="8">
         <f>COUNTIF(C28:AG28,"I")</f>
         <v/>
       </c>
@@ -2061,23 +2071,23 @@
       <c r="AE29" s="7" t="n"/>
       <c r="AF29" s="7" t="n"/>
       <c r="AG29" s="7" t="n"/>
-      <c r="AH29" s="6">
+      <c r="AH29" s="8">
         <f>COUNTIF(C29:AG29,"A")</f>
         <v/>
       </c>
-      <c r="AI29" s="6">
+      <c r="AI29" s="8">
         <f>COUNTIF(C29:AG29,"F")</f>
         <v/>
       </c>
-      <c r="AJ29" s="6">
+      <c r="AJ29" s="8">
         <f>COUNTIF(C29:AG29,"R")</f>
         <v/>
       </c>
-      <c r="AK29" s="6">
+      <c r="AK29" s="8">
         <f>COUNTIF(C29:AG29,"V")</f>
         <v/>
       </c>
-      <c r="AL29" s="6">
+      <c r="AL29" s="8">
         <f>COUNTIF(C29:AG29,"I")</f>
         <v/>
       </c>
@@ -2118,23 +2128,23 @@
       <c r="AE30" s="7" t="n"/>
       <c r="AF30" s="7" t="n"/>
       <c r="AG30" s="7" t="n"/>
-      <c r="AH30" s="6">
+      <c r="AH30" s="8">
         <f>COUNTIF(C30:AG30,"A")</f>
         <v/>
       </c>
-      <c r="AI30" s="6">
+      <c r="AI30" s="8">
         <f>COUNTIF(C30:AG30,"F")</f>
         <v/>
       </c>
-      <c r="AJ30" s="6">
+      <c r="AJ30" s="8">
         <f>COUNTIF(C30:AG30,"R")</f>
         <v/>
       </c>
-      <c r="AK30" s="6">
+      <c r="AK30" s="8">
         <f>COUNTIF(C30:AG30,"V")</f>
         <v/>
       </c>
-      <c r="AL30" s="6">
+      <c r="AL30" s="8">
         <f>COUNTIF(C30:AG30,"I")</f>
         <v/>
       </c>
@@ -2175,23 +2185,23 @@
       <c r="AE31" s="7" t="n"/>
       <c r="AF31" s="7" t="n"/>
       <c r="AG31" s="7" t="n"/>
-      <c r="AH31" s="6">
+      <c r="AH31" s="8">
         <f>COUNTIF(C31:AG31,"A")</f>
         <v/>
       </c>
-      <c r="AI31" s="6">
+      <c r="AI31" s="8">
         <f>COUNTIF(C31:AG31,"F")</f>
         <v/>
       </c>
-      <c r="AJ31" s="6">
+      <c r="AJ31" s="8">
         <f>COUNTIF(C31:AG31,"R")</f>
         <v/>
       </c>
-      <c r="AK31" s="6">
+      <c r="AK31" s="8">
         <f>COUNTIF(C31:AG31,"V")</f>
         <v/>
       </c>
-      <c r="AL31" s="6">
+      <c r="AL31" s="8">
         <f>COUNTIF(C31:AG31,"I")</f>
         <v/>
       </c>
@@ -2232,23 +2242,23 @@
       <c r="AE32" s="7" t="n"/>
       <c r="AF32" s="7" t="n"/>
       <c r="AG32" s="7" t="n"/>
-      <c r="AH32" s="6">
+      <c r="AH32" s="8">
         <f>COUNTIF(C32:AG32,"A")</f>
         <v/>
       </c>
-      <c r="AI32" s="6">
+      <c r="AI32" s="8">
         <f>COUNTIF(C32:AG32,"F")</f>
         <v/>
       </c>
-      <c r="AJ32" s="6">
+      <c r="AJ32" s="8">
         <f>COUNTIF(C32:AG32,"R")</f>
         <v/>
       </c>
-      <c r="AK32" s="6">
+      <c r="AK32" s="8">
         <f>COUNTIF(C32:AG32,"V")</f>
         <v/>
       </c>
-      <c r="AL32" s="6">
+      <c r="AL32" s="8">
         <f>COUNTIF(C32:AG32,"I")</f>
         <v/>
       </c>
@@ -2289,23 +2299,23 @@
       <c r="AE33" s="7" t="n"/>
       <c r="AF33" s="7" t="n"/>
       <c r="AG33" s="7" t="n"/>
-      <c r="AH33" s="6">
+      <c r="AH33" s="8">
         <f>COUNTIF(C33:AG33,"A")</f>
         <v/>
       </c>
-      <c r="AI33" s="6">
+      <c r="AI33" s="8">
         <f>COUNTIF(C33:AG33,"F")</f>
         <v/>
       </c>
-      <c r="AJ33" s="6">
+      <c r="AJ33" s="8">
         <f>COUNTIF(C33:AG33,"R")</f>
         <v/>
       </c>
-      <c r="AK33" s="6">
+      <c r="AK33" s="8">
         <f>COUNTIF(C33:AG33,"V")</f>
         <v/>
       </c>
-      <c r="AL33" s="6">
+      <c r="AL33" s="8">
         <f>COUNTIF(C33:AG33,"I")</f>
         <v/>
       </c>
@@ -2346,23 +2356,23 @@
       <c r="AE34" s="7" t="n"/>
       <c r="AF34" s="7" t="n"/>
       <c r="AG34" s="7" t="n"/>
-      <c r="AH34" s="6">
+      <c r="AH34" s="8">
         <f>COUNTIF(C34:AG34,"A")</f>
         <v/>
       </c>
-      <c r="AI34" s="6">
+      <c r="AI34" s="8">
         <f>COUNTIF(C34:AG34,"F")</f>
         <v/>
       </c>
-      <c r="AJ34" s="6">
+      <c r="AJ34" s="8">
         <f>COUNTIF(C34:AG34,"R")</f>
         <v/>
       </c>
-      <c r="AK34" s="6">
+      <c r="AK34" s="8">
         <f>COUNTIF(C34:AG34,"V")</f>
         <v/>
       </c>
-      <c r="AL34" s="6">
+      <c r="AL34" s="8">
         <f>COUNTIF(C34:AG34,"I")</f>
         <v/>
       </c>
@@ -2403,23 +2413,23 @@
       <c r="AE35" s="7" t="n"/>
       <c r="AF35" s="7" t="n"/>
       <c r="AG35" s="7" t="n"/>
-      <c r="AH35" s="6">
+      <c r="AH35" s="8">
         <f>COUNTIF(C35:AG35,"A")</f>
         <v/>
       </c>
-      <c r="AI35" s="6">
+      <c r="AI35" s="8">
         <f>COUNTIF(C35:AG35,"F")</f>
         <v/>
       </c>
-      <c r="AJ35" s="6">
+      <c r="AJ35" s="8">
         <f>COUNTIF(C35:AG35,"R")</f>
         <v/>
       </c>
-      <c r="AK35" s="6">
+      <c r="AK35" s="8">
         <f>COUNTIF(C35:AG35,"V")</f>
         <v/>
       </c>
-      <c r="AL35" s="6">
+      <c r="AL35" s="8">
         <f>COUNTIF(C35:AG35,"I")</f>
         <v/>
       </c>
@@ -2460,32 +2470,32 @@
       <c r="AE36" s="7" t="n"/>
       <c r="AF36" s="7" t="n"/>
       <c r="AG36" s="7" t="n"/>
-      <c r="AH36" s="6">
+      <c r="AH36" s="8">
         <f>COUNTIF(C36:AG36,"A")</f>
         <v/>
       </c>
-      <c r="AI36" s="6">
+      <c r="AI36" s="8">
         <f>COUNTIF(C36:AG36,"F")</f>
         <v/>
       </c>
-      <c r="AJ36" s="6">
+      <c r="AJ36" s="8">
         <f>COUNTIF(C36:AG36,"R")</f>
         <v/>
       </c>
-      <c r="AK36" s="6">
+      <c r="AK36" s="8">
         <f>COUNTIF(C36:AG36,"V")</f>
         <v/>
       </c>
-      <c r="AL36" s="6">
+      <c r="AL36" s="8">
         <f>COUNTIF(C36:AG36,"I")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="C4:J4"/>
     <mergeCell ref="A1:AL1"/>
-    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="C5:J5"/>
     <mergeCell ref="A2:AL2"/>
   </mergeCells>
   <dataValidations count="1">
@@ -2513,61 +2523,61 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Control de asistencia</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Guía de uso</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Escribe el mes y los nombres de tus empleados (hasta 30).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Cada día selecciona la clave en la lista: A, F, R, V, I, D o P.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Las columnas finales suman automáticamente asistencias, faltas, retardos, vacaciones e incapacidades.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Imprime en horizontal; cabe en una sola hoja.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
         </is>

--- a/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
+++ b/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -235,7 +235,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -260,8 +262,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -699,6 +705,7 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -756,6 +763,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -787,6 +795,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="13" t="n"/>
@@ -801,6 +810,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -949,6 +959,7 @@
       <c r="AK2" s="22" t="n"/>
       <c r="AL2" s="23" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="24" t="inlineStr">
         <is>
@@ -1172,1716 +1183,1717 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="26" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="9" t="n"/>
-      <c r="C7" s="26" t="n"/>
-      <c r="D7" s="26" t="n"/>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="26" t="n"/>
-      <c r="G7" s="26" t="n"/>
-      <c r="H7" s="26" t="n"/>
-      <c r="I7" s="26" t="n"/>
-      <c r="J7" s="26" t="n"/>
-      <c r="K7" s="26" t="n"/>
-      <c r="L7" s="26" t="n"/>
-      <c r="M7" s="26" t="n"/>
-      <c r="N7" s="26" t="n"/>
-      <c r="O7" s="26" t="n"/>
-      <c r="P7" s="26" t="n"/>
-      <c r="Q7" s="26" t="n"/>
-      <c r="R7" s="26" t="n"/>
-      <c r="S7" s="26" t="n"/>
-      <c r="T7" s="26" t="n"/>
-      <c r="U7" s="26" t="n"/>
-      <c r="V7" s="26" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
-      <c r="Y7" s="26" t="n"/>
-      <c r="Z7" s="26" t="n"/>
-      <c r="AA7" s="26" t="n"/>
-      <c r="AB7" s="26" t="n"/>
-      <c r="AC7" s="26" t="n"/>
-      <c r="AD7" s="26" t="n"/>
-      <c r="AE7" s="26" t="n"/>
-      <c r="AF7" s="26" t="n"/>
-      <c r="AG7" s="26" t="n"/>
-      <c r="AH7" s="27">
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="27" t="n"/>
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="27" t="n"/>
+      <c r="P7" s="27" t="n"/>
+      <c r="Q7" s="27" t="n"/>
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n"/>
+      <c r="T7" s="27" t="n"/>
+      <c r="U7" s="27" t="n"/>
+      <c r="V7" s="27" t="n"/>
+      <c r="W7" s="27" t="n"/>
+      <c r="X7" s="27" t="n"/>
+      <c r="Y7" s="27" t="n"/>
+      <c r="Z7" s="27" t="n"/>
+      <c r="AA7" s="27" t="n"/>
+      <c r="AB7" s="27" t="n"/>
+      <c r="AC7" s="27" t="n"/>
+      <c r="AD7" s="27" t="n"/>
+      <c r="AE7" s="27" t="n"/>
+      <c r="AF7" s="27" t="n"/>
+      <c r="AG7" s="27" t="n"/>
+      <c r="AH7" s="28">
         <f>COUNTIF(C7:AG7,"A")</f>
         <v/>
       </c>
-      <c r="AI7" s="27">
+      <c r="AI7" s="28">
         <f>COUNTIF(C7:AG7,"F")</f>
         <v/>
       </c>
-      <c r="AJ7" s="27">
+      <c r="AJ7" s="28">
         <f>COUNTIF(C7:AG7,"R")</f>
         <v/>
       </c>
-      <c r="AK7" s="27">
+      <c r="AK7" s="28">
         <f>COUNTIF(C7:AG7,"V")</f>
         <v/>
       </c>
-      <c r="AL7" s="27">
+      <c r="AL7" s="28">
         <f>COUNTIF(C7:AG7,"I")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="26" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="9" t="n"/>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="26" t="n"/>
-      <c r="G8" s="26" t="n"/>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="26" t="n"/>
-      <c r="J8" s="26" t="n"/>
-      <c r="K8" s="26" t="n"/>
-      <c r="L8" s="26" t="n"/>
-      <c r="M8" s="26" t="n"/>
-      <c r="N8" s="26" t="n"/>
-      <c r="O8" s="26" t="n"/>
-      <c r="P8" s="26" t="n"/>
-      <c r="Q8" s="26" t="n"/>
-      <c r="R8" s="26" t="n"/>
-      <c r="S8" s="26" t="n"/>
-      <c r="T8" s="26" t="n"/>
-      <c r="U8" s="26" t="n"/>
-      <c r="V8" s="26" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
-      <c r="Y8" s="26" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="26" t="n"/>
-      <c r="AB8" s="26" t="n"/>
-      <c r="AC8" s="26" t="n"/>
-      <c r="AD8" s="26" t="n"/>
-      <c r="AE8" s="26" t="n"/>
-      <c r="AF8" s="26" t="n"/>
-      <c r="AG8" s="26" t="n"/>
-      <c r="AH8" s="27">
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
+      <c r="H8" s="27" t="n"/>
+      <c r="I8" s="27" t="n"/>
+      <c r="J8" s="27" t="n"/>
+      <c r="K8" s="27" t="n"/>
+      <c r="L8" s="27" t="n"/>
+      <c r="M8" s="27" t="n"/>
+      <c r="N8" s="27" t="n"/>
+      <c r="O8" s="27" t="n"/>
+      <c r="P8" s="27" t="n"/>
+      <c r="Q8" s="27" t="n"/>
+      <c r="R8" s="27" t="n"/>
+      <c r="S8" s="27" t="n"/>
+      <c r="T8" s="27" t="n"/>
+      <c r="U8" s="27" t="n"/>
+      <c r="V8" s="27" t="n"/>
+      <c r="W8" s="27" t="n"/>
+      <c r="X8" s="27" t="n"/>
+      <c r="Y8" s="27" t="n"/>
+      <c r="Z8" s="27" t="n"/>
+      <c r="AA8" s="27" t="n"/>
+      <c r="AB8" s="27" t="n"/>
+      <c r="AC8" s="27" t="n"/>
+      <c r="AD8" s="27" t="n"/>
+      <c r="AE8" s="27" t="n"/>
+      <c r="AF8" s="27" t="n"/>
+      <c r="AG8" s="27" t="n"/>
+      <c r="AH8" s="28">
         <f>COUNTIF(C8:AG8,"A")</f>
         <v/>
       </c>
-      <c r="AI8" s="27">
+      <c r="AI8" s="28">
         <f>COUNTIF(C8:AG8,"F")</f>
         <v/>
       </c>
-      <c r="AJ8" s="27">
+      <c r="AJ8" s="28">
         <f>COUNTIF(C8:AG8,"R")</f>
         <v/>
       </c>
-      <c r="AK8" s="27">
+      <c r="AK8" s="28">
         <f>COUNTIF(C8:AG8,"V")</f>
         <v/>
       </c>
-      <c r="AL8" s="27">
+      <c r="AL8" s="28">
         <f>COUNTIF(C8:AG8,"I")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="26" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
-      <c r="F9" s="26" t="n"/>
-      <c r="G9" s="26" t="n"/>
-      <c r="H9" s="26" t="n"/>
-      <c r="I9" s="26" t="n"/>
-      <c r="J9" s="26" t="n"/>
-      <c r="K9" s="26" t="n"/>
-      <c r="L9" s="26" t="n"/>
-      <c r="M9" s="26" t="n"/>
-      <c r="N9" s="26" t="n"/>
-      <c r="O9" s="26" t="n"/>
-      <c r="P9" s="26" t="n"/>
-      <c r="Q9" s="26" t="n"/>
-      <c r="R9" s="26" t="n"/>
-      <c r="S9" s="26" t="n"/>
-      <c r="T9" s="26" t="n"/>
-      <c r="U9" s="26" t="n"/>
-      <c r="V9" s="26" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
-      <c r="Y9" s="26" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="26" t="n"/>
-      <c r="AB9" s="26" t="n"/>
-      <c r="AC9" s="26" t="n"/>
-      <c r="AD9" s="26" t="n"/>
-      <c r="AE9" s="26" t="n"/>
-      <c r="AF9" s="26" t="n"/>
-      <c r="AG9" s="26" t="n"/>
-      <c r="AH9" s="27">
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="27" t="n"/>
+      <c r="J9" s="27" t="n"/>
+      <c r="K9" s="27" t="n"/>
+      <c r="L9" s="27" t="n"/>
+      <c r="M9" s="27" t="n"/>
+      <c r="N9" s="27" t="n"/>
+      <c r="O9" s="27" t="n"/>
+      <c r="P9" s="27" t="n"/>
+      <c r="Q9" s="27" t="n"/>
+      <c r="R9" s="27" t="n"/>
+      <c r="S9" s="27" t="n"/>
+      <c r="T9" s="27" t="n"/>
+      <c r="U9" s="27" t="n"/>
+      <c r="V9" s="27" t="n"/>
+      <c r="W9" s="27" t="n"/>
+      <c r="X9" s="27" t="n"/>
+      <c r="Y9" s="27" t="n"/>
+      <c r="Z9" s="27" t="n"/>
+      <c r="AA9" s="27" t="n"/>
+      <c r="AB9" s="27" t="n"/>
+      <c r="AC9" s="27" t="n"/>
+      <c r="AD9" s="27" t="n"/>
+      <c r="AE9" s="27" t="n"/>
+      <c r="AF9" s="27" t="n"/>
+      <c r="AG9" s="27" t="n"/>
+      <c r="AH9" s="28">
         <f>COUNTIF(C9:AG9,"A")</f>
         <v/>
       </c>
-      <c r="AI9" s="27">
+      <c r="AI9" s="28">
         <f>COUNTIF(C9:AG9,"F")</f>
         <v/>
       </c>
-      <c r="AJ9" s="27">
+      <c r="AJ9" s="28">
         <f>COUNTIF(C9:AG9,"R")</f>
         <v/>
       </c>
-      <c r="AK9" s="27">
+      <c r="AK9" s="28">
         <f>COUNTIF(C9:AG9,"V")</f>
         <v/>
       </c>
-      <c r="AL9" s="27">
+      <c r="AL9" s="28">
         <f>COUNTIF(C9:AG9,"I")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="26" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="9" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="26" t="n"/>
-      <c r="I10" s="26" t="n"/>
-      <c r="J10" s="26" t="n"/>
-      <c r="K10" s="26" t="n"/>
-      <c r="L10" s="26" t="n"/>
-      <c r="M10" s="26" t="n"/>
-      <c r="N10" s="26" t="n"/>
-      <c r="O10" s="26" t="n"/>
-      <c r="P10" s="26" t="n"/>
-      <c r="Q10" s="26" t="n"/>
-      <c r="R10" s="26" t="n"/>
-      <c r="S10" s="26" t="n"/>
-      <c r="T10" s="26" t="n"/>
-      <c r="U10" s="26" t="n"/>
-      <c r="V10" s="26" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
-      <c r="Y10" s="26" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="26" t="n"/>
-      <c r="AB10" s="26" t="n"/>
-      <c r="AC10" s="26" t="n"/>
-      <c r="AD10" s="26" t="n"/>
-      <c r="AE10" s="26" t="n"/>
-      <c r="AF10" s="26" t="n"/>
-      <c r="AG10" s="26" t="n"/>
-      <c r="AH10" s="27">
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="27" t="n"/>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="27" t="n"/>
+      <c r="J10" s="27" t="n"/>
+      <c r="K10" s="27" t="n"/>
+      <c r="L10" s="27" t="n"/>
+      <c r="M10" s="27" t="n"/>
+      <c r="N10" s="27" t="n"/>
+      <c r="O10" s="27" t="n"/>
+      <c r="P10" s="27" t="n"/>
+      <c r="Q10" s="27" t="n"/>
+      <c r="R10" s="27" t="n"/>
+      <c r="S10" s="27" t="n"/>
+      <c r="T10" s="27" t="n"/>
+      <c r="U10" s="27" t="n"/>
+      <c r="V10" s="27" t="n"/>
+      <c r="W10" s="27" t="n"/>
+      <c r="X10" s="27" t="n"/>
+      <c r="Y10" s="27" t="n"/>
+      <c r="Z10" s="27" t="n"/>
+      <c r="AA10" s="27" t="n"/>
+      <c r="AB10" s="27" t="n"/>
+      <c r="AC10" s="27" t="n"/>
+      <c r="AD10" s="27" t="n"/>
+      <c r="AE10" s="27" t="n"/>
+      <c r="AF10" s="27" t="n"/>
+      <c r="AG10" s="27" t="n"/>
+      <c r="AH10" s="28">
         <f>COUNTIF(C10:AG10,"A")</f>
         <v/>
       </c>
-      <c r="AI10" s="27">
+      <c r="AI10" s="28">
         <f>COUNTIF(C10:AG10,"F")</f>
         <v/>
       </c>
-      <c r="AJ10" s="27">
+      <c r="AJ10" s="28">
         <f>COUNTIF(C10:AG10,"R")</f>
         <v/>
       </c>
-      <c r="AK10" s="27">
+      <c r="AK10" s="28">
         <f>COUNTIF(C10:AG10,"V")</f>
         <v/>
       </c>
-      <c r="AL10" s="27">
+      <c r="AL10" s="28">
         <f>COUNTIF(C10:AG10,"I")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="26" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="9" t="n"/>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="26" t="n"/>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="26" t="n"/>
-      <c r="J11" s="26" t="n"/>
-      <c r="K11" s="26" t="n"/>
-      <c r="L11" s="26" t="n"/>
-      <c r="M11" s="26" t="n"/>
-      <c r="N11" s="26" t="n"/>
-      <c r="O11" s="26" t="n"/>
-      <c r="P11" s="26" t="n"/>
-      <c r="Q11" s="26" t="n"/>
-      <c r="R11" s="26" t="n"/>
-      <c r="S11" s="26" t="n"/>
-      <c r="T11" s="26" t="n"/>
-      <c r="U11" s="26" t="n"/>
-      <c r="V11" s="26" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="26" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="26" t="n"/>
-      <c r="AB11" s="26" t="n"/>
-      <c r="AC11" s="26" t="n"/>
-      <c r="AD11" s="26" t="n"/>
-      <c r="AE11" s="26" t="n"/>
-      <c r="AF11" s="26" t="n"/>
-      <c r="AG11" s="26" t="n"/>
-      <c r="AH11" s="27">
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
+      <c r="H11" s="27" t="n"/>
+      <c r="I11" s="27" t="n"/>
+      <c r="J11" s="27" t="n"/>
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="27" t="n"/>
+      <c r="M11" s="27" t="n"/>
+      <c r="N11" s="27" t="n"/>
+      <c r="O11" s="27" t="n"/>
+      <c r="P11" s="27" t="n"/>
+      <c r="Q11" s="27" t="n"/>
+      <c r="R11" s="27" t="n"/>
+      <c r="S11" s="27" t="n"/>
+      <c r="T11" s="27" t="n"/>
+      <c r="U11" s="27" t="n"/>
+      <c r="V11" s="27" t="n"/>
+      <c r="W11" s="27" t="n"/>
+      <c r="X11" s="27" t="n"/>
+      <c r="Y11" s="27" t="n"/>
+      <c r="Z11" s="27" t="n"/>
+      <c r="AA11" s="27" t="n"/>
+      <c r="AB11" s="27" t="n"/>
+      <c r="AC11" s="27" t="n"/>
+      <c r="AD11" s="27" t="n"/>
+      <c r="AE11" s="27" t="n"/>
+      <c r="AF11" s="27" t="n"/>
+      <c r="AG11" s="27" t="n"/>
+      <c r="AH11" s="28">
         <f>COUNTIF(C11:AG11,"A")</f>
         <v/>
       </c>
-      <c r="AI11" s="27">
+      <c r="AI11" s="28">
         <f>COUNTIF(C11:AG11,"F")</f>
         <v/>
       </c>
-      <c r="AJ11" s="27">
+      <c r="AJ11" s="28">
         <f>COUNTIF(C11:AG11,"R")</f>
         <v/>
       </c>
-      <c r="AK11" s="27">
+      <c r="AK11" s="28">
         <f>COUNTIF(C11:AG11,"V")</f>
         <v/>
       </c>
-      <c r="AL11" s="27">
+      <c r="AL11" s="28">
         <f>COUNTIF(C11:AG11,"I")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="26" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="9" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="26" t="n"/>
-      <c r="O12" s="26" t="n"/>
-      <c r="P12" s="26" t="n"/>
-      <c r="Q12" s="26" t="n"/>
-      <c r="R12" s="26" t="n"/>
-      <c r="S12" s="26" t="n"/>
-      <c r="T12" s="26" t="n"/>
-      <c r="U12" s="26" t="n"/>
-      <c r="V12" s="26" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="26" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="26" t="n"/>
-      <c r="AB12" s="26" t="n"/>
-      <c r="AC12" s="26" t="n"/>
-      <c r="AD12" s="26" t="n"/>
-      <c r="AE12" s="26" t="n"/>
-      <c r="AF12" s="26" t="n"/>
-      <c r="AG12" s="26" t="n"/>
-      <c r="AH12" s="27">
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="27" t="n"/>
+      <c r="J12" s="27" t="n"/>
+      <c r="K12" s="27" t="n"/>
+      <c r="L12" s="27" t="n"/>
+      <c r="M12" s="27" t="n"/>
+      <c r="N12" s="27" t="n"/>
+      <c r="O12" s="27" t="n"/>
+      <c r="P12" s="27" t="n"/>
+      <c r="Q12" s="27" t="n"/>
+      <c r="R12" s="27" t="n"/>
+      <c r="S12" s="27" t="n"/>
+      <c r="T12" s="27" t="n"/>
+      <c r="U12" s="27" t="n"/>
+      <c r="V12" s="27" t="n"/>
+      <c r="W12" s="27" t="n"/>
+      <c r="X12" s="27" t="n"/>
+      <c r="Y12" s="27" t="n"/>
+      <c r="Z12" s="27" t="n"/>
+      <c r="AA12" s="27" t="n"/>
+      <c r="AB12" s="27" t="n"/>
+      <c r="AC12" s="27" t="n"/>
+      <c r="AD12" s="27" t="n"/>
+      <c r="AE12" s="27" t="n"/>
+      <c r="AF12" s="27" t="n"/>
+      <c r="AG12" s="27" t="n"/>
+      <c r="AH12" s="28">
         <f>COUNTIF(C12:AG12,"A")</f>
         <v/>
       </c>
-      <c r="AI12" s="27">
+      <c r="AI12" s="28">
         <f>COUNTIF(C12:AG12,"F")</f>
         <v/>
       </c>
-      <c r="AJ12" s="27">
+      <c r="AJ12" s="28">
         <f>COUNTIF(C12:AG12,"R")</f>
         <v/>
       </c>
-      <c r="AK12" s="27">
+      <c r="AK12" s="28">
         <f>COUNTIF(C12:AG12,"V")</f>
         <v/>
       </c>
-      <c r="AL12" s="27">
+      <c r="AL12" s="28">
         <f>COUNTIF(C12:AG12,"I")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="26" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="26" t="n"/>
-      <c r="G13" s="26" t="n"/>
-      <c r="H13" s="26" t="n"/>
-      <c r="I13" s="26" t="n"/>
-      <c r="J13" s="26" t="n"/>
-      <c r="K13" s="26" t="n"/>
-      <c r="L13" s="26" t="n"/>
-      <c r="M13" s="26" t="n"/>
-      <c r="N13" s="26" t="n"/>
-      <c r="O13" s="26" t="n"/>
-      <c r="P13" s="26" t="n"/>
-      <c r="Q13" s="26" t="n"/>
-      <c r="R13" s="26" t="n"/>
-      <c r="S13" s="26" t="n"/>
-      <c r="T13" s="26" t="n"/>
-      <c r="U13" s="26" t="n"/>
-      <c r="V13" s="26" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
-      <c r="Y13" s="26" t="n"/>
-      <c r="Z13" s="26" t="n"/>
-      <c r="AA13" s="26" t="n"/>
-      <c r="AB13" s="26" t="n"/>
-      <c r="AC13" s="26" t="n"/>
-      <c r="AD13" s="26" t="n"/>
-      <c r="AE13" s="26" t="n"/>
-      <c r="AF13" s="26" t="n"/>
-      <c r="AG13" s="26" t="n"/>
-      <c r="AH13" s="27">
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="27" t="n"/>
+      <c r="H13" s="27" t="n"/>
+      <c r="I13" s="27" t="n"/>
+      <c r="J13" s="27" t="n"/>
+      <c r="K13" s="27" t="n"/>
+      <c r="L13" s="27" t="n"/>
+      <c r="M13" s="27" t="n"/>
+      <c r="N13" s="27" t="n"/>
+      <c r="O13" s="27" t="n"/>
+      <c r="P13" s="27" t="n"/>
+      <c r="Q13" s="27" t="n"/>
+      <c r="R13" s="27" t="n"/>
+      <c r="S13" s="27" t="n"/>
+      <c r="T13" s="27" t="n"/>
+      <c r="U13" s="27" t="n"/>
+      <c r="V13" s="27" t="n"/>
+      <c r="W13" s="27" t="n"/>
+      <c r="X13" s="27" t="n"/>
+      <c r="Y13" s="27" t="n"/>
+      <c r="Z13" s="27" t="n"/>
+      <c r="AA13" s="27" t="n"/>
+      <c r="AB13" s="27" t="n"/>
+      <c r="AC13" s="27" t="n"/>
+      <c r="AD13" s="27" t="n"/>
+      <c r="AE13" s="27" t="n"/>
+      <c r="AF13" s="27" t="n"/>
+      <c r="AG13" s="27" t="n"/>
+      <c r="AH13" s="28">
         <f>COUNTIF(C13:AG13,"A")</f>
         <v/>
       </c>
-      <c r="AI13" s="27">
+      <c r="AI13" s="28">
         <f>COUNTIF(C13:AG13,"F")</f>
         <v/>
       </c>
-      <c r="AJ13" s="27">
+      <c r="AJ13" s="28">
         <f>COUNTIF(C13:AG13,"R")</f>
         <v/>
       </c>
-      <c r="AK13" s="27">
+      <c r="AK13" s="28">
         <f>COUNTIF(C13:AG13,"V")</f>
         <v/>
       </c>
-      <c r="AL13" s="27">
+      <c r="AL13" s="28">
         <f>COUNTIF(C13:AG13,"I")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="26" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="9" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="26" t="n"/>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="26" t="n"/>
-      <c r="L14" s="26" t="n"/>
-      <c r="M14" s="26" t="n"/>
-      <c r="N14" s="26" t="n"/>
-      <c r="O14" s="26" t="n"/>
-      <c r="P14" s="26" t="n"/>
-      <c r="Q14" s="26" t="n"/>
-      <c r="R14" s="26" t="n"/>
-      <c r="S14" s="26" t="n"/>
-      <c r="T14" s="26" t="n"/>
-      <c r="U14" s="26" t="n"/>
-      <c r="V14" s="26" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="26" t="n"/>
-      <c r="Z14" s="26" t="n"/>
-      <c r="AA14" s="26" t="n"/>
-      <c r="AB14" s="26" t="n"/>
-      <c r="AC14" s="26" t="n"/>
-      <c r="AD14" s="26" t="n"/>
-      <c r="AE14" s="26" t="n"/>
-      <c r="AF14" s="26" t="n"/>
-      <c r="AG14" s="26" t="n"/>
-      <c r="AH14" s="27">
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="27" t="n"/>
+      <c r="O14" s="27" t="n"/>
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="27" t="n"/>
+      <c r="R14" s="27" t="n"/>
+      <c r="S14" s="27" t="n"/>
+      <c r="T14" s="27" t="n"/>
+      <c r="U14" s="27" t="n"/>
+      <c r="V14" s="27" t="n"/>
+      <c r="W14" s="27" t="n"/>
+      <c r="X14" s="27" t="n"/>
+      <c r="Y14" s="27" t="n"/>
+      <c r="Z14" s="27" t="n"/>
+      <c r="AA14" s="27" t="n"/>
+      <c r="AB14" s="27" t="n"/>
+      <c r="AC14" s="27" t="n"/>
+      <c r="AD14" s="27" t="n"/>
+      <c r="AE14" s="27" t="n"/>
+      <c r="AF14" s="27" t="n"/>
+      <c r="AG14" s="27" t="n"/>
+      <c r="AH14" s="28">
         <f>COUNTIF(C14:AG14,"A")</f>
         <v/>
       </c>
-      <c r="AI14" s="27">
+      <c r="AI14" s="28">
         <f>COUNTIF(C14:AG14,"F")</f>
         <v/>
       </c>
-      <c r="AJ14" s="27">
+      <c r="AJ14" s="28">
         <f>COUNTIF(C14:AG14,"R")</f>
         <v/>
       </c>
-      <c r="AK14" s="27">
+      <c r="AK14" s="28">
         <f>COUNTIF(C14:AG14,"V")</f>
         <v/>
       </c>
-      <c r="AL14" s="27">
+      <c r="AL14" s="28">
         <f>COUNTIF(C14:AG14,"I")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="26" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="9" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="26" t="n"/>
-      <c r="H15" s="26" t="n"/>
-      <c r="I15" s="26" t="n"/>
-      <c r="J15" s="26" t="n"/>
-      <c r="K15" s="26" t="n"/>
-      <c r="L15" s="26" t="n"/>
-      <c r="M15" s="26" t="n"/>
-      <c r="N15" s="26" t="n"/>
-      <c r="O15" s="26" t="n"/>
-      <c r="P15" s="26" t="n"/>
-      <c r="Q15" s="26" t="n"/>
-      <c r="R15" s="26" t="n"/>
-      <c r="S15" s="26" t="n"/>
-      <c r="T15" s="26" t="n"/>
-      <c r="U15" s="26" t="n"/>
-      <c r="V15" s="26" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="26" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="26" t="n"/>
-      <c r="AB15" s="26" t="n"/>
-      <c r="AC15" s="26" t="n"/>
-      <c r="AD15" s="26" t="n"/>
-      <c r="AE15" s="26" t="n"/>
-      <c r="AF15" s="26" t="n"/>
-      <c r="AG15" s="26" t="n"/>
-      <c r="AH15" s="27">
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="27" t="n"/>
+      <c r="K15" s="27" t="n"/>
+      <c r="L15" s="27" t="n"/>
+      <c r="M15" s="27" t="n"/>
+      <c r="N15" s="27" t="n"/>
+      <c r="O15" s="27" t="n"/>
+      <c r="P15" s="27" t="n"/>
+      <c r="Q15" s="27" t="n"/>
+      <c r="R15" s="27" t="n"/>
+      <c r="S15" s="27" t="n"/>
+      <c r="T15" s="27" t="n"/>
+      <c r="U15" s="27" t="n"/>
+      <c r="V15" s="27" t="n"/>
+      <c r="W15" s="27" t="n"/>
+      <c r="X15" s="27" t="n"/>
+      <c r="Y15" s="27" t="n"/>
+      <c r="Z15" s="27" t="n"/>
+      <c r="AA15" s="27" t="n"/>
+      <c r="AB15" s="27" t="n"/>
+      <c r="AC15" s="27" t="n"/>
+      <c r="AD15" s="27" t="n"/>
+      <c r="AE15" s="27" t="n"/>
+      <c r="AF15" s="27" t="n"/>
+      <c r="AG15" s="27" t="n"/>
+      <c r="AH15" s="28">
         <f>COUNTIF(C15:AG15,"A")</f>
         <v/>
       </c>
-      <c r="AI15" s="27">
+      <c r="AI15" s="28">
         <f>COUNTIF(C15:AG15,"F")</f>
         <v/>
       </c>
-      <c r="AJ15" s="27">
+      <c r="AJ15" s="28">
         <f>COUNTIF(C15:AG15,"R")</f>
         <v/>
       </c>
-      <c r="AK15" s="27">
+      <c r="AK15" s="28">
         <f>COUNTIF(C15:AG15,"V")</f>
         <v/>
       </c>
-      <c r="AL15" s="27">
+      <c r="AL15" s="28">
         <f>COUNTIF(C15:AG15,"I")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="26" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="9" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="26" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="26" t="n"/>
-      <c r="I16" s="26" t="n"/>
-      <c r="J16" s="26" t="n"/>
-      <c r="K16" s="26" t="n"/>
-      <c r="L16" s="26" t="n"/>
-      <c r="M16" s="26" t="n"/>
-      <c r="N16" s="26" t="n"/>
-      <c r="O16" s="26" t="n"/>
-      <c r="P16" s="26" t="n"/>
-      <c r="Q16" s="26" t="n"/>
-      <c r="R16" s="26" t="n"/>
-      <c r="S16" s="26" t="n"/>
-      <c r="T16" s="26" t="n"/>
-      <c r="U16" s="26" t="n"/>
-      <c r="V16" s="26" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
-      <c r="Y16" s="26" t="n"/>
-      <c r="Z16" s="26" t="n"/>
-      <c r="AA16" s="26" t="n"/>
-      <c r="AB16" s="26" t="n"/>
-      <c r="AC16" s="26" t="n"/>
-      <c r="AD16" s="26" t="n"/>
-      <c r="AE16" s="26" t="n"/>
-      <c r="AF16" s="26" t="n"/>
-      <c r="AG16" s="26" t="n"/>
-      <c r="AH16" s="27">
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="27" t="n"/>
+      <c r="L16" s="27" t="n"/>
+      <c r="M16" s="27" t="n"/>
+      <c r="N16" s="27" t="n"/>
+      <c r="O16" s="27" t="n"/>
+      <c r="P16" s="27" t="n"/>
+      <c r="Q16" s="27" t="n"/>
+      <c r="R16" s="27" t="n"/>
+      <c r="S16" s="27" t="n"/>
+      <c r="T16" s="27" t="n"/>
+      <c r="U16" s="27" t="n"/>
+      <c r="V16" s="27" t="n"/>
+      <c r="W16" s="27" t="n"/>
+      <c r="X16" s="27" t="n"/>
+      <c r="Y16" s="27" t="n"/>
+      <c r="Z16" s="27" t="n"/>
+      <c r="AA16" s="27" t="n"/>
+      <c r="AB16" s="27" t="n"/>
+      <c r="AC16" s="27" t="n"/>
+      <c r="AD16" s="27" t="n"/>
+      <c r="AE16" s="27" t="n"/>
+      <c r="AF16" s="27" t="n"/>
+      <c r="AG16" s="27" t="n"/>
+      <c r="AH16" s="28">
         <f>COUNTIF(C16:AG16,"A")</f>
         <v/>
       </c>
-      <c r="AI16" s="27">
+      <c r="AI16" s="28">
         <f>COUNTIF(C16:AG16,"F")</f>
         <v/>
       </c>
-      <c r="AJ16" s="27">
+      <c r="AJ16" s="28">
         <f>COUNTIF(C16:AG16,"R")</f>
         <v/>
       </c>
-      <c r="AK16" s="27">
+      <c r="AK16" s="28">
         <f>COUNTIF(C16:AG16,"V")</f>
         <v/>
       </c>
-      <c r="AL16" s="27">
+      <c r="AL16" s="28">
         <f>COUNTIF(C16:AG16,"I")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="26" t="n">
         <v>11</v>
       </c>
       <c r="B17" s="9" t="n"/>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="26" t="n"/>
-      <c r="G17" s="26" t="n"/>
-      <c r="H17" s="26" t="n"/>
-      <c r="I17" s="26" t="n"/>
-      <c r="J17" s="26" t="n"/>
-      <c r="K17" s="26" t="n"/>
-      <c r="L17" s="26" t="n"/>
-      <c r="M17" s="26" t="n"/>
-      <c r="N17" s="26" t="n"/>
-      <c r="O17" s="26" t="n"/>
-      <c r="P17" s="26" t="n"/>
-      <c r="Q17" s="26" t="n"/>
-      <c r="R17" s="26" t="n"/>
-      <c r="S17" s="26" t="n"/>
-      <c r="T17" s="26" t="n"/>
-      <c r="U17" s="26" t="n"/>
-      <c r="V17" s="26" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="26" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="26" t="n"/>
-      <c r="AB17" s="26" t="n"/>
-      <c r="AC17" s="26" t="n"/>
-      <c r="AD17" s="26" t="n"/>
-      <c r="AE17" s="26" t="n"/>
-      <c r="AF17" s="26" t="n"/>
-      <c r="AG17" s="26" t="n"/>
-      <c r="AH17" s="27">
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="27" t="n"/>
+      <c r="L17" s="27" t="n"/>
+      <c r="M17" s="27" t="n"/>
+      <c r="N17" s="27" t="n"/>
+      <c r="O17" s="27" t="n"/>
+      <c r="P17" s="27" t="n"/>
+      <c r="Q17" s="27" t="n"/>
+      <c r="R17" s="27" t="n"/>
+      <c r="S17" s="27" t="n"/>
+      <c r="T17" s="27" t="n"/>
+      <c r="U17" s="27" t="n"/>
+      <c r="V17" s="27" t="n"/>
+      <c r="W17" s="27" t="n"/>
+      <c r="X17" s="27" t="n"/>
+      <c r="Y17" s="27" t="n"/>
+      <c r="Z17" s="27" t="n"/>
+      <c r="AA17" s="27" t="n"/>
+      <c r="AB17" s="27" t="n"/>
+      <c r="AC17" s="27" t="n"/>
+      <c r="AD17" s="27" t="n"/>
+      <c r="AE17" s="27" t="n"/>
+      <c r="AF17" s="27" t="n"/>
+      <c r="AG17" s="27" t="n"/>
+      <c r="AH17" s="28">
         <f>COUNTIF(C17:AG17,"A")</f>
         <v/>
       </c>
-      <c r="AI17" s="27">
+      <c r="AI17" s="28">
         <f>COUNTIF(C17:AG17,"F")</f>
         <v/>
       </c>
-      <c r="AJ17" s="27">
+      <c r="AJ17" s="28">
         <f>COUNTIF(C17:AG17,"R")</f>
         <v/>
       </c>
-      <c r="AK17" s="27">
+      <c r="AK17" s="28">
         <f>COUNTIF(C17:AG17,"V")</f>
         <v/>
       </c>
-      <c r="AL17" s="27">
+      <c r="AL17" s="28">
         <f>COUNTIF(C17:AG17,"I")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="26" t="n">
         <v>12</v>
       </c>
       <c r="B18" s="9" t="n"/>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="26" t="n"/>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="26" t="n"/>
-      <c r="K18" s="26" t="n"/>
-      <c r="L18" s="26" t="n"/>
-      <c r="M18" s="26" t="n"/>
-      <c r="N18" s="26" t="n"/>
-      <c r="O18" s="26" t="n"/>
-      <c r="P18" s="26" t="n"/>
-      <c r="Q18" s="26" t="n"/>
-      <c r="R18" s="26" t="n"/>
-      <c r="S18" s="26" t="n"/>
-      <c r="T18" s="26" t="n"/>
-      <c r="U18" s="26" t="n"/>
-      <c r="V18" s="26" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="26" t="n"/>
-      <c r="Z18" s="26" t="n"/>
-      <c r="AA18" s="26" t="n"/>
-      <c r="AB18" s="26" t="n"/>
-      <c r="AC18" s="26" t="n"/>
-      <c r="AD18" s="26" t="n"/>
-      <c r="AE18" s="26" t="n"/>
-      <c r="AF18" s="26" t="n"/>
-      <c r="AG18" s="26" t="n"/>
-      <c r="AH18" s="27">
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="27" t="n"/>
+      <c r="H18" s="27" t="n"/>
+      <c r="I18" s="27" t="n"/>
+      <c r="J18" s="27" t="n"/>
+      <c r="K18" s="27" t="n"/>
+      <c r="L18" s="27" t="n"/>
+      <c r="M18" s="27" t="n"/>
+      <c r="N18" s="27" t="n"/>
+      <c r="O18" s="27" t="n"/>
+      <c r="P18" s="27" t="n"/>
+      <c r="Q18" s="27" t="n"/>
+      <c r="R18" s="27" t="n"/>
+      <c r="S18" s="27" t="n"/>
+      <c r="T18" s="27" t="n"/>
+      <c r="U18" s="27" t="n"/>
+      <c r="V18" s="27" t="n"/>
+      <c r="W18" s="27" t="n"/>
+      <c r="X18" s="27" t="n"/>
+      <c r="Y18" s="27" t="n"/>
+      <c r="Z18" s="27" t="n"/>
+      <c r="AA18" s="27" t="n"/>
+      <c r="AB18" s="27" t="n"/>
+      <c r="AC18" s="27" t="n"/>
+      <c r="AD18" s="27" t="n"/>
+      <c r="AE18" s="27" t="n"/>
+      <c r="AF18" s="27" t="n"/>
+      <c r="AG18" s="27" t="n"/>
+      <c r="AH18" s="28">
         <f>COUNTIF(C18:AG18,"A")</f>
         <v/>
       </c>
-      <c r="AI18" s="27">
+      <c r="AI18" s="28">
         <f>COUNTIF(C18:AG18,"F")</f>
         <v/>
       </c>
-      <c r="AJ18" s="27">
+      <c r="AJ18" s="28">
         <f>COUNTIF(C18:AG18,"R")</f>
         <v/>
       </c>
-      <c r="AK18" s="27">
+      <c r="AK18" s="28">
         <f>COUNTIF(C18:AG18,"V")</f>
         <v/>
       </c>
-      <c r="AL18" s="27">
+      <c r="AL18" s="28">
         <f>COUNTIF(C18:AG18,"I")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="26" t="n">
         <v>13</v>
       </c>
       <c r="B19" s="9" t="n"/>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="26" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="26" t="n"/>
-      <c r="G19" s="26" t="n"/>
-      <c r="H19" s="26" t="n"/>
-      <c r="I19" s="26" t="n"/>
-      <c r="J19" s="26" t="n"/>
-      <c r="K19" s="26" t="n"/>
-      <c r="L19" s="26" t="n"/>
-      <c r="M19" s="26" t="n"/>
-      <c r="N19" s="26" t="n"/>
-      <c r="O19" s="26" t="n"/>
-      <c r="P19" s="26" t="n"/>
-      <c r="Q19" s="26" t="n"/>
-      <c r="R19" s="26" t="n"/>
-      <c r="S19" s="26" t="n"/>
-      <c r="T19" s="26" t="n"/>
-      <c r="U19" s="26" t="n"/>
-      <c r="V19" s="26" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
-      <c r="Y19" s="26" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="26" t="n"/>
-      <c r="AB19" s="26" t="n"/>
-      <c r="AC19" s="26" t="n"/>
-      <c r="AD19" s="26" t="n"/>
-      <c r="AE19" s="26" t="n"/>
-      <c r="AF19" s="26" t="n"/>
-      <c r="AG19" s="26" t="n"/>
-      <c r="AH19" s="27">
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="27" t="n"/>
+      <c r="H19" s="27" t="n"/>
+      <c r="I19" s="27" t="n"/>
+      <c r="J19" s="27" t="n"/>
+      <c r="K19" s="27" t="n"/>
+      <c r="L19" s="27" t="n"/>
+      <c r="M19" s="27" t="n"/>
+      <c r="N19" s="27" t="n"/>
+      <c r="O19" s="27" t="n"/>
+      <c r="P19" s="27" t="n"/>
+      <c r="Q19" s="27" t="n"/>
+      <c r="R19" s="27" t="n"/>
+      <c r="S19" s="27" t="n"/>
+      <c r="T19" s="27" t="n"/>
+      <c r="U19" s="27" t="n"/>
+      <c r="V19" s="27" t="n"/>
+      <c r="W19" s="27" t="n"/>
+      <c r="X19" s="27" t="n"/>
+      <c r="Y19" s="27" t="n"/>
+      <c r="Z19" s="27" t="n"/>
+      <c r="AA19" s="27" t="n"/>
+      <c r="AB19" s="27" t="n"/>
+      <c r="AC19" s="27" t="n"/>
+      <c r="AD19" s="27" t="n"/>
+      <c r="AE19" s="27" t="n"/>
+      <c r="AF19" s="27" t="n"/>
+      <c r="AG19" s="27" t="n"/>
+      <c r="AH19" s="28">
         <f>COUNTIF(C19:AG19,"A")</f>
         <v/>
       </c>
-      <c r="AI19" s="27">
+      <c r="AI19" s="28">
         <f>COUNTIF(C19:AG19,"F")</f>
         <v/>
       </c>
-      <c r="AJ19" s="27">
+      <c r="AJ19" s="28">
         <f>COUNTIF(C19:AG19,"R")</f>
         <v/>
       </c>
-      <c r="AK19" s="27">
+      <c r="AK19" s="28">
         <f>COUNTIF(C19:AG19,"V")</f>
         <v/>
       </c>
-      <c r="AL19" s="27">
+      <c r="AL19" s="28">
         <f>COUNTIF(C19:AG19,"I")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="26" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="9" t="n"/>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="26" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="26" t="n"/>
-      <c r="I20" s="26" t="n"/>
-      <c r="J20" s="26" t="n"/>
-      <c r="K20" s="26" t="n"/>
-      <c r="L20" s="26" t="n"/>
-      <c r="M20" s="26" t="n"/>
-      <c r="N20" s="26" t="n"/>
-      <c r="O20" s="26" t="n"/>
-      <c r="P20" s="26" t="n"/>
-      <c r="Q20" s="26" t="n"/>
-      <c r="R20" s="26" t="n"/>
-      <c r="S20" s="26" t="n"/>
-      <c r="T20" s="26" t="n"/>
-      <c r="U20" s="26" t="n"/>
-      <c r="V20" s="26" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
-      <c r="Y20" s="26" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="26" t="n"/>
-      <c r="AB20" s="26" t="n"/>
-      <c r="AC20" s="26" t="n"/>
-      <c r="AD20" s="26" t="n"/>
-      <c r="AE20" s="26" t="n"/>
-      <c r="AF20" s="26" t="n"/>
-      <c r="AG20" s="26" t="n"/>
-      <c r="AH20" s="27">
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="27" t="n"/>
+      <c r="I20" s="27" t="n"/>
+      <c r="J20" s="27" t="n"/>
+      <c r="K20" s="27" t="n"/>
+      <c r="L20" s="27" t="n"/>
+      <c r="M20" s="27" t="n"/>
+      <c r="N20" s="27" t="n"/>
+      <c r="O20" s="27" t="n"/>
+      <c r="P20" s="27" t="n"/>
+      <c r="Q20" s="27" t="n"/>
+      <c r="R20" s="27" t="n"/>
+      <c r="S20" s="27" t="n"/>
+      <c r="T20" s="27" t="n"/>
+      <c r="U20" s="27" t="n"/>
+      <c r="V20" s="27" t="n"/>
+      <c r="W20" s="27" t="n"/>
+      <c r="X20" s="27" t="n"/>
+      <c r="Y20" s="27" t="n"/>
+      <c r="Z20" s="27" t="n"/>
+      <c r="AA20" s="27" t="n"/>
+      <c r="AB20" s="27" t="n"/>
+      <c r="AC20" s="27" t="n"/>
+      <c r="AD20" s="27" t="n"/>
+      <c r="AE20" s="27" t="n"/>
+      <c r="AF20" s="27" t="n"/>
+      <c r="AG20" s="27" t="n"/>
+      <c r="AH20" s="28">
         <f>COUNTIF(C20:AG20,"A")</f>
         <v/>
       </c>
-      <c r="AI20" s="27">
+      <c r="AI20" s="28">
         <f>COUNTIF(C20:AG20,"F")</f>
         <v/>
       </c>
-      <c r="AJ20" s="27">
+      <c r="AJ20" s="28">
         <f>COUNTIF(C20:AG20,"R")</f>
         <v/>
       </c>
-      <c r="AK20" s="27">
+      <c r="AK20" s="28">
         <f>COUNTIF(C20:AG20,"V")</f>
         <v/>
       </c>
-      <c r="AL20" s="27">
+      <c r="AL20" s="28">
         <f>COUNTIF(C20:AG20,"I")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="26" t="n">
         <v>15</v>
       </c>
       <c r="B21" s="9" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="26" t="n"/>
-      <c r="G21" s="26" t="n"/>
-      <c r="H21" s="26" t="n"/>
-      <c r="I21" s="26" t="n"/>
-      <c r="J21" s="26" t="n"/>
-      <c r="K21" s="26" t="n"/>
-      <c r="L21" s="26" t="n"/>
-      <c r="M21" s="26" t="n"/>
-      <c r="N21" s="26" t="n"/>
-      <c r="O21" s="26" t="n"/>
-      <c r="P21" s="26" t="n"/>
-      <c r="Q21" s="26" t="n"/>
-      <c r="R21" s="26" t="n"/>
-      <c r="S21" s="26" t="n"/>
-      <c r="T21" s="26" t="n"/>
-      <c r="U21" s="26" t="n"/>
-      <c r="V21" s="26" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
-      <c r="Y21" s="26" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="26" t="n"/>
-      <c r="AB21" s="26" t="n"/>
-      <c r="AC21" s="26" t="n"/>
-      <c r="AD21" s="26" t="n"/>
-      <c r="AE21" s="26" t="n"/>
-      <c r="AF21" s="26" t="n"/>
-      <c r="AG21" s="26" t="n"/>
-      <c r="AH21" s="27">
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="27" t="n"/>
+      <c r="H21" s="27" t="n"/>
+      <c r="I21" s="27" t="n"/>
+      <c r="J21" s="27" t="n"/>
+      <c r="K21" s="27" t="n"/>
+      <c r="L21" s="27" t="n"/>
+      <c r="M21" s="27" t="n"/>
+      <c r="N21" s="27" t="n"/>
+      <c r="O21" s="27" t="n"/>
+      <c r="P21" s="27" t="n"/>
+      <c r="Q21" s="27" t="n"/>
+      <c r="R21" s="27" t="n"/>
+      <c r="S21" s="27" t="n"/>
+      <c r="T21" s="27" t="n"/>
+      <c r="U21" s="27" t="n"/>
+      <c r="V21" s="27" t="n"/>
+      <c r="W21" s="27" t="n"/>
+      <c r="X21" s="27" t="n"/>
+      <c r="Y21" s="27" t="n"/>
+      <c r="Z21" s="27" t="n"/>
+      <c r="AA21" s="27" t="n"/>
+      <c r="AB21" s="27" t="n"/>
+      <c r="AC21" s="27" t="n"/>
+      <c r="AD21" s="27" t="n"/>
+      <c r="AE21" s="27" t="n"/>
+      <c r="AF21" s="27" t="n"/>
+      <c r="AG21" s="27" t="n"/>
+      <c r="AH21" s="28">
         <f>COUNTIF(C21:AG21,"A")</f>
         <v/>
       </c>
-      <c r="AI21" s="27">
+      <c r="AI21" s="28">
         <f>COUNTIF(C21:AG21,"F")</f>
         <v/>
       </c>
-      <c r="AJ21" s="27">
+      <c r="AJ21" s="28">
         <f>COUNTIF(C21:AG21,"R")</f>
         <v/>
       </c>
-      <c r="AK21" s="27">
+      <c r="AK21" s="28">
         <f>COUNTIF(C21:AG21,"V")</f>
         <v/>
       </c>
-      <c r="AL21" s="27">
+      <c r="AL21" s="28">
         <f>COUNTIF(C21:AG21,"I")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="26" t="n">
         <v>16</v>
       </c>
       <c r="B22" s="9" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="26" t="n"/>
-      <c r="G22" s="26" t="n"/>
-      <c r="H22" s="26" t="n"/>
-      <c r="I22" s="26" t="n"/>
-      <c r="J22" s="26" t="n"/>
-      <c r="K22" s="26" t="n"/>
-      <c r="L22" s="26" t="n"/>
-      <c r="M22" s="26" t="n"/>
-      <c r="N22" s="26" t="n"/>
-      <c r="O22" s="26" t="n"/>
-      <c r="P22" s="26" t="n"/>
-      <c r="Q22" s="26" t="n"/>
-      <c r="R22" s="26" t="n"/>
-      <c r="S22" s="26" t="n"/>
-      <c r="T22" s="26" t="n"/>
-      <c r="U22" s="26" t="n"/>
-      <c r="V22" s="26" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
-      <c r="Y22" s="26" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="26" t="n"/>
-      <c r="AB22" s="26" t="n"/>
-      <c r="AC22" s="26" t="n"/>
-      <c r="AD22" s="26" t="n"/>
-      <c r="AE22" s="26" t="n"/>
-      <c r="AF22" s="26" t="n"/>
-      <c r="AG22" s="26" t="n"/>
-      <c r="AH22" s="27">
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="27" t="n"/>
+      <c r="H22" s="27" t="n"/>
+      <c r="I22" s="27" t="n"/>
+      <c r="J22" s="27" t="n"/>
+      <c r="K22" s="27" t="n"/>
+      <c r="L22" s="27" t="n"/>
+      <c r="M22" s="27" t="n"/>
+      <c r="N22" s="27" t="n"/>
+      <c r="O22" s="27" t="n"/>
+      <c r="P22" s="27" t="n"/>
+      <c r="Q22" s="27" t="n"/>
+      <c r="R22" s="27" t="n"/>
+      <c r="S22" s="27" t="n"/>
+      <c r="T22" s="27" t="n"/>
+      <c r="U22" s="27" t="n"/>
+      <c r="V22" s="27" t="n"/>
+      <c r="W22" s="27" t="n"/>
+      <c r="X22" s="27" t="n"/>
+      <c r="Y22" s="27" t="n"/>
+      <c r="Z22" s="27" t="n"/>
+      <c r="AA22" s="27" t="n"/>
+      <c r="AB22" s="27" t="n"/>
+      <c r="AC22" s="27" t="n"/>
+      <c r="AD22" s="27" t="n"/>
+      <c r="AE22" s="27" t="n"/>
+      <c r="AF22" s="27" t="n"/>
+      <c r="AG22" s="27" t="n"/>
+      <c r="AH22" s="28">
         <f>COUNTIF(C22:AG22,"A")</f>
         <v/>
       </c>
-      <c r="AI22" s="27">
+      <c r="AI22" s="28">
         <f>COUNTIF(C22:AG22,"F")</f>
         <v/>
       </c>
-      <c r="AJ22" s="27">
+      <c r="AJ22" s="28">
         <f>COUNTIF(C22:AG22,"R")</f>
         <v/>
       </c>
-      <c r="AK22" s="27">
+      <c r="AK22" s="28">
         <f>COUNTIF(C22:AG22,"V")</f>
         <v/>
       </c>
-      <c r="AL22" s="27">
+      <c r="AL22" s="28">
         <f>COUNTIF(C22:AG22,"I")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="26" t="n">
         <v>17</v>
       </c>
       <c r="B23" s="9" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="26" t="n"/>
-      <c r="G23" s="26" t="n"/>
-      <c r="H23" s="26" t="n"/>
-      <c r="I23" s="26" t="n"/>
-      <c r="J23" s="26" t="n"/>
-      <c r="K23" s="26" t="n"/>
-      <c r="L23" s="26" t="n"/>
-      <c r="M23" s="26" t="n"/>
-      <c r="N23" s="26" t="n"/>
-      <c r="O23" s="26" t="n"/>
-      <c r="P23" s="26" t="n"/>
-      <c r="Q23" s="26" t="n"/>
-      <c r="R23" s="26" t="n"/>
-      <c r="S23" s="26" t="n"/>
-      <c r="T23" s="26" t="n"/>
-      <c r="U23" s="26" t="n"/>
-      <c r="V23" s="26" t="n"/>
-      <c r="W23" s="26" t="n"/>
-      <c r="X23" s="26" t="n"/>
-      <c r="Y23" s="26" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="26" t="n"/>
-      <c r="AB23" s="26" t="n"/>
-      <c r="AC23" s="26" t="n"/>
-      <c r="AD23" s="26" t="n"/>
-      <c r="AE23" s="26" t="n"/>
-      <c r="AF23" s="26" t="n"/>
-      <c r="AG23" s="26" t="n"/>
-      <c r="AH23" s="27">
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="27" t="n"/>
+      <c r="H23" s="27" t="n"/>
+      <c r="I23" s="27" t="n"/>
+      <c r="J23" s="27" t="n"/>
+      <c r="K23" s="27" t="n"/>
+      <c r="L23" s="27" t="n"/>
+      <c r="M23" s="27" t="n"/>
+      <c r="N23" s="27" t="n"/>
+      <c r="O23" s="27" t="n"/>
+      <c r="P23" s="27" t="n"/>
+      <c r="Q23" s="27" t="n"/>
+      <c r="R23" s="27" t="n"/>
+      <c r="S23" s="27" t="n"/>
+      <c r="T23" s="27" t="n"/>
+      <c r="U23" s="27" t="n"/>
+      <c r="V23" s="27" t="n"/>
+      <c r="W23" s="27" t="n"/>
+      <c r="X23" s="27" t="n"/>
+      <c r="Y23" s="27" t="n"/>
+      <c r="Z23" s="27" t="n"/>
+      <c r="AA23" s="27" t="n"/>
+      <c r="AB23" s="27" t="n"/>
+      <c r="AC23" s="27" t="n"/>
+      <c r="AD23" s="27" t="n"/>
+      <c r="AE23" s="27" t="n"/>
+      <c r="AF23" s="27" t="n"/>
+      <c r="AG23" s="27" t="n"/>
+      <c r="AH23" s="28">
         <f>COUNTIF(C23:AG23,"A")</f>
         <v/>
       </c>
-      <c r="AI23" s="27">
+      <c r="AI23" s="28">
         <f>COUNTIF(C23:AG23,"F")</f>
         <v/>
       </c>
-      <c r="AJ23" s="27">
+      <c r="AJ23" s="28">
         <f>COUNTIF(C23:AG23,"R")</f>
         <v/>
       </c>
-      <c r="AK23" s="27">
+      <c r="AK23" s="28">
         <f>COUNTIF(C23:AG23,"V")</f>
         <v/>
       </c>
-      <c r="AL23" s="27">
+      <c r="AL23" s="28">
         <f>COUNTIF(C23:AG23,"I")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="26" t="n">
         <v>18</v>
       </c>
       <c r="B24" s="9" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
-      <c r="H24" s="26" t="n"/>
-      <c r="I24" s="26" t="n"/>
-      <c r="J24" s="26" t="n"/>
-      <c r="K24" s="26" t="n"/>
-      <c r="L24" s="26" t="n"/>
-      <c r="M24" s="26" t="n"/>
-      <c r="N24" s="26" t="n"/>
-      <c r="O24" s="26" t="n"/>
-      <c r="P24" s="26" t="n"/>
-      <c r="Q24" s="26" t="n"/>
-      <c r="R24" s="26" t="n"/>
-      <c r="S24" s="26" t="n"/>
-      <c r="T24" s="26" t="n"/>
-      <c r="U24" s="26" t="n"/>
-      <c r="V24" s="26" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
-      <c r="Y24" s="26" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="26" t="n"/>
-      <c r="AB24" s="26" t="n"/>
-      <c r="AC24" s="26" t="n"/>
-      <c r="AD24" s="26" t="n"/>
-      <c r="AE24" s="26" t="n"/>
-      <c r="AF24" s="26" t="n"/>
-      <c r="AG24" s="26" t="n"/>
-      <c r="AH24" s="27">
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="27" t="n"/>
+      <c r="H24" s="27" t="n"/>
+      <c r="I24" s="27" t="n"/>
+      <c r="J24" s="27" t="n"/>
+      <c r="K24" s="27" t="n"/>
+      <c r="L24" s="27" t="n"/>
+      <c r="M24" s="27" t="n"/>
+      <c r="N24" s="27" t="n"/>
+      <c r="O24" s="27" t="n"/>
+      <c r="P24" s="27" t="n"/>
+      <c r="Q24" s="27" t="n"/>
+      <c r="R24" s="27" t="n"/>
+      <c r="S24" s="27" t="n"/>
+      <c r="T24" s="27" t="n"/>
+      <c r="U24" s="27" t="n"/>
+      <c r="V24" s="27" t="n"/>
+      <c r="W24" s="27" t="n"/>
+      <c r="X24" s="27" t="n"/>
+      <c r="Y24" s="27" t="n"/>
+      <c r="Z24" s="27" t="n"/>
+      <c r="AA24" s="27" t="n"/>
+      <c r="AB24" s="27" t="n"/>
+      <c r="AC24" s="27" t="n"/>
+      <c r="AD24" s="27" t="n"/>
+      <c r="AE24" s="27" t="n"/>
+      <c r="AF24" s="27" t="n"/>
+      <c r="AG24" s="27" t="n"/>
+      <c r="AH24" s="28">
         <f>COUNTIF(C24:AG24,"A")</f>
         <v/>
       </c>
-      <c r="AI24" s="27">
+      <c r="AI24" s="28">
         <f>COUNTIF(C24:AG24,"F")</f>
         <v/>
       </c>
-      <c r="AJ24" s="27">
+      <c r="AJ24" s="28">
         <f>COUNTIF(C24:AG24,"R")</f>
         <v/>
       </c>
-      <c r="AK24" s="27">
+      <c r="AK24" s="28">
         <f>COUNTIF(C24:AG24,"V")</f>
         <v/>
       </c>
-      <c r="AL24" s="27">
+      <c r="AL24" s="28">
         <f>COUNTIF(C24:AG24,"I")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="26" t="n">
         <v>19</v>
       </c>
       <c r="B25" s="9" t="n"/>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="26" t="n"/>
-      <c r="G25" s="26" t="n"/>
-      <c r="H25" s="26" t="n"/>
-      <c r="I25" s="26" t="n"/>
-      <c r="J25" s="26" t="n"/>
-      <c r="K25" s="26" t="n"/>
-      <c r="L25" s="26" t="n"/>
-      <c r="M25" s="26" t="n"/>
-      <c r="N25" s="26" t="n"/>
-      <c r="O25" s="26" t="n"/>
-      <c r="P25" s="26" t="n"/>
-      <c r="Q25" s="26" t="n"/>
-      <c r="R25" s="26" t="n"/>
-      <c r="S25" s="26" t="n"/>
-      <c r="T25" s="26" t="n"/>
-      <c r="U25" s="26" t="n"/>
-      <c r="V25" s="26" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
-      <c r="Y25" s="26" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="26" t="n"/>
-      <c r="AB25" s="26" t="n"/>
-      <c r="AC25" s="26" t="n"/>
-      <c r="AD25" s="26" t="n"/>
-      <c r="AE25" s="26" t="n"/>
-      <c r="AF25" s="26" t="n"/>
-      <c r="AG25" s="26" t="n"/>
-      <c r="AH25" s="27">
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="27" t="n"/>
+      <c r="I25" s="27" t="n"/>
+      <c r="J25" s="27" t="n"/>
+      <c r="K25" s="27" t="n"/>
+      <c r="L25" s="27" t="n"/>
+      <c r="M25" s="27" t="n"/>
+      <c r="N25" s="27" t="n"/>
+      <c r="O25" s="27" t="n"/>
+      <c r="P25" s="27" t="n"/>
+      <c r="Q25" s="27" t="n"/>
+      <c r="R25" s="27" t="n"/>
+      <c r="S25" s="27" t="n"/>
+      <c r="T25" s="27" t="n"/>
+      <c r="U25" s="27" t="n"/>
+      <c r="V25" s="27" t="n"/>
+      <c r="W25" s="27" t="n"/>
+      <c r="X25" s="27" t="n"/>
+      <c r="Y25" s="27" t="n"/>
+      <c r="Z25" s="27" t="n"/>
+      <c r="AA25" s="27" t="n"/>
+      <c r="AB25" s="27" t="n"/>
+      <c r="AC25" s="27" t="n"/>
+      <c r="AD25" s="27" t="n"/>
+      <c r="AE25" s="27" t="n"/>
+      <c r="AF25" s="27" t="n"/>
+      <c r="AG25" s="27" t="n"/>
+      <c r="AH25" s="28">
         <f>COUNTIF(C25:AG25,"A")</f>
         <v/>
       </c>
-      <c r="AI25" s="27">
+      <c r="AI25" s="28">
         <f>COUNTIF(C25:AG25,"F")</f>
         <v/>
       </c>
-      <c r="AJ25" s="27">
+      <c r="AJ25" s="28">
         <f>COUNTIF(C25:AG25,"R")</f>
         <v/>
       </c>
-      <c r="AK25" s="27">
+      <c r="AK25" s="28">
         <f>COUNTIF(C25:AG25,"V")</f>
         <v/>
       </c>
-      <c r="AL25" s="27">
+      <c r="AL25" s="28">
         <f>COUNTIF(C25:AG25,"I")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="26" t="n">
         <v>20</v>
       </c>
       <c r="B26" s="9" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="26" t="n"/>
-      <c r="G26" s="26" t="n"/>
-      <c r="H26" s="26" t="n"/>
-      <c r="I26" s="26" t="n"/>
-      <c r="J26" s="26" t="n"/>
-      <c r="K26" s="26" t="n"/>
-      <c r="L26" s="26" t="n"/>
-      <c r="M26" s="26" t="n"/>
-      <c r="N26" s="26" t="n"/>
-      <c r="O26" s="26" t="n"/>
-      <c r="P26" s="26" t="n"/>
-      <c r="Q26" s="26" t="n"/>
-      <c r="R26" s="26" t="n"/>
-      <c r="S26" s="26" t="n"/>
-      <c r="T26" s="26" t="n"/>
-      <c r="U26" s="26" t="n"/>
-      <c r="V26" s="26" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
-      <c r="Y26" s="26" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="26" t="n"/>
-      <c r="AB26" s="26" t="n"/>
-      <c r="AC26" s="26" t="n"/>
-      <c r="AD26" s="26" t="n"/>
-      <c r="AE26" s="26" t="n"/>
-      <c r="AF26" s="26" t="n"/>
-      <c r="AG26" s="26" t="n"/>
-      <c r="AH26" s="27">
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
+      <c r="H26" s="27" t="n"/>
+      <c r="I26" s="27" t="n"/>
+      <c r="J26" s="27" t="n"/>
+      <c r="K26" s="27" t="n"/>
+      <c r="L26" s="27" t="n"/>
+      <c r="M26" s="27" t="n"/>
+      <c r="N26" s="27" t="n"/>
+      <c r="O26" s="27" t="n"/>
+      <c r="P26" s="27" t="n"/>
+      <c r="Q26" s="27" t="n"/>
+      <c r="R26" s="27" t="n"/>
+      <c r="S26" s="27" t="n"/>
+      <c r="T26" s="27" t="n"/>
+      <c r="U26" s="27" t="n"/>
+      <c r="V26" s="27" t="n"/>
+      <c r="W26" s="27" t="n"/>
+      <c r="X26" s="27" t="n"/>
+      <c r="Y26" s="27" t="n"/>
+      <c r="Z26" s="27" t="n"/>
+      <c r="AA26" s="27" t="n"/>
+      <c r="AB26" s="27" t="n"/>
+      <c r="AC26" s="27" t="n"/>
+      <c r="AD26" s="27" t="n"/>
+      <c r="AE26" s="27" t="n"/>
+      <c r="AF26" s="27" t="n"/>
+      <c r="AG26" s="27" t="n"/>
+      <c r="AH26" s="28">
         <f>COUNTIF(C26:AG26,"A")</f>
         <v/>
       </c>
-      <c r="AI26" s="27">
+      <c r="AI26" s="28">
         <f>COUNTIF(C26:AG26,"F")</f>
         <v/>
       </c>
-      <c r="AJ26" s="27">
+      <c r="AJ26" s="28">
         <f>COUNTIF(C26:AG26,"R")</f>
         <v/>
       </c>
-      <c r="AK26" s="27">
+      <c r="AK26" s="28">
         <f>COUNTIF(C26:AG26,"V")</f>
         <v/>
       </c>
-      <c r="AL26" s="27">
+      <c r="AL26" s="28">
         <f>COUNTIF(C26:AG26,"I")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="26" t="n">
         <v>21</v>
       </c>
       <c r="B27" s="9" t="n"/>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="26" t="n"/>
-      <c r="G27" s="26" t="n"/>
-      <c r="H27" s="26" t="n"/>
-      <c r="I27" s="26" t="n"/>
-      <c r="J27" s="26" t="n"/>
-      <c r="K27" s="26" t="n"/>
-      <c r="L27" s="26" t="n"/>
-      <c r="M27" s="26" t="n"/>
-      <c r="N27" s="26" t="n"/>
-      <c r="O27" s="26" t="n"/>
-      <c r="P27" s="26" t="n"/>
-      <c r="Q27" s="26" t="n"/>
-      <c r="R27" s="26" t="n"/>
-      <c r="S27" s="26" t="n"/>
-      <c r="T27" s="26" t="n"/>
-      <c r="U27" s="26" t="n"/>
-      <c r="V27" s="26" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="26" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="26" t="n"/>
-      <c r="AB27" s="26" t="n"/>
-      <c r="AC27" s="26" t="n"/>
-      <c r="AD27" s="26" t="n"/>
-      <c r="AE27" s="26" t="n"/>
-      <c r="AF27" s="26" t="n"/>
-      <c r="AG27" s="26" t="n"/>
-      <c r="AH27" s="27">
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="27" t="n"/>
+      <c r="H27" s="27" t="n"/>
+      <c r="I27" s="27" t="n"/>
+      <c r="J27" s="27" t="n"/>
+      <c r="K27" s="27" t="n"/>
+      <c r="L27" s="27" t="n"/>
+      <c r="M27" s="27" t="n"/>
+      <c r="N27" s="27" t="n"/>
+      <c r="O27" s="27" t="n"/>
+      <c r="P27" s="27" t="n"/>
+      <c r="Q27" s="27" t="n"/>
+      <c r="R27" s="27" t="n"/>
+      <c r="S27" s="27" t="n"/>
+      <c r="T27" s="27" t="n"/>
+      <c r="U27" s="27" t="n"/>
+      <c r="V27" s="27" t="n"/>
+      <c r="W27" s="27" t="n"/>
+      <c r="X27" s="27" t="n"/>
+      <c r="Y27" s="27" t="n"/>
+      <c r="Z27" s="27" t="n"/>
+      <c r="AA27" s="27" t="n"/>
+      <c r="AB27" s="27" t="n"/>
+      <c r="AC27" s="27" t="n"/>
+      <c r="AD27" s="27" t="n"/>
+      <c r="AE27" s="27" t="n"/>
+      <c r="AF27" s="27" t="n"/>
+      <c r="AG27" s="27" t="n"/>
+      <c r="AH27" s="28">
         <f>COUNTIF(C27:AG27,"A")</f>
         <v/>
       </c>
-      <c r="AI27" s="27">
+      <c r="AI27" s="28">
         <f>COUNTIF(C27:AG27,"F")</f>
         <v/>
       </c>
-      <c r="AJ27" s="27">
+      <c r="AJ27" s="28">
         <f>COUNTIF(C27:AG27,"R")</f>
         <v/>
       </c>
-      <c r="AK27" s="27">
+      <c r="AK27" s="28">
         <f>COUNTIF(C27:AG27,"V")</f>
         <v/>
       </c>
-      <c r="AL27" s="27">
+      <c r="AL27" s="28">
         <f>COUNTIF(C27:AG27,"I")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="26" t="n">
         <v>22</v>
       </c>
       <c r="B28" s="9" t="n"/>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="26" t="n"/>
-      <c r="G28" s="26" t="n"/>
-      <c r="H28" s="26" t="n"/>
-      <c r="I28" s="26" t="n"/>
-      <c r="J28" s="26" t="n"/>
-      <c r="K28" s="26" t="n"/>
-      <c r="L28" s="26" t="n"/>
-      <c r="M28" s="26" t="n"/>
-      <c r="N28" s="26" t="n"/>
-      <c r="O28" s="26" t="n"/>
-      <c r="P28" s="26" t="n"/>
-      <c r="Q28" s="26" t="n"/>
-      <c r="R28" s="26" t="n"/>
-      <c r="S28" s="26" t="n"/>
-      <c r="T28" s="26" t="n"/>
-      <c r="U28" s="26" t="n"/>
-      <c r="V28" s="26" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
-      <c r="Y28" s="26" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="26" t="n"/>
-      <c r="AB28" s="26" t="n"/>
-      <c r="AC28" s="26" t="n"/>
-      <c r="AD28" s="26" t="n"/>
-      <c r="AE28" s="26" t="n"/>
-      <c r="AF28" s="26" t="n"/>
-      <c r="AG28" s="26" t="n"/>
-      <c r="AH28" s="27">
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
+      <c r="H28" s="27" t="n"/>
+      <c r="I28" s="27" t="n"/>
+      <c r="J28" s="27" t="n"/>
+      <c r="K28" s="27" t="n"/>
+      <c r="L28" s="27" t="n"/>
+      <c r="M28" s="27" t="n"/>
+      <c r="N28" s="27" t="n"/>
+      <c r="O28" s="27" t="n"/>
+      <c r="P28" s="27" t="n"/>
+      <c r="Q28" s="27" t="n"/>
+      <c r="R28" s="27" t="n"/>
+      <c r="S28" s="27" t="n"/>
+      <c r="T28" s="27" t="n"/>
+      <c r="U28" s="27" t="n"/>
+      <c r="V28" s="27" t="n"/>
+      <c r="W28" s="27" t="n"/>
+      <c r="X28" s="27" t="n"/>
+      <c r="Y28" s="27" t="n"/>
+      <c r="Z28" s="27" t="n"/>
+      <c r="AA28" s="27" t="n"/>
+      <c r="AB28" s="27" t="n"/>
+      <c r="AC28" s="27" t="n"/>
+      <c r="AD28" s="27" t="n"/>
+      <c r="AE28" s="27" t="n"/>
+      <c r="AF28" s="27" t="n"/>
+      <c r="AG28" s="27" t="n"/>
+      <c r="AH28" s="28">
         <f>COUNTIF(C28:AG28,"A")</f>
         <v/>
       </c>
-      <c r="AI28" s="27">
+      <c r="AI28" s="28">
         <f>COUNTIF(C28:AG28,"F")</f>
         <v/>
       </c>
-      <c r="AJ28" s="27">
+      <c r="AJ28" s="28">
         <f>COUNTIF(C28:AG28,"R")</f>
         <v/>
       </c>
-      <c r="AK28" s="27">
+      <c r="AK28" s="28">
         <f>COUNTIF(C28:AG28,"V")</f>
         <v/>
       </c>
-      <c r="AL28" s="27">
+      <c r="AL28" s="28">
         <f>COUNTIF(C28:AG28,"I")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="26" t="n">
         <v>23</v>
       </c>
       <c r="B29" s="9" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-      <c r="G29" s="26" t="n"/>
-      <c r="H29" s="26" t="n"/>
-      <c r="I29" s="26" t="n"/>
-      <c r="J29" s="26" t="n"/>
-      <c r="K29" s="26" t="n"/>
-      <c r="L29" s="26" t="n"/>
-      <c r="M29" s="26" t="n"/>
-      <c r="N29" s="26" t="n"/>
-      <c r="O29" s="26" t="n"/>
-      <c r="P29" s="26" t="n"/>
-      <c r="Q29" s="26" t="n"/>
-      <c r="R29" s="26" t="n"/>
-      <c r="S29" s="26" t="n"/>
-      <c r="T29" s="26" t="n"/>
-      <c r="U29" s="26" t="n"/>
-      <c r="V29" s="26" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
-      <c r="Y29" s="26" t="n"/>
-      <c r="Z29" s="26" t="n"/>
-      <c r="AA29" s="26" t="n"/>
-      <c r="AB29" s="26" t="n"/>
-      <c r="AC29" s="26" t="n"/>
-      <c r="AD29" s="26" t="n"/>
-      <c r="AE29" s="26" t="n"/>
-      <c r="AF29" s="26" t="n"/>
-      <c r="AG29" s="26" t="n"/>
-      <c r="AH29" s="27">
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="27" t="n"/>
+      <c r="H29" s="27" t="n"/>
+      <c r="I29" s="27" t="n"/>
+      <c r="J29" s="27" t="n"/>
+      <c r="K29" s="27" t="n"/>
+      <c r="L29" s="27" t="n"/>
+      <c r="M29" s="27" t="n"/>
+      <c r="N29" s="27" t="n"/>
+      <c r="O29" s="27" t="n"/>
+      <c r="P29" s="27" t="n"/>
+      <c r="Q29" s="27" t="n"/>
+      <c r="R29" s="27" t="n"/>
+      <c r="S29" s="27" t="n"/>
+      <c r="T29" s="27" t="n"/>
+      <c r="U29" s="27" t="n"/>
+      <c r="V29" s="27" t="n"/>
+      <c r="W29" s="27" t="n"/>
+      <c r="X29" s="27" t="n"/>
+      <c r="Y29" s="27" t="n"/>
+      <c r="Z29" s="27" t="n"/>
+      <c r="AA29" s="27" t="n"/>
+      <c r="AB29" s="27" t="n"/>
+      <c r="AC29" s="27" t="n"/>
+      <c r="AD29" s="27" t="n"/>
+      <c r="AE29" s="27" t="n"/>
+      <c r="AF29" s="27" t="n"/>
+      <c r="AG29" s="27" t="n"/>
+      <c r="AH29" s="28">
         <f>COUNTIF(C29:AG29,"A")</f>
         <v/>
       </c>
-      <c r="AI29" s="27">
+      <c r="AI29" s="28">
         <f>COUNTIF(C29:AG29,"F")</f>
         <v/>
       </c>
-      <c r="AJ29" s="27">
+      <c r="AJ29" s="28">
         <f>COUNTIF(C29:AG29,"R")</f>
         <v/>
       </c>
-      <c r="AK29" s="27">
+      <c r="AK29" s="28">
         <f>COUNTIF(C29:AG29,"V")</f>
         <v/>
       </c>
-      <c r="AL29" s="27">
+      <c r="AL29" s="28">
         <f>COUNTIF(C29:AG29,"I")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="26" t="n">
         <v>24</v>
       </c>
       <c r="B30" s="9" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
-      <c r="G30" s="26" t="n"/>
-      <c r="H30" s="26" t="n"/>
-      <c r="I30" s="26" t="n"/>
-      <c r="J30" s="26" t="n"/>
-      <c r="K30" s="26" t="n"/>
-      <c r="L30" s="26" t="n"/>
-      <c r="M30" s="26" t="n"/>
-      <c r="N30" s="26" t="n"/>
-      <c r="O30" s="26" t="n"/>
-      <c r="P30" s="26" t="n"/>
-      <c r="Q30" s="26" t="n"/>
-      <c r="R30" s="26" t="n"/>
-      <c r="S30" s="26" t="n"/>
-      <c r="T30" s="26" t="n"/>
-      <c r="U30" s="26" t="n"/>
-      <c r="V30" s="26" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
-      <c r="Y30" s="26" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="26" t="n"/>
-      <c r="AB30" s="26" t="n"/>
-      <c r="AC30" s="26" t="n"/>
-      <c r="AD30" s="26" t="n"/>
-      <c r="AE30" s="26" t="n"/>
-      <c r="AF30" s="26" t="n"/>
-      <c r="AG30" s="26" t="n"/>
-      <c r="AH30" s="27">
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="n"/>
+      <c r="H30" s="27" t="n"/>
+      <c r="I30" s="27" t="n"/>
+      <c r="J30" s="27" t="n"/>
+      <c r="K30" s="27" t="n"/>
+      <c r="L30" s="27" t="n"/>
+      <c r="M30" s="27" t="n"/>
+      <c r="N30" s="27" t="n"/>
+      <c r="O30" s="27" t="n"/>
+      <c r="P30" s="27" t="n"/>
+      <c r="Q30" s="27" t="n"/>
+      <c r="R30" s="27" t="n"/>
+      <c r="S30" s="27" t="n"/>
+      <c r="T30" s="27" t="n"/>
+      <c r="U30" s="27" t="n"/>
+      <c r="V30" s="27" t="n"/>
+      <c r="W30" s="27" t="n"/>
+      <c r="X30" s="27" t="n"/>
+      <c r="Y30" s="27" t="n"/>
+      <c r="Z30" s="27" t="n"/>
+      <c r="AA30" s="27" t="n"/>
+      <c r="AB30" s="27" t="n"/>
+      <c r="AC30" s="27" t="n"/>
+      <c r="AD30" s="27" t="n"/>
+      <c r="AE30" s="27" t="n"/>
+      <c r="AF30" s="27" t="n"/>
+      <c r="AG30" s="27" t="n"/>
+      <c r="AH30" s="28">
         <f>COUNTIF(C30:AG30,"A")</f>
         <v/>
       </c>
-      <c r="AI30" s="27">
+      <c r="AI30" s="28">
         <f>COUNTIF(C30:AG30,"F")</f>
         <v/>
       </c>
-      <c r="AJ30" s="27">
+      <c r="AJ30" s="28">
         <f>COUNTIF(C30:AG30,"R")</f>
         <v/>
       </c>
-      <c r="AK30" s="27">
+      <c r="AK30" s="28">
         <f>COUNTIF(C30:AG30,"V")</f>
         <v/>
       </c>
-      <c r="AL30" s="27">
+      <c r="AL30" s="28">
         <f>COUNTIF(C30:AG30,"I")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="26" t="n">
         <v>25</v>
       </c>
       <c r="B31" s="9" t="n"/>
-      <c r="C31" s="26" t="n"/>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="26" t="n"/>
-      <c r="G31" s="26" t="n"/>
-      <c r="H31" s="26" t="n"/>
-      <c r="I31" s="26" t="n"/>
-      <c r="J31" s="26" t="n"/>
-      <c r="K31" s="26" t="n"/>
-      <c r="L31" s="26" t="n"/>
-      <c r="M31" s="26" t="n"/>
-      <c r="N31" s="26" t="n"/>
-      <c r="O31" s="26" t="n"/>
-      <c r="P31" s="26" t="n"/>
-      <c r="Q31" s="26" t="n"/>
-      <c r="R31" s="26" t="n"/>
-      <c r="S31" s="26" t="n"/>
-      <c r="T31" s="26" t="n"/>
-      <c r="U31" s="26" t="n"/>
-      <c r="V31" s="26" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
-      <c r="Y31" s="26" t="n"/>
-      <c r="Z31" s="26" t="n"/>
-      <c r="AA31" s="26" t="n"/>
-      <c r="AB31" s="26" t="n"/>
-      <c r="AC31" s="26" t="n"/>
-      <c r="AD31" s="26" t="n"/>
-      <c r="AE31" s="26" t="n"/>
-      <c r="AF31" s="26" t="n"/>
-      <c r="AG31" s="26" t="n"/>
-      <c r="AH31" s="27">
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="27" t="n"/>
+      <c r="E31" s="27" t="n"/>
+      <c r="F31" s="27" t="n"/>
+      <c r="G31" s="27" t="n"/>
+      <c r="H31" s="27" t="n"/>
+      <c r="I31" s="27" t="n"/>
+      <c r="J31" s="27" t="n"/>
+      <c r="K31" s="27" t="n"/>
+      <c r="L31" s="27" t="n"/>
+      <c r="M31" s="27" t="n"/>
+      <c r="N31" s="27" t="n"/>
+      <c r="O31" s="27" t="n"/>
+      <c r="P31" s="27" t="n"/>
+      <c r="Q31" s="27" t="n"/>
+      <c r="R31" s="27" t="n"/>
+      <c r="S31" s="27" t="n"/>
+      <c r="T31" s="27" t="n"/>
+      <c r="U31" s="27" t="n"/>
+      <c r="V31" s="27" t="n"/>
+      <c r="W31" s="27" t="n"/>
+      <c r="X31" s="27" t="n"/>
+      <c r="Y31" s="27" t="n"/>
+      <c r="Z31" s="27" t="n"/>
+      <c r="AA31" s="27" t="n"/>
+      <c r="AB31" s="27" t="n"/>
+      <c r="AC31" s="27" t="n"/>
+      <c r="AD31" s="27" t="n"/>
+      <c r="AE31" s="27" t="n"/>
+      <c r="AF31" s="27" t="n"/>
+      <c r="AG31" s="27" t="n"/>
+      <c r="AH31" s="28">
         <f>COUNTIF(C31:AG31,"A")</f>
         <v/>
       </c>
-      <c r="AI31" s="27">
+      <c r="AI31" s="28">
         <f>COUNTIF(C31:AG31,"F")</f>
         <v/>
       </c>
-      <c r="AJ31" s="27">
+      <c r="AJ31" s="28">
         <f>COUNTIF(C31:AG31,"R")</f>
         <v/>
       </c>
-      <c r="AK31" s="27">
+      <c r="AK31" s="28">
         <f>COUNTIF(C31:AG31,"V")</f>
         <v/>
       </c>
-      <c r="AL31" s="27">
+      <c r="AL31" s="28">
         <f>COUNTIF(C31:AG31,"I")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="26" t="n">
         <v>26</v>
       </c>
       <c r="B32" s="9" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
-      <c r="H32" s="26" t="n"/>
-      <c r="I32" s="26" t="n"/>
-      <c r="J32" s="26" t="n"/>
-      <c r="K32" s="26" t="n"/>
-      <c r="L32" s="26" t="n"/>
-      <c r="M32" s="26" t="n"/>
-      <c r="N32" s="26" t="n"/>
-      <c r="O32" s="26" t="n"/>
-      <c r="P32" s="26" t="n"/>
-      <c r="Q32" s="26" t="n"/>
-      <c r="R32" s="26" t="n"/>
-      <c r="S32" s="26" t="n"/>
-      <c r="T32" s="26" t="n"/>
-      <c r="U32" s="26" t="n"/>
-      <c r="V32" s="26" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="26" t="n"/>
-      <c r="Z32" s="26" t="n"/>
-      <c r="AA32" s="26" t="n"/>
-      <c r="AB32" s="26" t="n"/>
-      <c r="AC32" s="26" t="n"/>
-      <c r="AD32" s="26" t="n"/>
-      <c r="AE32" s="26" t="n"/>
-      <c r="AF32" s="26" t="n"/>
-      <c r="AG32" s="26" t="n"/>
-      <c r="AH32" s="27">
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="27" t="n"/>
+      <c r="H32" s="27" t="n"/>
+      <c r="I32" s="27" t="n"/>
+      <c r="J32" s="27" t="n"/>
+      <c r="K32" s="27" t="n"/>
+      <c r="L32" s="27" t="n"/>
+      <c r="M32" s="27" t="n"/>
+      <c r="N32" s="27" t="n"/>
+      <c r="O32" s="27" t="n"/>
+      <c r="P32" s="27" t="n"/>
+      <c r="Q32" s="27" t="n"/>
+      <c r="R32" s="27" t="n"/>
+      <c r="S32" s="27" t="n"/>
+      <c r="T32" s="27" t="n"/>
+      <c r="U32" s="27" t="n"/>
+      <c r="V32" s="27" t="n"/>
+      <c r="W32" s="27" t="n"/>
+      <c r="X32" s="27" t="n"/>
+      <c r="Y32" s="27" t="n"/>
+      <c r="Z32" s="27" t="n"/>
+      <c r="AA32" s="27" t="n"/>
+      <c r="AB32" s="27" t="n"/>
+      <c r="AC32" s="27" t="n"/>
+      <c r="AD32" s="27" t="n"/>
+      <c r="AE32" s="27" t="n"/>
+      <c r="AF32" s="27" t="n"/>
+      <c r="AG32" s="27" t="n"/>
+      <c r="AH32" s="28">
         <f>COUNTIF(C32:AG32,"A")</f>
         <v/>
       </c>
-      <c r="AI32" s="27">
+      <c r="AI32" s="28">
         <f>COUNTIF(C32:AG32,"F")</f>
         <v/>
       </c>
-      <c r="AJ32" s="27">
+      <c r="AJ32" s="28">
         <f>COUNTIF(C32:AG32,"R")</f>
         <v/>
       </c>
-      <c r="AK32" s="27">
+      <c r="AK32" s="28">
         <f>COUNTIF(C32:AG32,"V")</f>
         <v/>
       </c>
-      <c r="AL32" s="27">
+      <c r="AL32" s="28">
         <f>COUNTIF(C32:AG32,"I")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="26" t="n">
         <v>27</v>
       </c>
       <c r="B33" s="9" t="n"/>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="26" t="n"/>
-      <c r="G33" s="26" t="n"/>
-      <c r="H33" s="26" t="n"/>
-      <c r="I33" s="26" t="n"/>
-      <c r="J33" s="26" t="n"/>
-      <c r="K33" s="26" t="n"/>
-      <c r="L33" s="26" t="n"/>
-      <c r="M33" s="26" t="n"/>
-      <c r="N33" s="26" t="n"/>
-      <c r="O33" s="26" t="n"/>
-      <c r="P33" s="26" t="n"/>
-      <c r="Q33" s="26" t="n"/>
-      <c r="R33" s="26" t="n"/>
-      <c r="S33" s="26" t="n"/>
-      <c r="T33" s="26" t="n"/>
-      <c r="U33" s="26" t="n"/>
-      <c r="V33" s="26" t="n"/>
-      <c r="W33" s="26" t="n"/>
-      <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="26" t="n"/>
-      <c r="Z33" s="26" t="n"/>
-      <c r="AA33" s="26" t="n"/>
-      <c r="AB33" s="26" t="n"/>
-      <c r="AC33" s="26" t="n"/>
-      <c r="AD33" s="26" t="n"/>
-      <c r="AE33" s="26" t="n"/>
-      <c r="AF33" s="26" t="n"/>
-      <c r="AG33" s="26" t="n"/>
-      <c r="AH33" s="27">
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="27" t="n"/>
+      <c r="H33" s="27" t="n"/>
+      <c r="I33" s="27" t="n"/>
+      <c r="J33" s="27" t="n"/>
+      <c r="K33" s="27" t="n"/>
+      <c r="L33" s="27" t="n"/>
+      <c r="M33" s="27" t="n"/>
+      <c r="N33" s="27" t="n"/>
+      <c r="O33" s="27" t="n"/>
+      <c r="P33" s="27" t="n"/>
+      <c r="Q33" s="27" t="n"/>
+      <c r="R33" s="27" t="n"/>
+      <c r="S33" s="27" t="n"/>
+      <c r="T33" s="27" t="n"/>
+      <c r="U33" s="27" t="n"/>
+      <c r="V33" s="27" t="n"/>
+      <c r="W33" s="27" t="n"/>
+      <c r="X33" s="27" t="n"/>
+      <c r="Y33" s="27" t="n"/>
+      <c r="Z33" s="27" t="n"/>
+      <c r="AA33" s="27" t="n"/>
+      <c r="AB33" s="27" t="n"/>
+      <c r="AC33" s="27" t="n"/>
+      <c r="AD33" s="27" t="n"/>
+      <c r="AE33" s="27" t="n"/>
+      <c r="AF33" s="27" t="n"/>
+      <c r="AG33" s="27" t="n"/>
+      <c r="AH33" s="28">
         <f>COUNTIF(C33:AG33,"A")</f>
         <v/>
       </c>
-      <c r="AI33" s="27">
+      <c r="AI33" s="28">
         <f>COUNTIF(C33:AG33,"F")</f>
         <v/>
       </c>
-      <c r="AJ33" s="27">
+      <c r="AJ33" s="28">
         <f>COUNTIF(C33:AG33,"R")</f>
         <v/>
       </c>
-      <c r="AK33" s="27">
+      <c r="AK33" s="28">
         <f>COUNTIF(C33:AG33,"V")</f>
         <v/>
       </c>
-      <c r="AL33" s="27">
+      <c r="AL33" s="28">
         <f>COUNTIF(C33:AG33,"I")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="26" t="n">
         <v>28</v>
       </c>
       <c r="B34" s="9" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="26" t="n"/>
-      <c r="G34" s="26" t="n"/>
-      <c r="H34" s="26" t="n"/>
-      <c r="I34" s="26" t="n"/>
-      <c r="J34" s="26" t="n"/>
-      <c r="K34" s="26" t="n"/>
-      <c r="L34" s="26" t="n"/>
-      <c r="M34" s="26" t="n"/>
-      <c r="N34" s="26" t="n"/>
-      <c r="O34" s="26" t="n"/>
-      <c r="P34" s="26" t="n"/>
-      <c r="Q34" s="26" t="n"/>
-      <c r="R34" s="26" t="n"/>
-      <c r="S34" s="26" t="n"/>
-      <c r="T34" s="26" t="n"/>
-      <c r="U34" s="26" t="n"/>
-      <c r="V34" s="26" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="26" t="n"/>
-      <c r="Z34" s="26" t="n"/>
-      <c r="AA34" s="26" t="n"/>
-      <c r="AB34" s="26" t="n"/>
-      <c r="AC34" s="26" t="n"/>
-      <c r="AD34" s="26" t="n"/>
-      <c r="AE34" s="26" t="n"/>
-      <c r="AF34" s="26" t="n"/>
-      <c r="AG34" s="26" t="n"/>
-      <c r="AH34" s="27">
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="27" t="n"/>
+      <c r="H34" s="27" t="n"/>
+      <c r="I34" s="27" t="n"/>
+      <c r="J34" s="27" t="n"/>
+      <c r="K34" s="27" t="n"/>
+      <c r="L34" s="27" t="n"/>
+      <c r="M34" s="27" t="n"/>
+      <c r="N34" s="27" t="n"/>
+      <c r="O34" s="27" t="n"/>
+      <c r="P34" s="27" t="n"/>
+      <c r="Q34" s="27" t="n"/>
+      <c r="R34" s="27" t="n"/>
+      <c r="S34" s="27" t="n"/>
+      <c r="T34" s="27" t="n"/>
+      <c r="U34" s="27" t="n"/>
+      <c r="V34" s="27" t="n"/>
+      <c r="W34" s="27" t="n"/>
+      <c r="X34" s="27" t="n"/>
+      <c r="Y34" s="27" t="n"/>
+      <c r="Z34" s="27" t="n"/>
+      <c r="AA34" s="27" t="n"/>
+      <c r="AB34" s="27" t="n"/>
+      <c r="AC34" s="27" t="n"/>
+      <c r="AD34" s="27" t="n"/>
+      <c r="AE34" s="27" t="n"/>
+      <c r="AF34" s="27" t="n"/>
+      <c r="AG34" s="27" t="n"/>
+      <c r="AH34" s="28">
         <f>COUNTIF(C34:AG34,"A")</f>
         <v/>
       </c>
-      <c r="AI34" s="27">
+      <c r="AI34" s="28">
         <f>COUNTIF(C34:AG34,"F")</f>
         <v/>
       </c>
-      <c r="AJ34" s="27">
+      <c r="AJ34" s="28">
         <f>COUNTIF(C34:AG34,"R")</f>
         <v/>
       </c>
-      <c r="AK34" s="27">
+      <c r="AK34" s="28">
         <f>COUNTIF(C34:AG34,"V")</f>
         <v/>
       </c>
-      <c r="AL34" s="27">
+      <c r="AL34" s="28">
         <f>COUNTIF(C34:AG34,"I")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="26" t="n">
         <v>29</v>
       </c>
       <c r="B35" s="9" t="n"/>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="26" t="n"/>
-      <c r="G35" s="26" t="n"/>
-      <c r="H35" s="26" t="n"/>
-      <c r="I35" s="26" t="n"/>
-      <c r="J35" s="26" t="n"/>
-      <c r="K35" s="26" t="n"/>
-      <c r="L35" s="26" t="n"/>
-      <c r="M35" s="26" t="n"/>
-      <c r="N35" s="26" t="n"/>
-      <c r="O35" s="26" t="n"/>
-      <c r="P35" s="26" t="n"/>
-      <c r="Q35" s="26" t="n"/>
-      <c r="R35" s="26" t="n"/>
-      <c r="S35" s="26" t="n"/>
-      <c r="T35" s="26" t="n"/>
-      <c r="U35" s="26" t="n"/>
-      <c r="V35" s="26" t="n"/>
-      <c r="W35" s="26" t="n"/>
-      <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="26" t="n"/>
-      <c r="Z35" s="26" t="n"/>
-      <c r="AA35" s="26" t="n"/>
-      <c r="AB35" s="26" t="n"/>
-      <c r="AC35" s="26" t="n"/>
-      <c r="AD35" s="26" t="n"/>
-      <c r="AE35" s="26" t="n"/>
-      <c r="AF35" s="26" t="n"/>
-      <c r="AG35" s="26" t="n"/>
-      <c r="AH35" s="27">
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="27" t="n"/>
+      <c r="F35" s="27" t="n"/>
+      <c r="G35" s="27" t="n"/>
+      <c r="H35" s="27" t="n"/>
+      <c r="I35" s="27" t="n"/>
+      <c r="J35" s="27" t="n"/>
+      <c r="K35" s="27" t="n"/>
+      <c r="L35" s="27" t="n"/>
+      <c r="M35" s="27" t="n"/>
+      <c r="N35" s="27" t="n"/>
+      <c r="O35" s="27" t="n"/>
+      <c r="P35" s="27" t="n"/>
+      <c r="Q35" s="27" t="n"/>
+      <c r="R35" s="27" t="n"/>
+      <c r="S35" s="27" t="n"/>
+      <c r="T35" s="27" t="n"/>
+      <c r="U35" s="27" t="n"/>
+      <c r="V35" s="27" t="n"/>
+      <c r="W35" s="27" t="n"/>
+      <c r="X35" s="27" t="n"/>
+      <c r="Y35" s="27" t="n"/>
+      <c r="Z35" s="27" t="n"/>
+      <c r="AA35" s="27" t="n"/>
+      <c r="AB35" s="27" t="n"/>
+      <c r="AC35" s="27" t="n"/>
+      <c r="AD35" s="27" t="n"/>
+      <c r="AE35" s="27" t="n"/>
+      <c r="AF35" s="27" t="n"/>
+      <c r="AG35" s="27" t="n"/>
+      <c r="AH35" s="28">
         <f>COUNTIF(C35:AG35,"A")</f>
         <v/>
       </c>
-      <c r="AI35" s="27">
+      <c r="AI35" s="28">
         <f>COUNTIF(C35:AG35,"F")</f>
         <v/>
       </c>
-      <c r="AJ35" s="27">
+      <c r="AJ35" s="28">
         <f>COUNTIF(C35:AG35,"R")</f>
         <v/>
       </c>
-      <c r="AK35" s="27">
+      <c r="AK35" s="28">
         <f>COUNTIF(C35:AG35,"V")</f>
         <v/>
       </c>
-      <c r="AL35" s="27">
+      <c r="AL35" s="28">
         <f>COUNTIF(C35:AG35,"I")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="26" t="n">
         <v>30</v>
       </c>
       <c r="B36" s="9" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="26" t="n"/>
-      <c r="G36" s="26" t="n"/>
-      <c r="H36" s="26" t="n"/>
-      <c r="I36" s="26" t="n"/>
-      <c r="J36" s="26" t="n"/>
-      <c r="K36" s="26" t="n"/>
-      <c r="L36" s="26" t="n"/>
-      <c r="M36" s="26" t="n"/>
-      <c r="N36" s="26" t="n"/>
-      <c r="O36" s="26" t="n"/>
-      <c r="P36" s="26" t="n"/>
-      <c r="Q36" s="26" t="n"/>
-      <c r="R36" s="26" t="n"/>
-      <c r="S36" s="26" t="n"/>
-      <c r="T36" s="26" t="n"/>
-      <c r="U36" s="26" t="n"/>
-      <c r="V36" s="26" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="26" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="26" t="n"/>
-      <c r="AB36" s="26" t="n"/>
-      <c r="AC36" s="26" t="n"/>
-      <c r="AD36" s="26" t="n"/>
-      <c r="AE36" s="26" t="n"/>
-      <c r="AF36" s="26" t="n"/>
-      <c r="AG36" s="26" t="n"/>
-      <c r="AH36" s="27">
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="27" t="n"/>
+      <c r="I36" s="27" t="n"/>
+      <c r="J36" s="27" t="n"/>
+      <c r="K36" s="27" t="n"/>
+      <c r="L36" s="27" t="n"/>
+      <c r="M36" s="27" t="n"/>
+      <c r="N36" s="27" t="n"/>
+      <c r="O36" s="27" t="n"/>
+      <c r="P36" s="27" t="n"/>
+      <c r="Q36" s="27" t="n"/>
+      <c r="R36" s="27" t="n"/>
+      <c r="S36" s="27" t="n"/>
+      <c r="T36" s="27" t="n"/>
+      <c r="U36" s="27" t="n"/>
+      <c r="V36" s="27" t="n"/>
+      <c r="W36" s="27" t="n"/>
+      <c r="X36" s="27" t="n"/>
+      <c r="Y36" s="27" t="n"/>
+      <c r="Z36" s="27" t="n"/>
+      <c r="AA36" s="27" t="n"/>
+      <c r="AB36" s="27" t="n"/>
+      <c r="AC36" s="27" t="n"/>
+      <c r="AD36" s="27" t="n"/>
+      <c r="AE36" s="27" t="n"/>
+      <c r="AF36" s="27" t="n"/>
+      <c r="AG36" s="27" t="n"/>
+      <c r="AH36" s="28">
         <f>COUNTIF(C36:AG36,"A")</f>
         <v/>
       </c>
-      <c r="AI36" s="27">
+      <c r="AI36" s="28">
         <f>COUNTIF(C36:AG36,"F")</f>
         <v/>
       </c>
-      <c r="AJ36" s="27">
+      <c r="AJ36" s="28">
         <f>COUNTIF(C36:AG36,"R")</f>
         <v/>
       </c>
-      <c r="AK36" s="27">
+      <c r="AK36" s="28">
         <f>COUNTIF(C36:AG36,"V")</f>
         <v/>
       </c>
-      <c r="AL36" s="27">
+      <c r="AL36" s="28">
         <f>COUNTIF(C36:AG36,"I")</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="5">
     <mergeCell ref="C4:J4"/>
     <mergeCell ref="A2:AI2"/>

--- a/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
+++ b/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
@@ -52,7 +52,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -62,7 +62,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -104,7 +104,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -127,7 +127,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -155,7 +155,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -5560,7 +5560,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
+++ b/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
@@ -979,7 +979,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1461,7 +1461,7 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="C38" s="4" t="n"/>

--- a/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
+++ b/plantillas/2_Recursos_Humanos/01_Control_de_Asistencia.xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMATO'!$6:$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="0;;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,144 +34,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
-      <sz val="18"/>
+      <sz val="24"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="30"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E7C8B"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
-      <color rgb="002B2B2B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -192,6 +201,16 @@
       </patternFill>
     </fill>
     <fill>
+      <gradientFill type="linear" degree="90">
+        <stop position="0">
+          <color rgb="0017426B"/>
+        </stop>
+        <stop position="1">
+          <color rgb="000B2A4A"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
@@ -202,7 +221,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -284,6 +303,20 @@
       <left style="thin">
         <color rgb="00C9D3DB"/>
       </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
       <top style="medium">
         <color rgb="00C9A227"/>
       </top>
@@ -333,6 +366,11 @@
     </border>
     <border>
       <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
         <color rgb="00C9D3DB"/>
       </bottom>
     </border>
@@ -340,24 +378,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -368,19 +406,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -389,54 +435,60 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="7" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -519,6 +571,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -549,11 +602,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0B2A4A"/>
+              <a:srgbClr val="2A6FBA"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="0B2A4A"/>
+                <a:srgbClr val="2A6FBA"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -579,11 +632,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C9A227"/>
+              <a:srgbClr val="E69F00"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="C9A227"/>
+                <a:srgbClr val="E69F00"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -599,7 +652,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -622,6 +675,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8ED"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -634,6 +697,12 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -954,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1213,7 +1282,7 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>CÓMO USARLO</t>
+          <t>FICHA TÉCNICA</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -1224,77 +1293,87 @@
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Escribe el mes y los nombres de tus empleados (hasta 50).</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Capacidad</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>50 empleados x 31 días</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Cada día selecciona la clave en la lista: A, F, R, V, I, D o P.</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Compatibilidad</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac)</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Las columnas finales suman automáticamente asistencias, faltas, retardos, vacaciones e incapacidades.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Idioma y moneda</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Español (México) · Pesos mexicanos (MXN) · IVA 16%</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
       <c r="G23" s="4" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Imprime en horizontal; cabe en una sola hoja.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Protección</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Hojas protegidas sin contraseña (Revisar &gt; Desproteger hoja)</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Arial (disponible en Windows, Mac y Google Sheets)</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
       <c r="G25" s="4" t="n"/>
     </row>
     <row r="26">
@@ -1310,7 +1389,7 @@
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>RECOMENDACIONES DE USO</t>
+          <t>CÓMO USARLO</t>
         </is>
       </c>
       <c r="C27" s="10" t="n"/>
@@ -1321,14 +1400,12 @@
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B28" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Llena el control a diario; los registros hechos al final del mes pierden precisión.</t>
+          <t>Escribe el mes y los nombres de tus empleados (hasta 50).</t>
         </is>
       </c>
       <c r="D28" s="4" t="n"/>
@@ -1338,14 +1415,12 @@
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B29" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Usa las claves A, F, R, V, I, D y P de forma uniforme para que los conteos sean correctos.</t>
+          <t>Cada día selecciona la clave en la lista: A, F, R, V, I, D o P.</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
@@ -1355,14 +1430,12 @@
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B30" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Tres retardos pueden equivaler a una falta según tu reglamento interior; defínelo por escrito.</t>
+          <t>Las columnas finales suman automáticamente asistencias, faltas, retardos, vacaciones e incapacidades.</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -1372,14 +1445,12 @@
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B31" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Conserva los controles firmados por al menos 2 años.</t>
+          <t>Imprime en horizontal; cabe en una sola hoja.</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
@@ -1387,47 +1458,53 @@
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
+      <c r="B32" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
     </row>
-    <row r="33" ht="24" customHeight="1">
+    <row r="33">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="n"/>
-      <c r="B34" s="17" t="inlineStr"/>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>CELDA DE CAPTURA: escribe aquí.</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="21" customHeight="1">
       <c r="A35" s="4" t="n"/>
-      <c r="B35" s="19" t="inlineStr"/>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Llena el control a diario; los registros hechos al final del mes pierden precisión.</t>
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
@@ -1435,12 +1512,16 @@
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="21" customHeight="1">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>ENCABEZADOS Y TÍTULOS.</t>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Usa las claves A, F, R, V, I, D y P de forma uniforme para que los conteos sean correctos.</t>
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
@@ -1448,48 +1529,166 @@
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="21" customHeight="1">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Tres retardos pueden equivaler a una falta según tu reglamento interior; defínelo por escrito.</t>
+        </is>
+      </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Conserva los controles firmados por al menos 2 años.</t>
+        </is>
+      </c>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="1" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="22" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="23" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="24" t="inlineStr"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>* CAMPO OBLIGATORIO: complétalo antes de imprimir o enviar.</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="1" t="n"/>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="16">
-    <mergeCell ref="C22:F22"/>
+  <mergeCells count="21">
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B4:F5"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId3"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
@@ -1547,7 +1746,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>CONTROL DE ASISTENCIA MENSUAL</t>
         </is>
@@ -1586,58 +1785,58 @@
       <c r="AG1" s="1" t="n"/>
       <c r="AH1" s="1" t="n"/>
       <c r="AI1" s="1" t="n"/>
-      <c r="AJ1" s="23" t="inlineStr">
+      <c r="AJ1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="AK1" s="24" t="n"/>
-      <c r="AL1" s="25" t="n"/>
+      <c r="AK1" s="28" t="n"/>
+      <c r="AL1" s="29" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>A=Asistencia · F=Falta · R=Retardo · V=Vacaciones · I=Incapacidad · D=Descanso · P=Permiso</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n"/>
-      <c r="C2" s="27" t="n"/>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="27" t="n"/>
-      <c r="F2" s="27" t="n"/>
-      <c r="G2" s="27" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="I2" s="27" t="n"/>
-      <c r="J2" s="27" t="n"/>
-      <c r="K2" s="27" t="n"/>
-      <c r="L2" s="27" t="n"/>
-      <c r="M2" s="27" t="n"/>
-      <c r="N2" s="27" t="n"/>
-      <c r="O2" s="27" t="n"/>
-      <c r="P2" s="27" t="n"/>
-      <c r="Q2" s="27" t="n"/>
-      <c r="R2" s="27" t="n"/>
-      <c r="S2" s="27" t="n"/>
-      <c r="T2" s="27" t="n"/>
-      <c r="U2" s="27" t="n"/>
-      <c r="V2" s="27" t="n"/>
-      <c r="W2" s="27" t="n"/>
-      <c r="X2" s="27" t="n"/>
-      <c r="Y2" s="27" t="n"/>
-      <c r="Z2" s="27" t="n"/>
-      <c r="AA2" s="27" t="n"/>
-      <c r="AB2" s="27" t="n"/>
-      <c r="AC2" s="27" t="n"/>
-      <c r="AD2" s="27" t="n"/>
-      <c r="AE2" s="27" t="n"/>
-      <c r="AF2" s="27" t="n"/>
-      <c r="AG2" s="27" t="n"/>
-      <c r="AH2" s="27" t="n"/>
-      <c r="AI2" s="27" t="n"/>
-      <c r="AJ2" s="28" t="n"/>
-      <c r="AK2" s="29" t="n"/>
-      <c r="AL2" s="30" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="31" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="31" t="n"/>
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="n"/>
+      <c r="H2" s="31" t="n"/>
+      <c r="I2" s="31" t="n"/>
+      <c r="J2" s="31" t="n"/>
+      <c r="K2" s="31" t="n"/>
+      <c r="L2" s="31" t="n"/>
+      <c r="M2" s="31" t="n"/>
+      <c r="N2" s="31" t="n"/>
+      <c r="O2" s="31" t="n"/>
+      <c r="P2" s="31" t="n"/>
+      <c r="Q2" s="31" t="n"/>
+      <c r="R2" s="31" t="n"/>
+      <c r="S2" s="31" t="n"/>
+      <c r="T2" s="31" t="n"/>
+      <c r="U2" s="31" t="n"/>
+      <c r="V2" s="31" t="n"/>
+      <c r="W2" s="31" t="n"/>
+      <c r="X2" s="31" t="n"/>
+      <c r="Y2" s="31" t="n"/>
+      <c r="Z2" s="31" t="n"/>
+      <c r="AA2" s="31" t="n"/>
+      <c r="AB2" s="31" t="n"/>
+      <c r="AC2" s="31" t="n"/>
+      <c r="AD2" s="31" t="n"/>
+      <c r="AE2" s="31" t="n"/>
+      <c r="AF2" s="31" t="n"/>
+      <c r="AG2" s="31" t="n"/>
+      <c r="AH2" s="31" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="32" t="n"/>
+      <c r="AK2" s="33" t="n"/>
+      <c r="AL2" s="34" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1681,19 +1880,19 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="31" t="inlineStr">
-        <is>
-          <t>EMPRESA</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="17" t="n"/>
-      <c r="I4" s="17" t="n"/>
-      <c r="J4" s="17" t="n"/>
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>EMPRESA *</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="20" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
@@ -1725,19 +1924,19 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>MES/AÑO</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="20" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
@@ -1767,3044 +1966,3044 @@
       <c r="AK5" s="4" t="n"/>
       <c r="AL5" s="4" t="n"/>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>EMPLEADO</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K6" s="32" t="inlineStr">
+      <c r="K6" s="36" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L6" s="32" t="inlineStr">
+      <c r="L6" s="36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M6" s="32" t="inlineStr">
+      <c r="M6" s="36" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N6" s="32" t="inlineStr">
+      <c r="N6" s="36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O6" s="32" t="inlineStr">
+      <c r="O6" s="36" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P6" s="32" t="inlineStr">
+      <c r="P6" s="36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q6" s="32" t="inlineStr">
+      <c r="Q6" s="36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R6" s="32" t="inlineStr">
+      <c r="R6" s="36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S6" s="32" t="inlineStr">
+      <c r="S6" s="36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T6" s="32" t="inlineStr">
+      <c r="T6" s="36" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="U6" s="32" t="inlineStr">
+      <c r="U6" s="36" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="V6" s="32" t="inlineStr">
+      <c r="V6" s="36" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W6" s="32" t="inlineStr">
+      <c r="W6" s="36" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="X6" s="32" t="inlineStr">
+      <c r="X6" s="36" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Y6" s="32" t="inlineStr">
+      <c r="Y6" s="36" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Z6" s="32" t="inlineStr">
+      <c r="Z6" s="36" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="AA6" s="32" t="inlineStr">
+      <c r="AA6" s="36" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AB6" s="32" t="inlineStr">
+      <c r="AB6" s="36" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AC6" s="32" t="inlineStr">
+      <c r="AC6" s="36" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AD6" s="32" t="inlineStr">
+      <c r="AD6" s="36" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="AE6" s="32" t="inlineStr">
+      <c r="AE6" s="36" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="AF6" s="32" t="inlineStr">
+      <c r="AF6" s="36" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AG6" s="32" t="inlineStr">
+      <c r="AG6" s="36" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AH6" s="32" t="inlineStr">
+      <c r="AH6" s="36" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AI6" s="32" t="inlineStr">
+      <c r="AI6" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AJ6" s="32" t="inlineStr">
+      <c r="AJ6" s="36" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AK6" s="32" t="inlineStr">
+      <c r="AK6" s="36" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="AL6" s="32" t="inlineStr">
+      <c r="AL6" s="36" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="33" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="34" t="n"/>
-      <c r="F7" s="34" t="n"/>
-      <c r="G7" s="34" t="n"/>
-      <c r="H7" s="34" t="n"/>
-      <c r="I7" s="34" t="n"/>
-      <c r="J7" s="34" t="n"/>
-      <c r="K7" s="34" t="n"/>
-      <c r="L7" s="34" t="n"/>
-      <c r="M7" s="34" t="n"/>
-      <c r="N7" s="34" t="n"/>
-      <c r="O7" s="34" t="n"/>
-      <c r="P7" s="34" t="n"/>
-      <c r="Q7" s="34" t="n"/>
-      <c r="R7" s="34" t="n"/>
-      <c r="S7" s="34" t="n"/>
-      <c r="T7" s="34" t="n"/>
-      <c r="U7" s="34" t="n"/>
-      <c r="V7" s="34" t="n"/>
-      <c r="W7" s="34" t="n"/>
-      <c r="X7" s="34" t="n"/>
-      <c r="Y7" s="34" t="n"/>
-      <c r="Z7" s="34" t="n"/>
-      <c r="AA7" s="34" t="n"/>
-      <c r="AB7" s="34" t="n"/>
-      <c r="AC7" s="34" t="n"/>
-      <c r="AD7" s="34" t="n"/>
-      <c r="AE7" s="34" t="n"/>
-      <c r="AF7" s="34" t="n"/>
-      <c r="AG7" s="34" t="n"/>
-      <c r="AH7" s="35">
+      <c r="B7" s="38" t="n"/>
+      <c r="C7" s="39" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="39" t="n"/>
+      <c r="H7" s="39" t="n"/>
+      <c r="I7" s="39" t="n"/>
+      <c r="J7" s="39" t="n"/>
+      <c r="K7" s="39" t="n"/>
+      <c r="L7" s="39" t="n"/>
+      <c r="M7" s="39" t="n"/>
+      <c r="N7" s="39" t="n"/>
+      <c r="O7" s="39" t="n"/>
+      <c r="P7" s="39" t="n"/>
+      <c r="Q7" s="39" t="n"/>
+      <c r="R7" s="39" t="n"/>
+      <c r="S7" s="39" t="n"/>
+      <c r="T7" s="39" t="n"/>
+      <c r="U7" s="39" t="n"/>
+      <c r="V7" s="39" t="n"/>
+      <c r="W7" s="39" t="n"/>
+      <c r="X7" s="39" t="n"/>
+      <c r="Y7" s="39" t="n"/>
+      <c r="Z7" s="39" t="n"/>
+      <c r="AA7" s="39" t="n"/>
+      <c r="AB7" s="39" t="n"/>
+      <c r="AC7" s="39" t="n"/>
+      <c r="AD7" s="39" t="n"/>
+      <c r="AE7" s="39" t="n"/>
+      <c r="AF7" s="39" t="n"/>
+      <c r="AG7" s="39" t="n"/>
+      <c r="AH7" s="40">
         <f>COUNTIF(C7:AG7,"A")</f>
         <v/>
       </c>
-      <c r="AI7" s="35">
+      <c r="AI7" s="40">
         <f>COUNTIF(C7:AG7,"F")</f>
         <v/>
       </c>
-      <c r="AJ7" s="35">
+      <c r="AJ7" s="40">
         <f>COUNTIF(C7:AG7,"R")</f>
         <v/>
       </c>
-      <c r="AK7" s="35">
+      <c r="AK7" s="40">
         <f>COUNTIF(C7:AG7,"V")</f>
         <v/>
       </c>
-      <c r="AL7" s="35">
+      <c r="AL7" s="40">
         <f>COUNTIF(C7:AG7,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="33" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n"/>
-      <c r="F8" s="34" t="n"/>
-      <c r="G8" s="34" t="n"/>
-      <c r="H8" s="34" t="n"/>
-      <c r="I8" s="34" t="n"/>
-      <c r="J8" s="34" t="n"/>
-      <c r="K8" s="34" t="n"/>
-      <c r="L8" s="34" t="n"/>
-      <c r="M8" s="34" t="n"/>
-      <c r="N8" s="34" t="n"/>
-      <c r="O8" s="34" t="n"/>
-      <c r="P8" s="34" t="n"/>
-      <c r="Q8" s="34" t="n"/>
-      <c r="R8" s="34" t="n"/>
-      <c r="S8" s="34" t="n"/>
-      <c r="T8" s="34" t="n"/>
-      <c r="U8" s="34" t="n"/>
-      <c r="V8" s="34" t="n"/>
-      <c r="W8" s="34" t="n"/>
-      <c r="X8" s="34" t="n"/>
-      <c r="Y8" s="34" t="n"/>
-      <c r="Z8" s="34" t="n"/>
-      <c r="AA8" s="34" t="n"/>
-      <c r="AB8" s="34" t="n"/>
-      <c r="AC8" s="34" t="n"/>
-      <c r="AD8" s="34" t="n"/>
-      <c r="AE8" s="34" t="n"/>
-      <c r="AF8" s="34" t="n"/>
-      <c r="AG8" s="34" t="n"/>
-      <c r="AH8" s="35">
+      <c r="B8" s="38" t="n"/>
+      <c r="C8" s="39" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="39" t="n"/>
+      <c r="H8" s="39" t="n"/>
+      <c r="I8" s="39" t="n"/>
+      <c r="J8" s="39" t="n"/>
+      <c r="K8" s="39" t="n"/>
+      <c r="L8" s="39" t="n"/>
+      <c r="M8" s="39" t="n"/>
+      <c r="N8" s="39" t="n"/>
+      <c r="O8" s="39" t="n"/>
+      <c r="P8" s="39" t="n"/>
+      <c r="Q8" s="39" t="n"/>
+      <c r="R8" s="39" t="n"/>
+      <c r="S8" s="39" t="n"/>
+      <c r="T8" s="39" t="n"/>
+      <c r="U8" s="39" t="n"/>
+      <c r="V8" s="39" t="n"/>
+      <c r="W8" s="39" t="n"/>
+      <c r="X8" s="39" t="n"/>
+      <c r="Y8" s="39" t="n"/>
+      <c r="Z8" s="39" t="n"/>
+      <c r="AA8" s="39" t="n"/>
+      <c r="AB8" s="39" t="n"/>
+      <c r="AC8" s="39" t="n"/>
+      <c r="AD8" s="39" t="n"/>
+      <c r="AE8" s="39" t="n"/>
+      <c r="AF8" s="39" t="n"/>
+      <c r="AG8" s="39" t="n"/>
+      <c r="AH8" s="40">
         <f>COUNTIF(C8:AG8,"A")</f>
         <v/>
       </c>
-      <c r="AI8" s="35">
+      <c r="AI8" s="40">
         <f>COUNTIF(C8:AG8,"F")</f>
         <v/>
       </c>
-      <c r="AJ8" s="35">
+      <c r="AJ8" s="40">
         <f>COUNTIF(C8:AG8,"R")</f>
         <v/>
       </c>
-      <c r="AK8" s="35">
+      <c r="AK8" s="40">
         <f>COUNTIF(C8:AG8,"V")</f>
         <v/>
       </c>
-      <c r="AL8" s="35">
+      <c r="AL8" s="40">
         <f>COUNTIF(C8:AG8,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="33" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="34" t="n"/>
-      <c r="F9" s="34" t="n"/>
-      <c r="G9" s="34" t="n"/>
-      <c r="H9" s="34" t="n"/>
-      <c r="I9" s="34" t="n"/>
-      <c r="J9" s="34" t="n"/>
-      <c r="K9" s="34" t="n"/>
-      <c r="L9" s="34" t="n"/>
-      <c r="M9" s="34" t="n"/>
-      <c r="N9" s="34" t="n"/>
-      <c r="O9" s="34" t="n"/>
-      <c r="P9" s="34" t="n"/>
-      <c r="Q9" s="34" t="n"/>
-      <c r="R9" s="34" t="n"/>
-      <c r="S9" s="34" t="n"/>
-      <c r="T9" s="34" t="n"/>
-      <c r="U9" s="34" t="n"/>
-      <c r="V9" s="34" t="n"/>
-      <c r="W9" s="34" t="n"/>
-      <c r="X9" s="34" t="n"/>
-      <c r="Y9" s="34" t="n"/>
-      <c r="Z9" s="34" t="n"/>
-      <c r="AA9" s="34" t="n"/>
-      <c r="AB9" s="34" t="n"/>
-      <c r="AC9" s="34" t="n"/>
-      <c r="AD9" s="34" t="n"/>
-      <c r="AE9" s="34" t="n"/>
-      <c r="AF9" s="34" t="n"/>
-      <c r="AG9" s="34" t="n"/>
-      <c r="AH9" s="35">
+      <c r="B9" s="38" t="n"/>
+      <c r="C9" s="39" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="39" t="n"/>
+      <c r="H9" s="39" t="n"/>
+      <c r="I9" s="39" t="n"/>
+      <c r="J9" s="39" t="n"/>
+      <c r="K9" s="39" t="n"/>
+      <c r="L9" s="39" t="n"/>
+      <c r="M9" s="39" t="n"/>
+      <c r="N9" s="39" t="n"/>
+      <c r="O9" s="39" t="n"/>
+      <c r="P9" s="39" t="n"/>
+      <c r="Q9" s="39" t="n"/>
+      <c r="R9" s="39" t="n"/>
+      <c r="S9" s="39" t="n"/>
+      <c r="T9" s="39" t="n"/>
+      <c r="U9" s="39" t="n"/>
+      <c r="V9" s="39" t="n"/>
+      <c r="W9" s="39" t="n"/>
+      <c r="X9" s="39" t="n"/>
+      <c r="Y9" s="39" t="n"/>
+      <c r="Z9" s="39" t="n"/>
+      <c r="AA9" s="39" t="n"/>
+      <c r="AB9" s="39" t="n"/>
+      <c r="AC9" s="39" t="n"/>
+      <c r="AD9" s="39" t="n"/>
+      <c r="AE9" s="39" t="n"/>
+      <c r="AF9" s="39" t="n"/>
+      <c r="AG9" s="39" t="n"/>
+      <c r="AH9" s="40">
         <f>COUNTIF(C9:AG9,"A")</f>
         <v/>
       </c>
-      <c r="AI9" s="35">
+      <c r="AI9" s="40">
         <f>COUNTIF(C9:AG9,"F")</f>
         <v/>
       </c>
-      <c r="AJ9" s="35">
+      <c r="AJ9" s="40">
         <f>COUNTIF(C9:AG9,"R")</f>
         <v/>
       </c>
-      <c r="AK9" s="35">
+      <c r="AK9" s="40">
         <f>COUNTIF(C9:AG9,"V")</f>
         <v/>
       </c>
-      <c r="AL9" s="35">
+      <c r="AL9" s="40">
         <f>COUNTIF(C9:AG9,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="33" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="34" t="n"/>
-      <c r="G10" s="34" t="n"/>
-      <c r="H10" s="34" t="n"/>
-      <c r="I10" s="34" t="n"/>
-      <c r="J10" s="34" t="n"/>
-      <c r="K10" s="34" t="n"/>
-      <c r="L10" s="34" t="n"/>
-      <c r="M10" s="34" t="n"/>
-      <c r="N10" s="34" t="n"/>
-      <c r="O10" s="34" t="n"/>
-      <c r="P10" s="34" t="n"/>
-      <c r="Q10" s="34" t="n"/>
-      <c r="R10" s="34" t="n"/>
-      <c r="S10" s="34" t="n"/>
-      <c r="T10" s="34" t="n"/>
-      <c r="U10" s="34" t="n"/>
-      <c r="V10" s="34" t="n"/>
-      <c r="W10" s="34" t="n"/>
-      <c r="X10" s="34" t="n"/>
-      <c r="Y10" s="34" t="n"/>
-      <c r="Z10" s="34" t="n"/>
-      <c r="AA10" s="34" t="n"/>
-      <c r="AB10" s="34" t="n"/>
-      <c r="AC10" s="34" t="n"/>
-      <c r="AD10" s="34" t="n"/>
-      <c r="AE10" s="34" t="n"/>
-      <c r="AF10" s="34" t="n"/>
-      <c r="AG10" s="34" t="n"/>
-      <c r="AH10" s="35">
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="39" t="n"/>
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="39" t="n"/>
+      <c r="J10" s="39" t="n"/>
+      <c r="K10" s="39" t="n"/>
+      <c r="L10" s="39" t="n"/>
+      <c r="M10" s="39" t="n"/>
+      <c r="N10" s="39" t="n"/>
+      <c r="O10" s="39" t="n"/>
+      <c r="P10" s="39" t="n"/>
+      <c r="Q10" s="39" t="n"/>
+      <c r="R10" s="39" t="n"/>
+      <c r="S10" s="39" t="n"/>
+      <c r="T10" s="39" t="n"/>
+      <c r="U10" s="39" t="n"/>
+      <c r="V10" s="39" t="n"/>
+      <c r="W10" s="39" t="n"/>
+      <c r="X10" s="39" t="n"/>
+      <c r="Y10" s="39" t="n"/>
+      <c r="Z10" s="39" t="n"/>
+      <c r="AA10" s="39" t="n"/>
+      <c r="AB10" s="39" t="n"/>
+      <c r="AC10" s="39" t="n"/>
+      <c r="AD10" s="39" t="n"/>
+      <c r="AE10" s="39" t="n"/>
+      <c r="AF10" s="39" t="n"/>
+      <c r="AG10" s="39" t="n"/>
+      <c r="AH10" s="40">
         <f>COUNTIF(C10:AG10,"A")</f>
         <v/>
       </c>
-      <c r="AI10" s="35">
+      <c r="AI10" s="40">
         <f>COUNTIF(C10:AG10,"F")</f>
         <v/>
       </c>
-      <c r="AJ10" s="35">
+      <c r="AJ10" s="40">
         <f>COUNTIF(C10:AG10,"R")</f>
         <v/>
       </c>
-      <c r="AK10" s="35">
+      <c r="AK10" s="40">
         <f>COUNTIF(C10:AG10,"V")</f>
         <v/>
       </c>
-      <c r="AL10" s="35">
+      <c r="AL10" s="40">
         <f>COUNTIF(C10:AG10,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="33" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n"/>
-      <c r="F11" s="34" t="n"/>
-      <c r="G11" s="34" t="n"/>
-      <c r="H11" s="34" t="n"/>
-      <c r="I11" s="34" t="n"/>
-      <c r="J11" s="34" t="n"/>
-      <c r="K11" s="34" t="n"/>
-      <c r="L11" s="34" t="n"/>
-      <c r="M11" s="34" t="n"/>
-      <c r="N11" s="34" t="n"/>
-      <c r="O11" s="34" t="n"/>
-      <c r="P11" s="34" t="n"/>
-      <c r="Q11" s="34" t="n"/>
-      <c r="R11" s="34" t="n"/>
-      <c r="S11" s="34" t="n"/>
-      <c r="T11" s="34" t="n"/>
-      <c r="U11" s="34" t="n"/>
-      <c r="V11" s="34" t="n"/>
-      <c r="W11" s="34" t="n"/>
-      <c r="X11" s="34" t="n"/>
-      <c r="Y11" s="34" t="n"/>
-      <c r="Z11" s="34" t="n"/>
-      <c r="AA11" s="34" t="n"/>
-      <c r="AB11" s="34" t="n"/>
-      <c r="AC11" s="34" t="n"/>
-      <c r="AD11" s="34" t="n"/>
-      <c r="AE11" s="34" t="n"/>
-      <c r="AF11" s="34" t="n"/>
-      <c r="AG11" s="34" t="n"/>
-      <c r="AH11" s="35">
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="39" t="n"/>
+      <c r="H11" s="39" t="n"/>
+      <c r="I11" s="39" t="n"/>
+      <c r="J11" s="39" t="n"/>
+      <c r="K11" s="39" t="n"/>
+      <c r="L11" s="39" t="n"/>
+      <c r="M11" s="39" t="n"/>
+      <c r="N11" s="39" t="n"/>
+      <c r="O11" s="39" t="n"/>
+      <c r="P11" s="39" t="n"/>
+      <c r="Q11" s="39" t="n"/>
+      <c r="R11" s="39" t="n"/>
+      <c r="S11" s="39" t="n"/>
+      <c r="T11" s="39" t="n"/>
+      <c r="U11" s="39" t="n"/>
+      <c r="V11" s="39" t="n"/>
+      <c r="W11" s="39" t="n"/>
+      <c r="X11" s="39" t="n"/>
+      <c r="Y11" s="39" t="n"/>
+      <c r="Z11" s="39" t="n"/>
+      <c r="AA11" s="39" t="n"/>
+      <c r="AB11" s="39" t="n"/>
+      <c r="AC11" s="39" t="n"/>
+      <c r="AD11" s="39" t="n"/>
+      <c r="AE11" s="39" t="n"/>
+      <c r="AF11" s="39" t="n"/>
+      <c r="AG11" s="39" t="n"/>
+      <c r="AH11" s="40">
         <f>COUNTIF(C11:AG11,"A")</f>
         <v/>
       </c>
-      <c r="AI11" s="35">
+      <c r="AI11" s="40">
         <f>COUNTIF(C11:AG11,"F")</f>
         <v/>
       </c>
-      <c r="AJ11" s="35">
+      <c r="AJ11" s="40">
         <f>COUNTIF(C11:AG11,"R")</f>
         <v/>
       </c>
-      <c r="AK11" s="35">
+      <c r="AK11" s="40">
         <f>COUNTIF(C11:AG11,"V")</f>
         <v/>
       </c>
-      <c r="AL11" s="35">
+      <c r="AL11" s="40">
         <f>COUNTIF(C11:AG11,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="33" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="34" t="n"/>
-      <c r="F12" s="34" t="n"/>
-      <c r="G12" s="34" t="n"/>
-      <c r="H12" s="34" t="n"/>
-      <c r="I12" s="34" t="n"/>
-      <c r="J12" s="34" t="n"/>
-      <c r="K12" s="34" t="n"/>
-      <c r="L12" s="34" t="n"/>
-      <c r="M12" s="34" t="n"/>
-      <c r="N12" s="34" t="n"/>
-      <c r="O12" s="34" t="n"/>
-      <c r="P12" s="34" t="n"/>
-      <c r="Q12" s="34" t="n"/>
-      <c r="R12" s="34" t="n"/>
-      <c r="S12" s="34" t="n"/>
-      <c r="T12" s="34" t="n"/>
-      <c r="U12" s="34" t="n"/>
-      <c r="V12" s="34" t="n"/>
-      <c r="W12" s="34" t="n"/>
-      <c r="X12" s="34" t="n"/>
-      <c r="Y12" s="34" t="n"/>
-      <c r="Z12" s="34" t="n"/>
-      <c r="AA12" s="34" t="n"/>
-      <c r="AB12" s="34" t="n"/>
-      <c r="AC12" s="34" t="n"/>
-      <c r="AD12" s="34" t="n"/>
-      <c r="AE12" s="34" t="n"/>
-      <c r="AF12" s="34" t="n"/>
-      <c r="AG12" s="34" t="n"/>
-      <c r="AH12" s="35">
+      <c r="B12" s="38" t="n"/>
+      <c r="C12" s="39" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="39" t="n"/>
+      <c r="H12" s="39" t="n"/>
+      <c r="I12" s="39" t="n"/>
+      <c r="J12" s="39" t="n"/>
+      <c r="K12" s="39" t="n"/>
+      <c r="L12" s="39" t="n"/>
+      <c r="M12" s="39" t="n"/>
+      <c r="N12" s="39" t="n"/>
+      <c r="O12" s="39" t="n"/>
+      <c r="P12" s="39" t="n"/>
+      <c r="Q12" s="39" t="n"/>
+      <c r="R12" s="39" t="n"/>
+      <c r="S12" s="39" t="n"/>
+      <c r="T12" s="39" t="n"/>
+      <c r="U12" s="39" t="n"/>
+      <c r="V12" s="39" t="n"/>
+      <c r="W12" s="39" t="n"/>
+      <c r="X12" s="39" t="n"/>
+      <c r="Y12" s="39" t="n"/>
+      <c r="Z12" s="39" t="n"/>
+      <c r="AA12" s="39" t="n"/>
+      <c r="AB12" s="39" t="n"/>
+      <c r="AC12" s="39" t="n"/>
+      <c r="AD12" s="39" t="n"/>
+      <c r="AE12" s="39" t="n"/>
+      <c r="AF12" s="39" t="n"/>
+      <c r="AG12" s="39" t="n"/>
+      <c r="AH12" s="40">
         <f>COUNTIF(C12:AG12,"A")</f>
         <v/>
       </c>
-      <c r="AI12" s="35">
+      <c r="AI12" s="40">
         <f>COUNTIF(C12:AG12,"F")</f>
         <v/>
       </c>
-      <c r="AJ12" s="35">
+      <c r="AJ12" s="40">
         <f>COUNTIF(C12:AG12,"R")</f>
         <v/>
       </c>
-      <c r="AK12" s="35">
+      <c r="AK12" s="40">
         <f>COUNTIF(C12:AG12,"V")</f>
         <v/>
       </c>
-      <c r="AL12" s="35">
+      <c r="AL12" s="40">
         <f>COUNTIF(C12:AG12,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="33" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n"/>
-      <c r="F13" s="34" t="n"/>
-      <c r="G13" s="34" t="n"/>
-      <c r="H13" s="34" t="n"/>
-      <c r="I13" s="34" t="n"/>
-      <c r="J13" s="34" t="n"/>
-      <c r="K13" s="34" t="n"/>
-      <c r="L13" s="34" t="n"/>
-      <c r="M13" s="34" t="n"/>
-      <c r="N13" s="34" t="n"/>
-      <c r="O13" s="34" t="n"/>
-      <c r="P13" s="34" t="n"/>
-      <c r="Q13" s="34" t="n"/>
-      <c r="R13" s="34" t="n"/>
-      <c r="S13" s="34" t="n"/>
-      <c r="T13" s="34" t="n"/>
-      <c r="U13" s="34" t="n"/>
-      <c r="V13" s="34" t="n"/>
-      <c r="W13" s="34" t="n"/>
-      <c r="X13" s="34" t="n"/>
-      <c r="Y13" s="34" t="n"/>
-      <c r="Z13" s="34" t="n"/>
-      <c r="AA13" s="34" t="n"/>
-      <c r="AB13" s="34" t="n"/>
-      <c r="AC13" s="34" t="n"/>
-      <c r="AD13" s="34" t="n"/>
-      <c r="AE13" s="34" t="n"/>
-      <c r="AF13" s="34" t="n"/>
-      <c r="AG13" s="34" t="n"/>
-      <c r="AH13" s="35">
+      <c r="B13" s="38" t="n"/>
+      <c r="C13" s="39" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="39" t="n"/>
+      <c r="H13" s="39" t="n"/>
+      <c r="I13" s="39" t="n"/>
+      <c r="J13" s="39" t="n"/>
+      <c r="K13" s="39" t="n"/>
+      <c r="L13" s="39" t="n"/>
+      <c r="M13" s="39" t="n"/>
+      <c r="N13" s="39" t="n"/>
+      <c r="O13" s="39" t="n"/>
+      <c r="P13" s="39" t="n"/>
+      <c r="Q13" s="39" t="n"/>
+      <c r="R13" s="39" t="n"/>
+      <c r="S13" s="39" t="n"/>
+      <c r="T13" s="39" t="n"/>
+      <c r="U13" s="39" t="n"/>
+      <c r="V13" s="39" t="n"/>
+      <c r="W13" s="39" t="n"/>
+      <c r="X13" s="39" t="n"/>
+      <c r="Y13" s="39" t="n"/>
+      <c r="Z13" s="39" t="n"/>
+      <c r="AA13" s="39" t="n"/>
+      <c r="AB13" s="39" t="n"/>
+      <c r="AC13" s="39" t="n"/>
+      <c r="AD13" s="39" t="n"/>
+      <c r="AE13" s="39" t="n"/>
+      <c r="AF13" s="39" t="n"/>
+      <c r="AG13" s="39" t="n"/>
+      <c r="AH13" s="40">
         <f>COUNTIF(C13:AG13,"A")</f>
         <v/>
       </c>
-      <c r="AI13" s="35">
+      <c r="AI13" s="40">
         <f>COUNTIF(C13:AG13,"F")</f>
         <v/>
       </c>
-      <c r="AJ13" s="35">
+      <c r="AJ13" s="40">
         <f>COUNTIF(C13:AG13,"R")</f>
         <v/>
       </c>
-      <c r="AK13" s="35">
+      <c r="AK13" s="40">
         <f>COUNTIF(C13:AG13,"V")</f>
         <v/>
       </c>
-      <c r="AL13" s="35">
+      <c r="AL13" s="40">
         <f>COUNTIF(C13:AG13,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="33" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n"/>
-      <c r="F14" s="34" t="n"/>
-      <c r="G14" s="34" t="n"/>
-      <c r="H14" s="34" t="n"/>
-      <c r="I14" s="34" t="n"/>
-      <c r="J14" s="34" t="n"/>
-      <c r="K14" s="34" t="n"/>
-      <c r="L14" s="34" t="n"/>
-      <c r="M14" s="34" t="n"/>
-      <c r="N14" s="34" t="n"/>
-      <c r="O14" s="34" t="n"/>
-      <c r="P14" s="34" t="n"/>
-      <c r="Q14" s="34" t="n"/>
-      <c r="R14" s="34" t="n"/>
-      <c r="S14" s="34" t="n"/>
-      <c r="T14" s="34" t="n"/>
-      <c r="U14" s="34" t="n"/>
-      <c r="V14" s="34" t="n"/>
-      <c r="W14" s="34" t="n"/>
-      <c r="X14" s="34" t="n"/>
-      <c r="Y14" s="34" t="n"/>
-      <c r="Z14" s="34" t="n"/>
-      <c r="AA14" s="34" t="n"/>
-      <c r="AB14" s="34" t="n"/>
-      <c r="AC14" s="34" t="n"/>
-      <c r="AD14" s="34" t="n"/>
-      <c r="AE14" s="34" t="n"/>
-      <c r="AF14" s="34" t="n"/>
-      <c r="AG14" s="34" t="n"/>
-      <c r="AH14" s="35">
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="39" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="39" t="n"/>
+      <c r="H14" s="39" t="n"/>
+      <c r="I14" s="39" t="n"/>
+      <c r="J14" s="39" t="n"/>
+      <c r="K14" s="39" t="n"/>
+      <c r="L14" s="39" t="n"/>
+      <c r="M14" s="39" t="n"/>
+      <c r="N14" s="39" t="n"/>
+      <c r="O14" s="39" t="n"/>
+      <c r="P14" s="39" t="n"/>
+      <c r="Q14" s="39" t="n"/>
+      <c r="R14" s="39" t="n"/>
+      <c r="S14" s="39" t="n"/>
+      <c r="T14" s="39" t="n"/>
+      <c r="U14" s="39" t="n"/>
+      <c r="V14" s="39" t="n"/>
+      <c r="W14" s="39" t="n"/>
+      <c r="X14" s="39" t="n"/>
+      <c r="Y14" s="39" t="n"/>
+      <c r="Z14" s="39" t="n"/>
+      <c r="AA14" s="39" t="n"/>
+      <c r="AB14" s="39" t="n"/>
+      <c r="AC14" s="39" t="n"/>
+      <c r="AD14" s="39" t="n"/>
+      <c r="AE14" s="39" t="n"/>
+      <c r="AF14" s="39" t="n"/>
+      <c r="AG14" s="39" t="n"/>
+      <c r="AH14" s="40">
         <f>COUNTIF(C14:AG14,"A")</f>
         <v/>
       </c>
-      <c r="AI14" s="35">
+      <c r="AI14" s="40">
         <f>COUNTIF(C14:AG14,"F")</f>
         <v/>
       </c>
-      <c r="AJ14" s="35">
+      <c r="AJ14" s="40">
         <f>COUNTIF(C14:AG14,"R")</f>
         <v/>
       </c>
-      <c r="AK14" s="35">
+      <c r="AK14" s="40">
         <f>COUNTIF(C14:AG14,"V")</f>
         <v/>
       </c>
-      <c r="AL14" s="35">
+      <c r="AL14" s="40">
         <f>COUNTIF(C14:AG14,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="33" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n"/>
-      <c r="F15" s="34" t="n"/>
-      <c r="G15" s="34" t="n"/>
-      <c r="H15" s="34" t="n"/>
-      <c r="I15" s="34" t="n"/>
-      <c r="J15" s="34" t="n"/>
-      <c r="K15" s="34" t="n"/>
-      <c r="L15" s="34" t="n"/>
-      <c r="M15" s="34" t="n"/>
-      <c r="N15" s="34" t="n"/>
-      <c r="O15" s="34" t="n"/>
-      <c r="P15" s="34" t="n"/>
-      <c r="Q15" s="34" t="n"/>
-      <c r="R15" s="34" t="n"/>
-      <c r="S15" s="34" t="n"/>
-      <c r="T15" s="34" t="n"/>
-      <c r="U15" s="34" t="n"/>
-      <c r="V15" s="34" t="n"/>
-      <c r="W15" s="34" t="n"/>
-      <c r="X15" s="34" t="n"/>
-      <c r="Y15" s="34" t="n"/>
-      <c r="Z15" s="34" t="n"/>
-      <c r="AA15" s="34" t="n"/>
-      <c r="AB15" s="34" t="n"/>
-      <c r="AC15" s="34" t="n"/>
-      <c r="AD15" s="34" t="n"/>
-      <c r="AE15" s="34" t="n"/>
-      <c r="AF15" s="34" t="n"/>
-      <c r="AG15" s="34" t="n"/>
-      <c r="AH15" s="35">
+      <c r="B15" s="38" t="n"/>
+      <c r="C15" s="39" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="39" t="n"/>
+      <c r="H15" s="39" t="n"/>
+      <c r="I15" s="39" t="n"/>
+      <c r="J15" s="39" t="n"/>
+      <c r="K15" s="39" t="n"/>
+      <c r="L15" s="39" t="n"/>
+      <c r="M15" s="39" t="n"/>
+      <c r="N15" s="39" t="n"/>
+      <c r="O15" s="39" t="n"/>
+      <c r="P15" s="39" t="n"/>
+      <c r="Q15" s="39" t="n"/>
+      <c r="R15" s="39" t="n"/>
+      <c r="S15" s="39" t="n"/>
+      <c r="T15" s="39" t="n"/>
+      <c r="U15" s="39" t="n"/>
+      <c r="V15" s="39" t="n"/>
+      <c r="W15" s="39" t="n"/>
+      <c r="X15" s="39" t="n"/>
+      <c r="Y15" s="39" t="n"/>
+      <c r="Z15" s="39" t="n"/>
+      <c r="AA15" s="39" t="n"/>
+      <c r="AB15" s="39" t="n"/>
+      <c r="AC15" s="39" t="n"/>
+      <c r="AD15" s="39" t="n"/>
+      <c r="AE15" s="39" t="n"/>
+      <c r="AF15" s="39" t="n"/>
+      <c r="AG15" s="39" t="n"/>
+      <c r="AH15" s="40">
         <f>COUNTIF(C15:AG15,"A")</f>
         <v/>
       </c>
-      <c r="AI15" s="35">
+      <c r="AI15" s="40">
         <f>COUNTIF(C15:AG15,"F")</f>
         <v/>
       </c>
-      <c r="AJ15" s="35">
+      <c r="AJ15" s="40">
         <f>COUNTIF(C15:AG15,"R")</f>
         <v/>
       </c>
-      <c r="AK15" s="35">
+      <c r="AK15" s="40">
         <f>COUNTIF(C15:AG15,"V")</f>
         <v/>
       </c>
-      <c r="AL15" s="35">
+      <c r="AL15" s="40">
         <f>COUNTIF(C15:AG15,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="33" t="n">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n"/>
-      <c r="F16" s="34" t="n"/>
-      <c r="G16" s="34" t="n"/>
-      <c r="H16" s="34" t="n"/>
-      <c r="I16" s="34" t="n"/>
-      <c r="J16" s="34" t="n"/>
-      <c r="K16" s="34" t="n"/>
-      <c r="L16" s="34" t="n"/>
-      <c r="M16" s="34" t="n"/>
-      <c r="N16" s="34" t="n"/>
-      <c r="O16" s="34" t="n"/>
-      <c r="P16" s="34" t="n"/>
-      <c r="Q16" s="34" t="n"/>
-      <c r="R16" s="34" t="n"/>
-      <c r="S16" s="34" t="n"/>
-      <c r="T16" s="34" t="n"/>
-      <c r="U16" s="34" t="n"/>
-      <c r="V16" s="34" t="n"/>
-      <c r="W16" s="34" t="n"/>
-      <c r="X16" s="34" t="n"/>
-      <c r="Y16" s="34" t="n"/>
-      <c r="Z16" s="34" t="n"/>
-      <c r="AA16" s="34" t="n"/>
-      <c r="AB16" s="34" t="n"/>
-      <c r="AC16" s="34" t="n"/>
-      <c r="AD16" s="34" t="n"/>
-      <c r="AE16" s="34" t="n"/>
-      <c r="AF16" s="34" t="n"/>
-      <c r="AG16" s="34" t="n"/>
-      <c r="AH16" s="35">
+      <c r="B16" s="38" t="n"/>
+      <c r="C16" s="39" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="39" t="n"/>
+      <c r="H16" s="39" t="n"/>
+      <c r="I16" s="39" t="n"/>
+      <c r="J16" s="39" t="n"/>
+      <c r="K16" s="39" t="n"/>
+      <c r="L16" s="39" t="n"/>
+      <c r="M16" s="39" t="n"/>
+      <c r="N16" s="39" t="n"/>
+      <c r="O16" s="39" t="n"/>
+      <c r="P16" s="39" t="n"/>
+      <c r="Q16" s="39" t="n"/>
+      <c r="R16" s="39" t="n"/>
+      <c r="S16" s="39" t="n"/>
+      <c r="T16" s="39" t="n"/>
+      <c r="U16" s="39" t="n"/>
+      <c r="V16" s="39" t="n"/>
+      <c r="W16" s="39" t="n"/>
+      <c r="X16" s="39" t="n"/>
+      <c r="Y16" s="39" t="n"/>
+      <c r="Z16" s="39" t="n"/>
+      <c r="AA16" s="39" t="n"/>
+      <c r="AB16" s="39" t="n"/>
+      <c r="AC16" s="39" t="n"/>
+      <c r="AD16" s="39" t="n"/>
+      <c r="AE16" s="39" t="n"/>
+      <c r="AF16" s="39" t="n"/>
+      <c r="AG16" s="39" t="n"/>
+      <c r="AH16" s="40">
         <f>COUNTIF(C16:AG16,"A")</f>
         <v/>
       </c>
-      <c r="AI16" s="35">
+      <c r="AI16" s="40">
         <f>COUNTIF(C16:AG16,"F")</f>
         <v/>
       </c>
-      <c r="AJ16" s="35">
+      <c r="AJ16" s="40">
         <f>COUNTIF(C16:AG16,"R")</f>
         <v/>
       </c>
-      <c r="AK16" s="35">
+      <c r="AK16" s="40">
         <f>COUNTIF(C16:AG16,"V")</f>
         <v/>
       </c>
-      <c r="AL16" s="35">
+      <c r="AL16" s="40">
         <f>COUNTIF(C16:AG16,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="33" t="n">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="37" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="34" t="n"/>
-      <c r="D17" s="34" t="n"/>
-      <c r="E17" s="34" t="n"/>
-      <c r="F17" s="34" t="n"/>
-      <c r="G17" s="34" t="n"/>
-      <c r="H17" s="34" t="n"/>
-      <c r="I17" s="34" t="n"/>
-      <c r="J17" s="34" t="n"/>
-      <c r="K17" s="34" t="n"/>
-      <c r="L17" s="34" t="n"/>
-      <c r="M17" s="34" t="n"/>
-      <c r="N17" s="34" t="n"/>
-      <c r="O17" s="34" t="n"/>
-      <c r="P17" s="34" t="n"/>
-      <c r="Q17" s="34" t="n"/>
-      <c r="R17" s="34" t="n"/>
-      <c r="S17" s="34" t="n"/>
-      <c r="T17" s="34" t="n"/>
-      <c r="U17" s="34" t="n"/>
-      <c r="V17" s="34" t="n"/>
-      <c r="W17" s="34" t="n"/>
-      <c r="X17" s="34" t="n"/>
-      <c r="Y17" s="34" t="n"/>
-      <c r="Z17" s="34" t="n"/>
-      <c r="AA17" s="34" t="n"/>
-      <c r="AB17" s="34" t="n"/>
-      <c r="AC17" s="34" t="n"/>
-      <c r="AD17" s="34" t="n"/>
-      <c r="AE17" s="34" t="n"/>
-      <c r="AF17" s="34" t="n"/>
-      <c r="AG17" s="34" t="n"/>
-      <c r="AH17" s="35">
+      <c r="B17" s="38" t="n"/>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="39" t="n"/>
+      <c r="H17" s="39" t="n"/>
+      <c r="I17" s="39" t="n"/>
+      <c r="J17" s="39" t="n"/>
+      <c r="K17" s="39" t="n"/>
+      <c r="L17" s="39" t="n"/>
+      <c r="M17" s="39" t="n"/>
+      <c r="N17" s="39" t="n"/>
+      <c r="O17" s="39" t="n"/>
+      <c r="P17" s="39" t="n"/>
+      <c r="Q17" s="39" t="n"/>
+      <c r="R17" s="39" t="n"/>
+      <c r="S17" s="39" t="n"/>
+      <c r="T17" s="39" t="n"/>
+      <c r="U17" s="39" t="n"/>
+      <c r="V17" s="39" t="n"/>
+      <c r="W17" s="39" t="n"/>
+      <c r="X17" s="39" t="n"/>
+      <c r="Y17" s="39" t="n"/>
+      <c r="Z17" s="39" t="n"/>
+      <c r="AA17" s="39" t="n"/>
+      <c r="AB17" s="39" t="n"/>
+      <c r="AC17" s="39" t="n"/>
+      <c r="AD17" s="39" t="n"/>
+      <c r="AE17" s="39" t="n"/>
+      <c r="AF17" s="39" t="n"/>
+      <c r="AG17" s="39" t="n"/>
+      <c r="AH17" s="40">
         <f>COUNTIF(C17:AG17,"A")</f>
         <v/>
       </c>
-      <c r="AI17" s="35">
+      <c r="AI17" s="40">
         <f>COUNTIF(C17:AG17,"F")</f>
         <v/>
       </c>
-      <c r="AJ17" s="35">
+      <c r="AJ17" s="40">
         <f>COUNTIF(C17:AG17,"R")</f>
         <v/>
       </c>
-      <c r="AK17" s="35">
+      <c r="AK17" s="40">
         <f>COUNTIF(C17:AG17,"V")</f>
         <v/>
       </c>
-      <c r="AL17" s="35">
+      <c r="AL17" s="40">
         <f>COUNTIF(C17:AG17,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="33" t="n">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="34" t="n"/>
-      <c r="D18" s="34" t="n"/>
-      <c r="E18" s="34" t="n"/>
-      <c r="F18" s="34" t="n"/>
-      <c r="G18" s="34" t="n"/>
-      <c r="H18" s="34" t="n"/>
-      <c r="I18" s="34" t="n"/>
-      <c r="J18" s="34" t="n"/>
-      <c r="K18" s="34" t="n"/>
-      <c r="L18" s="34" t="n"/>
-      <c r="M18" s="34" t="n"/>
-      <c r="N18" s="34" t="n"/>
-      <c r="O18" s="34" t="n"/>
-      <c r="P18" s="34" t="n"/>
-      <c r="Q18" s="34" t="n"/>
-      <c r="R18" s="34" t="n"/>
-      <c r="S18" s="34" t="n"/>
-      <c r="T18" s="34" t="n"/>
-      <c r="U18" s="34" t="n"/>
-      <c r="V18" s="34" t="n"/>
-      <c r="W18" s="34" t="n"/>
-      <c r="X18" s="34" t="n"/>
-      <c r="Y18" s="34" t="n"/>
-      <c r="Z18" s="34" t="n"/>
-      <c r="AA18" s="34" t="n"/>
-      <c r="AB18" s="34" t="n"/>
-      <c r="AC18" s="34" t="n"/>
-      <c r="AD18" s="34" t="n"/>
-      <c r="AE18" s="34" t="n"/>
-      <c r="AF18" s="34" t="n"/>
-      <c r="AG18" s="34" t="n"/>
-      <c r="AH18" s="35">
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="39" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="39" t="n"/>
+      <c r="H18" s="39" t="n"/>
+      <c r="I18" s="39" t="n"/>
+      <c r="J18" s="39" t="n"/>
+      <c r="K18" s="39" t="n"/>
+      <c r="L18" s="39" t="n"/>
+      <c r="M18" s="39" t="n"/>
+      <c r="N18" s="39" t="n"/>
+      <c r="O18" s="39" t="n"/>
+      <c r="P18" s="39" t="n"/>
+      <c r="Q18" s="39" t="n"/>
+      <c r="R18" s="39" t="n"/>
+      <c r="S18" s="39" t="n"/>
+      <c r="T18" s="39" t="n"/>
+      <c r="U18" s="39" t="n"/>
+      <c r="V18" s="39" t="n"/>
+      <c r="W18" s="39" t="n"/>
+      <c r="X18" s="39" t="n"/>
+      <c r="Y18" s="39" t="n"/>
+      <c r="Z18" s="39" t="n"/>
+      <c r="AA18" s="39" t="n"/>
+      <c r="AB18" s="39" t="n"/>
+      <c r="AC18" s="39" t="n"/>
+      <c r="AD18" s="39" t="n"/>
+      <c r="AE18" s="39" t="n"/>
+      <c r="AF18" s="39" t="n"/>
+      <c r="AG18" s="39" t="n"/>
+      <c r="AH18" s="40">
         <f>COUNTIF(C18:AG18,"A")</f>
         <v/>
       </c>
-      <c r="AI18" s="35">
+      <c r="AI18" s="40">
         <f>COUNTIF(C18:AG18,"F")</f>
         <v/>
       </c>
-      <c r="AJ18" s="35">
+      <c r="AJ18" s="40">
         <f>COUNTIF(C18:AG18,"R")</f>
         <v/>
       </c>
-      <c r="AK18" s="35">
+      <c r="AK18" s="40">
         <f>COUNTIF(C18:AG18,"V")</f>
         <v/>
       </c>
-      <c r="AL18" s="35">
+      <c r="AL18" s="40">
         <f>COUNTIF(C18:AG18,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="33" t="n">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="37" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="34" t="n"/>
-      <c r="E19" s="34" t="n"/>
-      <c r="F19" s="34" t="n"/>
-      <c r="G19" s="34" t="n"/>
-      <c r="H19" s="34" t="n"/>
-      <c r="I19" s="34" t="n"/>
-      <c r="J19" s="34" t="n"/>
-      <c r="K19" s="34" t="n"/>
-      <c r="L19" s="34" t="n"/>
-      <c r="M19" s="34" t="n"/>
-      <c r="N19" s="34" t="n"/>
-      <c r="O19" s="34" t="n"/>
-      <c r="P19" s="34" t="n"/>
-      <c r="Q19" s="34" t="n"/>
-      <c r="R19" s="34" t="n"/>
-      <c r="S19" s="34" t="n"/>
-      <c r="T19" s="34" t="n"/>
-      <c r="U19" s="34" t="n"/>
-      <c r="V19" s="34" t="n"/>
-      <c r="W19" s="34" t="n"/>
-      <c r="X19" s="34" t="n"/>
-      <c r="Y19" s="34" t="n"/>
-      <c r="Z19" s="34" t="n"/>
-      <c r="AA19" s="34" t="n"/>
-      <c r="AB19" s="34" t="n"/>
-      <c r="AC19" s="34" t="n"/>
-      <c r="AD19" s="34" t="n"/>
-      <c r="AE19" s="34" t="n"/>
-      <c r="AF19" s="34" t="n"/>
-      <c r="AG19" s="34" t="n"/>
-      <c r="AH19" s="35">
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="39" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="39" t="n"/>
+      <c r="H19" s="39" t="n"/>
+      <c r="I19" s="39" t="n"/>
+      <c r="J19" s="39" t="n"/>
+      <c r="K19" s="39" t="n"/>
+      <c r="L19" s="39" t="n"/>
+      <c r="M19" s="39" t="n"/>
+      <c r="N19" s="39" t="n"/>
+      <c r="O19" s="39" t="n"/>
+      <c r="P19" s="39" t="n"/>
+      <c r="Q19" s="39" t="n"/>
+      <c r="R19" s="39" t="n"/>
+      <c r="S19" s="39" t="n"/>
+      <c r="T19" s="39" t="n"/>
+      <c r="U19" s="39" t="n"/>
+      <c r="V19" s="39" t="n"/>
+      <c r="W19" s="39" t="n"/>
+      <c r="X19" s="39" t="n"/>
+      <c r="Y19" s="39" t="n"/>
+      <c r="Z19" s="39" t="n"/>
+      <c r="AA19" s="39" t="n"/>
+      <c r="AB19" s="39" t="n"/>
+      <c r="AC19" s="39" t="n"/>
+      <c r="AD19" s="39" t="n"/>
+      <c r="AE19" s="39" t="n"/>
+      <c r="AF19" s="39" t="n"/>
+      <c r="AG19" s="39" t="n"/>
+      <c r="AH19" s="40">
         <f>COUNTIF(C19:AG19,"A")</f>
         <v/>
       </c>
-      <c r="AI19" s="35">
+      <c r="AI19" s="40">
         <f>COUNTIF(C19:AG19,"F")</f>
         <v/>
       </c>
-      <c r="AJ19" s="35">
+      <c r="AJ19" s="40">
         <f>COUNTIF(C19:AG19,"R")</f>
         <v/>
       </c>
-      <c r="AK19" s="35">
+      <c r="AK19" s="40">
         <f>COUNTIF(C19:AG19,"V")</f>
         <v/>
       </c>
-      <c r="AL19" s="35">
+      <c r="AL19" s="40">
         <f>COUNTIF(C19:AG19,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="33" t="n">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="37" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="34" t="n"/>
-      <c r="D20" s="34" t="n"/>
-      <c r="E20" s="34" t="n"/>
-      <c r="F20" s="34" t="n"/>
-      <c r="G20" s="34" t="n"/>
-      <c r="H20" s="34" t="n"/>
-      <c r="I20" s="34" t="n"/>
-      <c r="J20" s="34" t="n"/>
-      <c r="K20" s="34" t="n"/>
-      <c r="L20" s="34" t="n"/>
-      <c r="M20" s="34" t="n"/>
-      <c r="N20" s="34" t="n"/>
-      <c r="O20" s="34" t="n"/>
-      <c r="P20" s="34" t="n"/>
-      <c r="Q20" s="34" t="n"/>
-      <c r="R20" s="34" t="n"/>
-      <c r="S20" s="34" t="n"/>
-      <c r="T20" s="34" t="n"/>
-      <c r="U20" s="34" t="n"/>
-      <c r="V20" s="34" t="n"/>
-      <c r="W20" s="34" t="n"/>
-      <c r="X20" s="34" t="n"/>
-      <c r="Y20" s="34" t="n"/>
-      <c r="Z20" s="34" t="n"/>
-      <c r="AA20" s="34" t="n"/>
-      <c r="AB20" s="34" t="n"/>
-      <c r="AC20" s="34" t="n"/>
-      <c r="AD20" s="34" t="n"/>
-      <c r="AE20" s="34" t="n"/>
-      <c r="AF20" s="34" t="n"/>
-      <c r="AG20" s="34" t="n"/>
-      <c r="AH20" s="35">
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="39" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="39" t="n"/>
+      <c r="H20" s="39" t="n"/>
+      <c r="I20" s="39" t="n"/>
+      <c r="J20" s="39" t="n"/>
+      <c r="K20" s="39" t="n"/>
+      <c r="L20" s="39" t="n"/>
+      <c r="M20" s="39" t="n"/>
+      <c r="N20" s="39" t="n"/>
+      <c r="O20" s="39" t="n"/>
+      <c r="P20" s="39" t="n"/>
+      <c r="Q20" s="39" t="n"/>
+      <c r="R20" s="39" t="n"/>
+      <c r="S20" s="39" t="n"/>
+      <c r="T20" s="39" t="n"/>
+      <c r="U20" s="39" t="n"/>
+      <c r="V20" s="39" t="n"/>
+      <c r="W20" s="39" t="n"/>
+      <c r="X20" s="39" t="n"/>
+      <c r="Y20" s="39" t="n"/>
+      <c r="Z20" s="39" t="n"/>
+      <c r="AA20" s="39" t="n"/>
+      <c r="AB20" s="39" t="n"/>
+      <c r="AC20" s="39" t="n"/>
+      <c r="AD20" s="39" t="n"/>
+      <c r="AE20" s="39" t="n"/>
+      <c r="AF20" s="39" t="n"/>
+      <c r="AG20" s="39" t="n"/>
+      <c r="AH20" s="40">
         <f>COUNTIF(C20:AG20,"A")</f>
         <v/>
       </c>
-      <c r="AI20" s="35">
+      <c r="AI20" s="40">
         <f>COUNTIF(C20:AG20,"F")</f>
         <v/>
       </c>
-      <c r="AJ20" s="35">
+      <c r="AJ20" s="40">
         <f>COUNTIF(C20:AG20,"R")</f>
         <v/>
       </c>
-      <c r="AK20" s="35">
+      <c r="AK20" s="40">
         <f>COUNTIF(C20:AG20,"V")</f>
         <v/>
       </c>
-      <c r="AL20" s="35">
+      <c r="AL20" s="40">
         <f>COUNTIF(C20:AG20,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="33" t="n">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="37" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="34" t="n"/>
-      <c r="D21" s="34" t="n"/>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="34" t="n"/>
-      <c r="G21" s="34" t="n"/>
-      <c r="H21" s="34" t="n"/>
-      <c r="I21" s="34" t="n"/>
-      <c r="J21" s="34" t="n"/>
-      <c r="K21" s="34" t="n"/>
-      <c r="L21" s="34" t="n"/>
-      <c r="M21" s="34" t="n"/>
-      <c r="N21" s="34" t="n"/>
-      <c r="O21" s="34" t="n"/>
-      <c r="P21" s="34" t="n"/>
-      <c r="Q21" s="34" t="n"/>
-      <c r="R21" s="34" t="n"/>
-      <c r="S21" s="34" t="n"/>
-      <c r="T21" s="34" t="n"/>
-      <c r="U21" s="34" t="n"/>
-      <c r="V21" s="34" t="n"/>
-      <c r="W21" s="34" t="n"/>
-      <c r="X21" s="34" t="n"/>
-      <c r="Y21" s="34" t="n"/>
-      <c r="Z21" s="34" t="n"/>
-      <c r="AA21" s="34" t="n"/>
-      <c r="AB21" s="34" t="n"/>
-      <c r="AC21" s="34" t="n"/>
-      <c r="AD21" s="34" t="n"/>
-      <c r="AE21" s="34" t="n"/>
-      <c r="AF21" s="34" t="n"/>
-      <c r="AG21" s="34" t="n"/>
-      <c r="AH21" s="35">
+      <c r="B21" s="38" t="n"/>
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="39" t="n"/>
+      <c r="H21" s="39" t="n"/>
+      <c r="I21" s="39" t="n"/>
+      <c r="J21" s="39" t="n"/>
+      <c r="K21" s="39" t="n"/>
+      <c r="L21" s="39" t="n"/>
+      <c r="M21" s="39" t="n"/>
+      <c r="N21" s="39" t="n"/>
+      <c r="O21" s="39" t="n"/>
+      <c r="P21" s="39" t="n"/>
+      <c r="Q21" s="39" t="n"/>
+      <c r="R21" s="39" t="n"/>
+      <c r="S21" s="39" t="n"/>
+      <c r="T21" s="39" t="n"/>
+      <c r="U21" s="39" t="n"/>
+      <c r="V21" s="39" t="n"/>
+      <c r="W21" s="39" t="n"/>
+      <c r="X21" s="39" t="n"/>
+      <c r="Y21" s="39" t="n"/>
+      <c r="Z21" s="39" t="n"/>
+      <c r="AA21" s="39" t="n"/>
+      <c r="AB21" s="39" t="n"/>
+      <c r="AC21" s="39" t="n"/>
+      <c r="AD21" s="39" t="n"/>
+      <c r="AE21" s="39" t="n"/>
+      <c r="AF21" s="39" t="n"/>
+      <c r="AG21" s="39" t="n"/>
+      <c r="AH21" s="40">
         <f>COUNTIF(C21:AG21,"A")</f>
         <v/>
       </c>
-      <c r="AI21" s="35">
+      <c r="AI21" s="40">
         <f>COUNTIF(C21:AG21,"F")</f>
         <v/>
       </c>
-      <c r="AJ21" s="35">
+      <c r="AJ21" s="40">
         <f>COUNTIF(C21:AG21,"R")</f>
         <v/>
       </c>
-      <c r="AK21" s="35">
+      <c r="AK21" s="40">
         <f>COUNTIF(C21:AG21,"V")</f>
         <v/>
       </c>
-      <c r="AL21" s="35">
+      <c r="AL21" s="40">
         <f>COUNTIF(C21:AG21,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="33" t="n">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="37" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="34" t="n"/>
-      <c r="D22" s="34" t="n"/>
-      <c r="E22" s="34" t="n"/>
-      <c r="F22" s="34" t="n"/>
-      <c r="G22" s="34" t="n"/>
-      <c r="H22" s="34" t="n"/>
-      <c r="I22" s="34" t="n"/>
-      <c r="J22" s="34" t="n"/>
-      <c r="K22" s="34" t="n"/>
-      <c r="L22" s="34" t="n"/>
-      <c r="M22" s="34" t="n"/>
-      <c r="N22" s="34" t="n"/>
-      <c r="O22" s="34" t="n"/>
-      <c r="P22" s="34" t="n"/>
-      <c r="Q22" s="34" t="n"/>
-      <c r="R22" s="34" t="n"/>
-      <c r="S22" s="34" t="n"/>
-      <c r="T22" s="34" t="n"/>
-      <c r="U22" s="34" t="n"/>
-      <c r="V22" s="34" t="n"/>
-      <c r="W22" s="34" t="n"/>
-      <c r="X22" s="34" t="n"/>
-      <c r="Y22" s="34" t="n"/>
-      <c r="Z22" s="34" t="n"/>
-      <c r="AA22" s="34" t="n"/>
-      <c r="AB22" s="34" t="n"/>
-      <c r="AC22" s="34" t="n"/>
-      <c r="AD22" s="34" t="n"/>
-      <c r="AE22" s="34" t="n"/>
-      <c r="AF22" s="34" t="n"/>
-      <c r="AG22" s="34" t="n"/>
-      <c r="AH22" s="35">
+      <c r="B22" s="38" t="n"/>
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
+      <c r="H22" s="39" t="n"/>
+      <c r="I22" s="39" t="n"/>
+      <c r="J22" s="39" t="n"/>
+      <c r="K22" s="39" t="n"/>
+      <c r="L22" s="39" t="n"/>
+      <c r="M22" s="39" t="n"/>
+      <c r="N22" s="39" t="n"/>
+      <c r="O22" s="39" t="n"/>
+      <c r="P22" s="39" t="n"/>
+      <c r="Q22" s="39" t="n"/>
+      <c r="R22" s="39" t="n"/>
+      <c r="S22" s="39" t="n"/>
+      <c r="T22" s="39" t="n"/>
+      <c r="U22" s="39" t="n"/>
+      <c r="V22" s="39" t="n"/>
+      <c r="W22" s="39" t="n"/>
+      <c r="X22" s="39" t="n"/>
+      <c r="Y22" s="39" t="n"/>
+      <c r="Z22" s="39" t="n"/>
+      <c r="AA22" s="39" t="n"/>
+      <c r="AB22" s="39" t="n"/>
+      <c r="AC22" s="39" t="n"/>
+      <c r="AD22" s="39" t="n"/>
+      <c r="AE22" s="39" t="n"/>
+      <c r="AF22" s="39" t="n"/>
+      <c r="AG22" s="39" t="n"/>
+      <c r="AH22" s="40">
         <f>COUNTIF(C22:AG22,"A")</f>
         <v/>
       </c>
-      <c r="AI22" s="35">
+      <c r="AI22" s="40">
         <f>COUNTIF(C22:AG22,"F")</f>
         <v/>
       </c>
-      <c r="AJ22" s="35">
+      <c r="AJ22" s="40">
         <f>COUNTIF(C22:AG22,"R")</f>
         <v/>
       </c>
-      <c r="AK22" s="35">
+      <c r="AK22" s="40">
         <f>COUNTIF(C22:AG22,"V")</f>
         <v/>
       </c>
-      <c r="AL22" s="35">
+      <c r="AL22" s="40">
         <f>COUNTIF(C22:AG22,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="33" t="n">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="37" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="34" t="n"/>
-      <c r="D23" s="34" t="n"/>
-      <c r="E23" s="34" t="n"/>
-      <c r="F23" s="34" t="n"/>
-      <c r="G23" s="34" t="n"/>
-      <c r="H23" s="34" t="n"/>
-      <c r="I23" s="34" t="n"/>
-      <c r="J23" s="34" t="n"/>
-      <c r="K23" s="34" t="n"/>
-      <c r="L23" s="34" t="n"/>
-      <c r="M23" s="34" t="n"/>
-      <c r="N23" s="34" t="n"/>
-      <c r="O23" s="34" t="n"/>
-      <c r="P23" s="34" t="n"/>
-      <c r="Q23" s="34" t="n"/>
-      <c r="R23" s="34" t="n"/>
-      <c r="S23" s="34" t="n"/>
-      <c r="T23" s="34" t="n"/>
-      <c r="U23" s="34" t="n"/>
-      <c r="V23" s="34" t="n"/>
-      <c r="W23" s="34" t="n"/>
-      <c r="X23" s="34" t="n"/>
-      <c r="Y23" s="34" t="n"/>
-      <c r="Z23" s="34" t="n"/>
-      <c r="AA23" s="34" t="n"/>
-      <c r="AB23" s="34" t="n"/>
-      <c r="AC23" s="34" t="n"/>
-      <c r="AD23" s="34" t="n"/>
-      <c r="AE23" s="34" t="n"/>
-      <c r="AF23" s="34" t="n"/>
-      <c r="AG23" s="34" t="n"/>
-      <c r="AH23" s="35">
+      <c r="B23" s="38" t="n"/>
+      <c r="C23" s="39" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
+      <c r="H23" s="39" t="n"/>
+      <c r="I23" s="39" t="n"/>
+      <c r="J23" s="39" t="n"/>
+      <c r="K23" s="39" t="n"/>
+      <c r="L23" s="39" t="n"/>
+      <c r="M23" s="39" t="n"/>
+      <c r="N23" s="39" t="n"/>
+      <c r="O23" s="39" t="n"/>
+      <c r="P23" s="39" t="n"/>
+      <c r="Q23" s="39" t="n"/>
+      <c r="R23" s="39" t="n"/>
+      <c r="S23" s="39" t="n"/>
+      <c r="T23" s="39" t="n"/>
+      <c r="U23" s="39" t="n"/>
+      <c r="V23" s="39" t="n"/>
+      <c r="W23" s="39" t="n"/>
+      <c r="X23" s="39" t="n"/>
+      <c r="Y23" s="39" t="n"/>
+      <c r="Z23" s="39" t="n"/>
+      <c r="AA23" s="39" t="n"/>
+      <c r="AB23" s="39" t="n"/>
+      <c r="AC23" s="39" t="n"/>
+      <c r="AD23" s="39" t="n"/>
+      <c r="AE23" s="39" t="n"/>
+      <c r="AF23" s="39" t="n"/>
+      <c r="AG23" s="39" t="n"/>
+      <c r="AH23" s="40">
         <f>COUNTIF(C23:AG23,"A")</f>
         <v/>
       </c>
-      <c r="AI23" s="35">
+      <c r="AI23" s="40">
         <f>COUNTIF(C23:AG23,"F")</f>
         <v/>
       </c>
-      <c r="AJ23" s="35">
+      <c r="AJ23" s="40">
         <f>COUNTIF(C23:AG23,"R")</f>
         <v/>
       </c>
-      <c r="AK23" s="35">
+      <c r="AK23" s="40">
         <f>COUNTIF(C23:AG23,"V")</f>
         <v/>
       </c>
-      <c r="AL23" s="35">
+      <c r="AL23" s="40">
         <f>COUNTIF(C23:AG23,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="33" t="n">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="37" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="34" t="n"/>
-      <c r="D24" s="34" t="n"/>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="34" t="n"/>
-      <c r="G24" s="34" t="n"/>
-      <c r="H24" s="34" t="n"/>
-      <c r="I24" s="34" t="n"/>
-      <c r="J24" s="34" t="n"/>
-      <c r="K24" s="34" t="n"/>
-      <c r="L24" s="34" t="n"/>
-      <c r="M24" s="34" t="n"/>
-      <c r="N24" s="34" t="n"/>
-      <c r="O24" s="34" t="n"/>
-      <c r="P24" s="34" t="n"/>
-      <c r="Q24" s="34" t="n"/>
-      <c r="R24" s="34" t="n"/>
-      <c r="S24" s="34" t="n"/>
-      <c r="T24" s="34" t="n"/>
-      <c r="U24" s="34" t="n"/>
-      <c r="V24" s="34" t="n"/>
-      <c r="W24" s="34" t="n"/>
-      <c r="X24" s="34" t="n"/>
-      <c r="Y24" s="34" t="n"/>
-      <c r="Z24" s="34" t="n"/>
-      <c r="AA24" s="34" t="n"/>
-      <c r="AB24" s="34" t="n"/>
-      <c r="AC24" s="34" t="n"/>
-      <c r="AD24" s="34" t="n"/>
-      <c r="AE24" s="34" t="n"/>
-      <c r="AF24" s="34" t="n"/>
-      <c r="AG24" s="34" t="n"/>
-      <c r="AH24" s="35">
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="39" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="39" t="n"/>
+      <c r="K24" s="39" t="n"/>
+      <c r="L24" s="39" t="n"/>
+      <c r="M24" s="39" t="n"/>
+      <c r="N24" s="39" t="n"/>
+      <c r="O24" s="39" t="n"/>
+      <c r="P24" s="39" t="n"/>
+      <c r="Q24" s="39" t="n"/>
+      <c r="R24" s="39" t="n"/>
+      <c r="S24" s="39" t="n"/>
+      <c r="T24" s="39" t="n"/>
+      <c r="U24" s="39" t="n"/>
+      <c r="V24" s="39" t="n"/>
+      <c r="W24" s="39" t="n"/>
+      <c r="X24" s="39" t="n"/>
+      <c r="Y24" s="39" t="n"/>
+      <c r="Z24" s="39" t="n"/>
+      <c r="AA24" s="39" t="n"/>
+      <c r="AB24" s="39" t="n"/>
+      <c r="AC24" s="39" t="n"/>
+      <c r="AD24" s="39" t="n"/>
+      <c r="AE24" s="39" t="n"/>
+      <c r="AF24" s="39" t="n"/>
+      <c r="AG24" s="39" t="n"/>
+      <c r="AH24" s="40">
         <f>COUNTIF(C24:AG24,"A")</f>
         <v/>
       </c>
-      <c r="AI24" s="35">
+      <c r="AI24" s="40">
         <f>COUNTIF(C24:AG24,"F")</f>
         <v/>
       </c>
-      <c r="AJ24" s="35">
+      <c r="AJ24" s="40">
         <f>COUNTIF(C24:AG24,"R")</f>
         <v/>
       </c>
-      <c r="AK24" s="35">
+      <c r="AK24" s="40">
         <f>COUNTIF(C24:AG24,"V")</f>
         <v/>
       </c>
-      <c r="AL24" s="35">
+      <c r="AL24" s="40">
         <f>COUNTIF(C24:AG24,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="33" t="n">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="37" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="34" t="n"/>
-      <c r="D25" s="34" t="n"/>
-      <c r="E25" s="34" t="n"/>
-      <c r="F25" s="34" t="n"/>
-      <c r="G25" s="34" t="n"/>
-      <c r="H25" s="34" t="n"/>
-      <c r="I25" s="34" t="n"/>
-      <c r="J25" s="34" t="n"/>
-      <c r="K25" s="34" t="n"/>
-      <c r="L25" s="34" t="n"/>
-      <c r="M25" s="34" t="n"/>
-      <c r="N25" s="34" t="n"/>
-      <c r="O25" s="34" t="n"/>
-      <c r="P25" s="34" t="n"/>
-      <c r="Q25" s="34" t="n"/>
-      <c r="R25" s="34" t="n"/>
-      <c r="S25" s="34" t="n"/>
-      <c r="T25" s="34" t="n"/>
-      <c r="U25" s="34" t="n"/>
-      <c r="V25" s="34" t="n"/>
-      <c r="W25" s="34" t="n"/>
-      <c r="X25" s="34" t="n"/>
-      <c r="Y25" s="34" t="n"/>
-      <c r="Z25" s="34" t="n"/>
-      <c r="AA25" s="34" t="n"/>
-      <c r="AB25" s="34" t="n"/>
-      <c r="AC25" s="34" t="n"/>
-      <c r="AD25" s="34" t="n"/>
-      <c r="AE25" s="34" t="n"/>
-      <c r="AF25" s="34" t="n"/>
-      <c r="AG25" s="34" t="n"/>
-      <c r="AH25" s="35">
+      <c r="B25" s="38" t="n"/>
+      <c r="C25" s="39" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+      <c r="H25" s="39" t="n"/>
+      <c r="I25" s="39" t="n"/>
+      <c r="J25" s="39" t="n"/>
+      <c r="K25" s="39" t="n"/>
+      <c r="L25" s="39" t="n"/>
+      <c r="M25" s="39" t="n"/>
+      <c r="N25" s="39" t="n"/>
+      <c r="O25" s="39" t="n"/>
+      <c r="P25" s="39" t="n"/>
+      <c r="Q25" s="39" t="n"/>
+      <c r="R25" s="39" t="n"/>
+      <c r="S25" s="39" t="n"/>
+      <c r="T25" s="39" t="n"/>
+      <c r="U25" s="39" t="n"/>
+      <c r="V25" s="39" t="n"/>
+      <c r="W25" s="39" t="n"/>
+      <c r="X25" s="39" t="n"/>
+      <c r="Y25" s="39" t="n"/>
+      <c r="Z25" s="39" t="n"/>
+      <c r="AA25" s="39" t="n"/>
+      <c r="AB25" s="39" t="n"/>
+      <c r="AC25" s="39" t="n"/>
+      <c r="AD25" s="39" t="n"/>
+      <c r="AE25" s="39" t="n"/>
+      <c r="AF25" s="39" t="n"/>
+      <c r="AG25" s="39" t="n"/>
+      <c r="AH25" s="40">
         <f>COUNTIF(C25:AG25,"A")</f>
         <v/>
       </c>
-      <c r="AI25" s="35">
+      <c r="AI25" s="40">
         <f>COUNTIF(C25:AG25,"F")</f>
         <v/>
       </c>
-      <c r="AJ25" s="35">
+      <c r="AJ25" s="40">
         <f>COUNTIF(C25:AG25,"R")</f>
         <v/>
       </c>
-      <c r="AK25" s="35">
+      <c r="AK25" s="40">
         <f>COUNTIF(C25:AG25,"V")</f>
         <v/>
       </c>
-      <c r="AL25" s="35">
+      <c r="AL25" s="40">
         <f>COUNTIF(C25:AG25,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="33" t="n">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="37" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="34" t="n"/>
-      <c r="D26" s="34" t="n"/>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="34" t="n"/>
-      <c r="G26" s="34" t="n"/>
-      <c r="H26" s="34" t="n"/>
-      <c r="I26" s="34" t="n"/>
-      <c r="J26" s="34" t="n"/>
-      <c r="K26" s="34" t="n"/>
-      <c r="L26" s="34" t="n"/>
-      <c r="M26" s="34" t="n"/>
-      <c r="N26" s="34" t="n"/>
-      <c r="O26" s="34" t="n"/>
-      <c r="P26" s="34" t="n"/>
-      <c r="Q26" s="34" t="n"/>
-      <c r="R26" s="34" t="n"/>
-      <c r="S26" s="34" t="n"/>
-      <c r="T26" s="34" t="n"/>
-      <c r="U26" s="34" t="n"/>
-      <c r="V26" s="34" t="n"/>
-      <c r="W26" s="34" t="n"/>
-      <c r="X26" s="34" t="n"/>
-      <c r="Y26" s="34" t="n"/>
-      <c r="Z26" s="34" t="n"/>
-      <c r="AA26" s="34" t="n"/>
-      <c r="AB26" s="34" t="n"/>
-      <c r="AC26" s="34" t="n"/>
-      <c r="AD26" s="34" t="n"/>
-      <c r="AE26" s="34" t="n"/>
-      <c r="AF26" s="34" t="n"/>
-      <c r="AG26" s="34" t="n"/>
-      <c r="AH26" s="35">
+      <c r="B26" s="38" t="n"/>
+      <c r="C26" s="39" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="39" t="n"/>
+      <c r="H26" s="39" t="n"/>
+      <c r="I26" s="39" t="n"/>
+      <c r="J26" s="39" t="n"/>
+      <c r="K26" s="39" t="n"/>
+      <c r="L26" s="39" t="n"/>
+      <c r="M26" s="39" t="n"/>
+      <c r="N26" s="39" t="n"/>
+      <c r="O26" s="39" t="n"/>
+      <c r="P26" s="39" t="n"/>
+      <c r="Q26" s="39" t="n"/>
+      <c r="R26" s="39" t="n"/>
+      <c r="S26" s="39" t="n"/>
+      <c r="T26" s="39" t="n"/>
+      <c r="U26" s="39" t="n"/>
+      <c r="V26" s="39" t="n"/>
+      <c r="W26" s="39" t="n"/>
+      <c r="X26" s="39" t="n"/>
+      <c r="Y26" s="39" t="n"/>
+      <c r="Z26" s="39" t="n"/>
+      <c r="AA26" s="39" t="n"/>
+      <c r="AB26" s="39" t="n"/>
+      <c r="AC26" s="39" t="n"/>
+      <c r="AD26" s="39" t="n"/>
+      <c r="AE26" s="39" t="n"/>
+      <c r="AF26" s="39" t="n"/>
+      <c r="AG26" s="39" t="n"/>
+      <c r="AH26" s="40">
         <f>COUNTIF(C26:AG26,"A")</f>
         <v/>
       </c>
-      <c r="AI26" s="35">
+      <c r="AI26" s="40">
         <f>COUNTIF(C26:AG26,"F")</f>
         <v/>
       </c>
-      <c r="AJ26" s="35">
+      <c r="AJ26" s="40">
         <f>COUNTIF(C26:AG26,"R")</f>
         <v/>
       </c>
-      <c r="AK26" s="35">
+      <c r="AK26" s="40">
         <f>COUNTIF(C26:AG26,"V")</f>
         <v/>
       </c>
-      <c r="AL26" s="35">
+      <c r="AL26" s="40">
         <f>COUNTIF(C26:AG26,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="33" t="n">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="37" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="34" t="n"/>
-      <c r="D27" s="34" t="n"/>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="34" t="n"/>
-      <c r="G27" s="34" t="n"/>
-      <c r="H27" s="34" t="n"/>
-      <c r="I27" s="34" t="n"/>
-      <c r="J27" s="34" t="n"/>
-      <c r="K27" s="34" t="n"/>
-      <c r="L27" s="34" t="n"/>
-      <c r="M27" s="34" t="n"/>
-      <c r="N27" s="34" t="n"/>
-      <c r="O27" s="34" t="n"/>
-      <c r="P27" s="34" t="n"/>
-      <c r="Q27" s="34" t="n"/>
-      <c r="R27" s="34" t="n"/>
-      <c r="S27" s="34" t="n"/>
-      <c r="T27" s="34" t="n"/>
-      <c r="U27" s="34" t="n"/>
-      <c r="V27" s="34" t="n"/>
-      <c r="W27" s="34" t="n"/>
-      <c r="X27" s="34" t="n"/>
-      <c r="Y27" s="34" t="n"/>
-      <c r="Z27" s="34" t="n"/>
-      <c r="AA27" s="34" t="n"/>
-      <c r="AB27" s="34" t="n"/>
-      <c r="AC27" s="34" t="n"/>
-      <c r="AD27" s="34" t="n"/>
-      <c r="AE27" s="34" t="n"/>
-      <c r="AF27" s="34" t="n"/>
-      <c r="AG27" s="34" t="n"/>
-      <c r="AH27" s="35">
+      <c r="B27" s="38" t="n"/>
+      <c r="C27" s="39" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="39" t="n"/>
+      <c r="H27" s="39" t="n"/>
+      <c r="I27" s="39" t="n"/>
+      <c r="J27" s="39" t="n"/>
+      <c r="K27" s="39" t="n"/>
+      <c r="L27" s="39" t="n"/>
+      <c r="M27" s="39" t="n"/>
+      <c r="N27" s="39" t="n"/>
+      <c r="O27" s="39" t="n"/>
+      <c r="P27" s="39" t="n"/>
+      <c r="Q27" s="39" t="n"/>
+      <c r="R27" s="39" t="n"/>
+      <c r="S27" s="39" t="n"/>
+      <c r="T27" s="39" t="n"/>
+      <c r="U27" s="39" t="n"/>
+      <c r="V27" s="39" t="n"/>
+      <c r="W27" s="39" t="n"/>
+      <c r="X27" s="39" t="n"/>
+      <c r="Y27" s="39" t="n"/>
+      <c r="Z27" s="39" t="n"/>
+      <c r="AA27" s="39" t="n"/>
+      <c r="AB27" s="39" t="n"/>
+      <c r="AC27" s="39" t="n"/>
+      <c r="AD27" s="39" t="n"/>
+      <c r="AE27" s="39" t="n"/>
+      <c r="AF27" s="39" t="n"/>
+      <c r="AG27" s="39" t="n"/>
+      <c r="AH27" s="40">
         <f>COUNTIF(C27:AG27,"A")</f>
         <v/>
       </c>
-      <c r="AI27" s="35">
+      <c r="AI27" s="40">
         <f>COUNTIF(C27:AG27,"F")</f>
         <v/>
       </c>
-      <c r="AJ27" s="35">
+      <c r="AJ27" s="40">
         <f>COUNTIF(C27:AG27,"R")</f>
         <v/>
       </c>
-      <c r="AK27" s="35">
+      <c r="AK27" s="40">
         <f>COUNTIF(C27:AG27,"V")</f>
         <v/>
       </c>
-      <c r="AL27" s="35">
+      <c r="AL27" s="40">
         <f>COUNTIF(C27:AG27,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="33" t="n">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="37" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="34" t="n"/>
-      <c r="D28" s="34" t="n"/>
-      <c r="E28" s="34" t="n"/>
-      <c r="F28" s="34" t="n"/>
-      <c r="G28" s="34" t="n"/>
-      <c r="H28" s="34" t="n"/>
-      <c r="I28" s="34" t="n"/>
-      <c r="J28" s="34" t="n"/>
-      <c r="K28" s="34" t="n"/>
-      <c r="L28" s="34" t="n"/>
-      <c r="M28" s="34" t="n"/>
-      <c r="N28" s="34" t="n"/>
-      <c r="O28" s="34" t="n"/>
-      <c r="P28" s="34" t="n"/>
-      <c r="Q28" s="34" t="n"/>
-      <c r="R28" s="34" t="n"/>
-      <c r="S28" s="34" t="n"/>
-      <c r="T28" s="34" t="n"/>
-      <c r="U28" s="34" t="n"/>
-      <c r="V28" s="34" t="n"/>
-      <c r="W28" s="34" t="n"/>
-      <c r="X28" s="34" t="n"/>
-      <c r="Y28" s="34" t="n"/>
-      <c r="Z28" s="34" t="n"/>
-      <c r="AA28" s="34" t="n"/>
-      <c r="AB28" s="34" t="n"/>
-      <c r="AC28" s="34" t="n"/>
-      <c r="AD28" s="34" t="n"/>
-      <c r="AE28" s="34" t="n"/>
-      <c r="AF28" s="34" t="n"/>
-      <c r="AG28" s="34" t="n"/>
-      <c r="AH28" s="35">
+      <c r="B28" s="38" t="n"/>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="39" t="n"/>
+      <c r="H28" s="39" t="n"/>
+      <c r="I28" s="39" t="n"/>
+      <c r="J28" s="39" t="n"/>
+      <c r="K28" s="39" t="n"/>
+      <c r="L28" s="39" t="n"/>
+      <c r="M28" s="39" t="n"/>
+      <c r="N28" s="39" t="n"/>
+      <c r="O28" s="39" t="n"/>
+      <c r="P28" s="39" t="n"/>
+      <c r="Q28" s="39" t="n"/>
+      <c r="R28" s="39" t="n"/>
+      <c r="S28" s="39" t="n"/>
+      <c r="T28" s="39" t="n"/>
+      <c r="U28" s="39" t="n"/>
+      <c r="V28" s="39" t="n"/>
+      <c r="W28" s="39" t="n"/>
+      <c r="X28" s="39" t="n"/>
+      <c r="Y28" s="39" t="n"/>
+      <c r="Z28" s="39" t="n"/>
+      <c r="AA28" s="39" t="n"/>
+      <c r="AB28" s="39" t="n"/>
+      <c r="AC28" s="39" t="n"/>
+      <c r="AD28" s="39" t="n"/>
+      <c r="AE28" s="39" t="n"/>
+      <c r="AF28" s="39" t="n"/>
+      <c r="AG28" s="39" t="n"/>
+      <c r="AH28" s="40">
         <f>COUNTIF(C28:AG28,"A")</f>
         <v/>
       </c>
-      <c r="AI28" s="35">
+      <c r="AI28" s="40">
         <f>COUNTIF(C28:AG28,"F")</f>
         <v/>
       </c>
-      <c r="AJ28" s="35">
+      <c r="AJ28" s="40">
         <f>COUNTIF(C28:AG28,"R")</f>
         <v/>
       </c>
-      <c r="AK28" s="35">
+      <c r="AK28" s="40">
         <f>COUNTIF(C28:AG28,"V")</f>
         <v/>
       </c>
-      <c r="AL28" s="35">
+      <c r="AL28" s="40">
         <f>COUNTIF(C28:AG28,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="33" t="n">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="37" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="34" t="n"/>
-      <c r="D29" s="34" t="n"/>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="34" t="n"/>
-      <c r="G29" s="34" t="n"/>
-      <c r="H29" s="34" t="n"/>
-      <c r="I29" s="34" t="n"/>
-      <c r="J29" s="34" t="n"/>
-      <c r="K29" s="34" t="n"/>
-      <c r="L29" s="34" t="n"/>
-      <c r="M29" s="34" t="n"/>
-      <c r="N29" s="34" t="n"/>
-      <c r="O29" s="34" t="n"/>
-      <c r="P29" s="34" t="n"/>
-      <c r="Q29" s="34" t="n"/>
-      <c r="R29" s="34" t="n"/>
-      <c r="S29" s="34" t="n"/>
-      <c r="T29" s="34" t="n"/>
-      <c r="U29" s="34" t="n"/>
-      <c r="V29" s="34" t="n"/>
-      <c r="W29" s="34" t="n"/>
-      <c r="X29" s="34" t="n"/>
-      <c r="Y29" s="34" t="n"/>
-      <c r="Z29" s="34" t="n"/>
-      <c r="AA29" s="34" t="n"/>
-      <c r="AB29" s="34" t="n"/>
-      <c r="AC29" s="34" t="n"/>
-      <c r="AD29" s="34" t="n"/>
-      <c r="AE29" s="34" t="n"/>
-      <c r="AF29" s="34" t="n"/>
-      <c r="AG29" s="34" t="n"/>
-      <c r="AH29" s="35">
+      <c r="B29" s="38" t="n"/>
+      <c r="C29" s="39" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="39" t="n"/>
+      <c r="H29" s="39" t="n"/>
+      <c r="I29" s="39" t="n"/>
+      <c r="J29" s="39" t="n"/>
+      <c r="K29" s="39" t="n"/>
+      <c r="L29" s="39" t="n"/>
+      <c r="M29" s="39" t="n"/>
+      <c r="N29" s="39" t="n"/>
+      <c r="O29" s="39" t="n"/>
+      <c r="P29" s="39" t="n"/>
+      <c r="Q29" s="39" t="n"/>
+      <c r="R29" s="39" t="n"/>
+      <c r="S29" s="39" t="n"/>
+      <c r="T29" s="39" t="n"/>
+      <c r="U29" s="39" t="n"/>
+      <c r="V29" s="39" t="n"/>
+      <c r="W29" s="39" t="n"/>
+      <c r="X29" s="39" t="n"/>
+      <c r="Y29" s="39" t="n"/>
+      <c r="Z29" s="39" t="n"/>
+      <c r="AA29" s="39" t="n"/>
+      <c r="AB29" s="39" t="n"/>
+      <c r="AC29" s="39" t="n"/>
+      <c r="AD29" s="39" t="n"/>
+      <c r="AE29" s="39" t="n"/>
+      <c r="AF29" s="39" t="n"/>
+      <c r="AG29" s="39" t="n"/>
+      <c r="AH29" s="40">
         <f>COUNTIF(C29:AG29,"A")</f>
         <v/>
       </c>
-      <c r="AI29" s="35">
+      <c r="AI29" s="40">
         <f>COUNTIF(C29:AG29,"F")</f>
         <v/>
       </c>
-      <c r="AJ29" s="35">
+      <c r="AJ29" s="40">
         <f>COUNTIF(C29:AG29,"R")</f>
         <v/>
       </c>
-      <c r="AK29" s="35">
+      <c r="AK29" s="40">
         <f>COUNTIF(C29:AG29,"V")</f>
         <v/>
       </c>
-      <c r="AL29" s="35">
+      <c r="AL29" s="40">
         <f>COUNTIF(C29:AG29,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="33" t="n">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="37" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="34" t="n"/>
-      <c r="D30" s="34" t="n"/>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="34" t="n"/>
-      <c r="G30" s="34" t="n"/>
-      <c r="H30" s="34" t="n"/>
-      <c r="I30" s="34" t="n"/>
-      <c r="J30" s="34" t="n"/>
-      <c r="K30" s="34" t="n"/>
-      <c r="L30" s="34" t="n"/>
-      <c r="M30" s="34" t="n"/>
-      <c r="N30" s="34" t="n"/>
-      <c r="O30" s="34" t="n"/>
-      <c r="P30" s="34" t="n"/>
-      <c r="Q30" s="34" t="n"/>
-      <c r="R30" s="34" t="n"/>
-      <c r="S30" s="34" t="n"/>
-      <c r="T30" s="34" t="n"/>
-      <c r="U30" s="34" t="n"/>
-      <c r="V30" s="34" t="n"/>
-      <c r="W30" s="34" t="n"/>
-      <c r="X30" s="34" t="n"/>
-      <c r="Y30" s="34" t="n"/>
-      <c r="Z30" s="34" t="n"/>
-      <c r="AA30" s="34" t="n"/>
-      <c r="AB30" s="34" t="n"/>
-      <c r="AC30" s="34" t="n"/>
-      <c r="AD30" s="34" t="n"/>
-      <c r="AE30" s="34" t="n"/>
-      <c r="AF30" s="34" t="n"/>
-      <c r="AG30" s="34" t="n"/>
-      <c r="AH30" s="35">
+      <c r="B30" s="38" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="39" t="n"/>
+      <c r="H30" s="39" t="n"/>
+      <c r="I30" s="39" t="n"/>
+      <c r="J30" s="39" t="n"/>
+      <c r="K30" s="39" t="n"/>
+      <c r="L30" s="39" t="n"/>
+      <c r="M30" s="39" t="n"/>
+      <c r="N30" s="39" t="n"/>
+      <c r="O30" s="39" t="n"/>
+      <c r="P30" s="39" t="n"/>
+      <c r="Q30" s="39" t="n"/>
+      <c r="R30" s="39" t="n"/>
+      <c r="S30" s="39" t="n"/>
+      <c r="T30" s="39" t="n"/>
+      <c r="U30" s="39" t="n"/>
+      <c r="V30" s="39" t="n"/>
+      <c r="W30" s="39" t="n"/>
+      <c r="X30" s="39" t="n"/>
+      <c r="Y30" s="39" t="n"/>
+      <c r="Z30" s="39" t="n"/>
+      <c r="AA30" s="39" t="n"/>
+      <c r="AB30" s="39" t="n"/>
+      <c r="AC30" s="39" t="n"/>
+      <c r="AD30" s="39" t="n"/>
+      <c r="AE30" s="39" t="n"/>
+      <c r="AF30" s="39" t="n"/>
+      <c r="AG30" s="39" t="n"/>
+      <c r="AH30" s="40">
         <f>COUNTIF(C30:AG30,"A")</f>
         <v/>
       </c>
-      <c r="AI30" s="35">
+      <c r="AI30" s="40">
         <f>COUNTIF(C30:AG30,"F")</f>
         <v/>
       </c>
-      <c r="AJ30" s="35">
+      <c r="AJ30" s="40">
         <f>COUNTIF(C30:AG30,"R")</f>
         <v/>
       </c>
-      <c r="AK30" s="35">
+      <c r="AK30" s="40">
         <f>COUNTIF(C30:AG30,"V")</f>
         <v/>
       </c>
-      <c r="AL30" s="35">
+      <c r="AL30" s="40">
         <f>COUNTIF(C30:AG30,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="33" t="n">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="37" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="34" t="n"/>
-      <c r="D31" s="34" t="n"/>
-      <c r="E31" s="34" t="n"/>
-      <c r="F31" s="34" t="n"/>
-      <c r="G31" s="34" t="n"/>
-      <c r="H31" s="34" t="n"/>
-      <c r="I31" s="34" t="n"/>
-      <c r="J31" s="34" t="n"/>
-      <c r="K31" s="34" t="n"/>
-      <c r="L31" s="34" t="n"/>
-      <c r="M31" s="34" t="n"/>
-      <c r="N31" s="34" t="n"/>
-      <c r="O31" s="34" t="n"/>
-      <c r="P31" s="34" t="n"/>
-      <c r="Q31" s="34" t="n"/>
-      <c r="R31" s="34" t="n"/>
-      <c r="S31" s="34" t="n"/>
-      <c r="T31" s="34" t="n"/>
-      <c r="U31" s="34" t="n"/>
-      <c r="V31" s="34" t="n"/>
-      <c r="W31" s="34" t="n"/>
-      <c r="X31" s="34" t="n"/>
-      <c r="Y31" s="34" t="n"/>
-      <c r="Z31" s="34" t="n"/>
-      <c r="AA31" s="34" t="n"/>
-      <c r="AB31" s="34" t="n"/>
-      <c r="AC31" s="34" t="n"/>
-      <c r="AD31" s="34" t="n"/>
-      <c r="AE31" s="34" t="n"/>
-      <c r="AF31" s="34" t="n"/>
-      <c r="AG31" s="34" t="n"/>
-      <c r="AH31" s="35">
+      <c r="B31" s="38" t="n"/>
+      <c r="C31" s="39" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="39" t="n"/>
+      <c r="H31" s="39" t="n"/>
+      <c r="I31" s="39" t="n"/>
+      <c r="J31" s="39" t="n"/>
+      <c r="K31" s="39" t="n"/>
+      <c r="L31" s="39" t="n"/>
+      <c r="M31" s="39" t="n"/>
+      <c r="N31" s="39" t="n"/>
+      <c r="O31" s="39" t="n"/>
+      <c r="P31" s="39" t="n"/>
+      <c r="Q31" s="39" t="n"/>
+      <c r="R31" s="39" t="n"/>
+      <c r="S31" s="39" t="n"/>
+      <c r="T31" s="39" t="n"/>
+      <c r="U31" s="39" t="n"/>
+      <c r="V31" s="39" t="n"/>
+      <c r="W31" s="39" t="n"/>
+      <c r="X31" s="39" t="n"/>
+      <c r="Y31" s="39" t="n"/>
+      <c r="Z31" s="39" t="n"/>
+      <c r="AA31" s="39" t="n"/>
+      <c r="AB31" s="39" t="n"/>
+      <c r="AC31" s="39" t="n"/>
+      <c r="AD31" s="39" t="n"/>
+      <c r="AE31" s="39" t="n"/>
+      <c r="AF31" s="39" t="n"/>
+      <c r="AG31" s="39" t="n"/>
+      <c r="AH31" s="40">
         <f>COUNTIF(C31:AG31,"A")</f>
         <v/>
       </c>
-      <c r="AI31" s="35">
+      <c r="AI31" s="40">
         <f>COUNTIF(C31:AG31,"F")</f>
         <v/>
       </c>
-      <c r="AJ31" s="35">
+      <c r="AJ31" s="40">
         <f>COUNTIF(C31:AG31,"R")</f>
         <v/>
       </c>
-      <c r="AK31" s="35">
+      <c r="AK31" s="40">
         <f>COUNTIF(C31:AG31,"V")</f>
         <v/>
       </c>
-      <c r="AL31" s="35">
+      <c r="AL31" s="40">
         <f>COUNTIF(C31:AG31,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="33" t="n">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="37" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="34" t="n"/>
-      <c r="D32" s="34" t="n"/>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="34" t="n"/>
-      <c r="G32" s="34" t="n"/>
-      <c r="H32" s="34" t="n"/>
-      <c r="I32" s="34" t="n"/>
-      <c r="J32" s="34" t="n"/>
-      <c r="K32" s="34" t="n"/>
-      <c r="L32" s="34" t="n"/>
-      <c r="M32" s="34" t="n"/>
-      <c r="N32" s="34" t="n"/>
-      <c r="O32" s="34" t="n"/>
-      <c r="P32" s="34" t="n"/>
-      <c r="Q32" s="34" t="n"/>
-      <c r="R32" s="34" t="n"/>
-      <c r="S32" s="34" t="n"/>
-      <c r="T32" s="34" t="n"/>
-      <c r="U32" s="34" t="n"/>
-      <c r="V32" s="34" t="n"/>
-      <c r="W32" s="34" t="n"/>
-      <c r="X32" s="34" t="n"/>
-      <c r="Y32" s="34" t="n"/>
-      <c r="Z32" s="34" t="n"/>
-      <c r="AA32" s="34" t="n"/>
-      <c r="AB32" s="34" t="n"/>
-      <c r="AC32" s="34" t="n"/>
-      <c r="AD32" s="34" t="n"/>
-      <c r="AE32" s="34" t="n"/>
-      <c r="AF32" s="34" t="n"/>
-      <c r="AG32" s="34" t="n"/>
-      <c r="AH32" s="35">
+      <c r="B32" s="38" t="n"/>
+      <c r="C32" s="39" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="39" t="n"/>
+      <c r="G32" s="39" t="n"/>
+      <c r="H32" s="39" t="n"/>
+      <c r="I32" s="39" t="n"/>
+      <c r="J32" s="39" t="n"/>
+      <c r="K32" s="39" t="n"/>
+      <c r="L32" s="39" t="n"/>
+      <c r="M32" s="39" t="n"/>
+      <c r="N32" s="39" t="n"/>
+      <c r="O32" s="39" t="n"/>
+      <c r="P32" s="39" t="n"/>
+      <c r="Q32" s="39" t="n"/>
+      <c r="R32" s="39" t="n"/>
+      <c r="S32" s="39" t="n"/>
+      <c r="T32" s="39" t="n"/>
+      <c r="U32" s="39" t="n"/>
+      <c r="V32" s="39" t="n"/>
+      <c r="W32" s="39" t="n"/>
+      <c r="X32" s="39" t="n"/>
+      <c r="Y32" s="39" t="n"/>
+      <c r="Z32" s="39" t="n"/>
+      <c r="AA32" s="39" t="n"/>
+      <c r="AB32" s="39" t="n"/>
+      <c r="AC32" s="39" t="n"/>
+      <c r="AD32" s="39" t="n"/>
+      <c r="AE32" s="39" t="n"/>
+      <c r="AF32" s="39" t="n"/>
+      <c r="AG32" s="39" t="n"/>
+      <c r="AH32" s="40">
         <f>COUNTIF(C32:AG32,"A")</f>
         <v/>
       </c>
-      <c r="AI32" s="35">
+      <c r="AI32" s="40">
         <f>COUNTIF(C32:AG32,"F")</f>
         <v/>
       </c>
-      <c r="AJ32" s="35">
+      <c r="AJ32" s="40">
         <f>COUNTIF(C32:AG32,"R")</f>
         <v/>
       </c>
-      <c r="AK32" s="35">
+      <c r="AK32" s="40">
         <f>COUNTIF(C32:AG32,"V")</f>
         <v/>
       </c>
-      <c r="AL32" s="35">
+      <c r="AL32" s="40">
         <f>COUNTIF(C32:AG32,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="33" t="n">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="37" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="34" t="n"/>
-      <c r="D33" s="34" t="n"/>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="34" t="n"/>
-      <c r="G33" s="34" t="n"/>
-      <c r="H33" s="34" t="n"/>
-      <c r="I33" s="34" t="n"/>
-      <c r="J33" s="34" t="n"/>
-      <c r="K33" s="34" t="n"/>
-      <c r="L33" s="34" t="n"/>
-      <c r="M33" s="34" t="n"/>
-      <c r="N33" s="34" t="n"/>
-      <c r="O33" s="34" t="n"/>
-      <c r="P33" s="34" t="n"/>
-      <c r="Q33" s="34" t="n"/>
-      <c r="R33" s="34" t="n"/>
-      <c r="S33" s="34" t="n"/>
-      <c r="T33" s="34" t="n"/>
-      <c r="U33" s="34" t="n"/>
-      <c r="V33" s="34" t="n"/>
-      <c r="W33" s="34" t="n"/>
-      <c r="X33" s="34" t="n"/>
-      <c r="Y33" s="34" t="n"/>
-      <c r="Z33" s="34" t="n"/>
-      <c r="AA33" s="34" t="n"/>
-      <c r="AB33" s="34" t="n"/>
-      <c r="AC33" s="34" t="n"/>
-      <c r="AD33" s="34" t="n"/>
-      <c r="AE33" s="34" t="n"/>
-      <c r="AF33" s="34" t="n"/>
-      <c r="AG33" s="34" t="n"/>
-      <c r="AH33" s="35">
+      <c r="B33" s="38" t="n"/>
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="39" t="n"/>
+      <c r="H33" s="39" t="n"/>
+      <c r="I33" s="39" t="n"/>
+      <c r="J33" s="39" t="n"/>
+      <c r="K33" s="39" t="n"/>
+      <c r="L33" s="39" t="n"/>
+      <c r="M33" s="39" t="n"/>
+      <c r="N33" s="39" t="n"/>
+      <c r="O33" s="39" t="n"/>
+      <c r="P33" s="39" t="n"/>
+      <c r="Q33" s="39" t="n"/>
+      <c r="R33" s="39" t="n"/>
+      <c r="S33" s="39" t="n"/>
+      <c r="T33" s="39" t="n"/>
+      <c r="U33" s="39" t="n"/>
+      <c r="V33" s="39" t="n"/>
+      <c r="W33" s="39" t="n"/>
+      <c r="X33" s="39" t="n"/>
+      <c r="Y33" s="39" t="n"/>
+      <c r="Z33" s="39" t="n"/>
+      <c r="AA33" s="39" t="n"/>
+      <c r="AB33" s="39" t="n"/>
+      <c r="AC33" s="39" t="n"/>
+      <c r="AD33" s="39" t="n"/>
+      <c r="AE33" s="39" t="n"/>
+      <c r="AF33" s="39" t="n"/>
+      <c r="AG33" s="39" t="n"/>
+      <c r="AH33" s="40">
         <f>COUNTIF(C33:AG33,"A")</f>
         <v/>
       </c>
-      <c r="AI33" s="35">
+      <c r="AI33" s="40">
         <f>COUNTIF(C33:AG33,"F")</f>
         <v/>
       </c>
-      <c r="AJ33" s="35">
+      <c r="AJ33" s="40">
         <f>COUNTIF(C33:AG33,"R")</f>
         <v/>
       </c>
-      <c r="AK33" s="35">
+      <c r="AK33" s="40">
         <f>COUNTIF(C33:AG33,"V")</f>
         <v/>
       </c>
-      <c r="AL33" s="35">
+      <c r="AL33" s="40">
         <f>COUNTIF(C33:AG33,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="33" t="n">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="37" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="34" t="n"/>
-      <c r="D34" s="34" t="n"/>
-      <c r="E34" s="34" t="n"/>
-      <c r="F34" s="34" t="n"/>
-      <c r="G34" s="34" t="n"/>
-      <c r="H34" s="34" t="n"/>
-      <c r="I34" s="34" t="n"/>
-      <c r="J34" s="34" t="n"/>
-      <c r="K34" s="34" t="n"/>
-      <c r="L34" s="34" t="n"/>
-      <c r="M34" s="34" t="n"/>
-      <c r="N34" s="34" t="n"/>
-      <c r="O34" s="34" t="n"/>
-      <c r="P34" s="34" t="n"/>
-      <c r="Q34" s="34" t="n"/>
-      <c r="R34" s="34" t="n"/>
-      <c r="S34" s="34" t="n"/>
-      <c r="T34" s="34" t="n"/>
-      <c r="U34" s="34" t="n"/>
-      <c r="V34" s="34" t="n"/>
-      <c r="W34" s="34" t="n"/>
-      <c r="X34" s="34" t="n"/>
-      <c r="Y34" s="34" t="n"/>
-      <c r="Z34" s="34" t="n"/>
-      <c r="AA34" s="34" t="n"/>
-      <c r="AB34" s="34" t="n"/>
-      <c r="AC34" s="34" t="n"/>
-      <c r="AD34" s="34" t="n"/>
-      <c r="AE34" s="34" t="n"/>
-      <c r="AF34" s="34" t="n"/>
-      <c r="AG34" s="34" t="n"/>
-      <c r="AH34" s="35">
+      <c r="B34" s="38" t="n"/>
+      <c r="C34" s="39" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="39" t="n"/>
+      <c r="H34" s="39" t="n"/>
+      <c r="I34" s="39" t="n"/>
+      <c r="J34" s="39" t="n"/>
+      <c r="K34" s="39" t="n"/>
+      <c r="L34" s="39" t="n"/>
+      <c r="M34" s="39" t="n"/>
+      <c r="N34" s="39" t="n"/>
+      <c r="O34" s="39" t="n"/>
+      <c r="P34" s="39" t="n"/>
+      <c r="Q34" s="39" t="n"/>
+      <c r="R34" s="39" t="n"/>
+      <c r="S34" s="39" t="n"/>
+      <c r="T34" s="39" t="n"/>
+      <c r="U34" s="39" t="n"/>
+      <c r="V34" s="39" t="n"/>
+      <c r="W34" s="39" t="n"/>
+      <c r="X34" s="39" t="n"/>
+      <c r="Y34" s="39" t="n"/>
+      <c r="Z34" s="39" t="n"/>
+      <c r="AA34" s="39" t="n"/>
+      <c r="AB34" s="39" t="n"/>
+      <c r="AC34" s="39" t="n"/>
+      <c r="AD34" s="39" t="n"/>
+      <c r="AE34" s="39" t="n"/>
+      <c r="AF34" s="39" t="n"/>
+      <c r="AG34" s="39" t="n"/>
+      <c r="AH34" s="40">
         <f>COUNTIF(C34:AG34,"A")</f>
         <v/>
       </c>
-      <c r="AI34" s="35">
+      <c r="AI34" s="40">
         <f>COUNTIF(C34:AG34,"F")</f>
         <v/>
       </c>
-      <c r="AJ34" s="35">
+      <c r="AJ34" s="40">
         <f>COUNTIF(C34:AG34,"R")</f>
         <v/>
       </c>
-      <c r="AK34" s="35">
+      <c r="AK34" s="40">
         <f>COUNTIF(C34:AG34,"V")</f>
         <v/>
       </c>
-      <c r="AL34" s="35">
+      <c r="AL34" s="40">
         <f>COUNTIF(C34:AG34,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="33" t="n">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="37" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="34" t="n"/>
-      <c r="G35" s="34" t="n"/>
-      <c r="H35" s="34" t="n"/>
-      <c r="I35" s="34" t="n"/>
-      <c r="J35" s="34" t="n"/>
-      <c r="K35" s="34" t="n"/>
-      <c r="L35" s="34" t="n"/>
-      <c r="M35" s="34" t="n"/>
-      <c r="N35" s="34" t="n"/>
-      <c r="O35" s="34" t="n"/>
-      <c r="P35" s="34" t="n"/>
-      <c r="Q35" s="34" t="n"/>
-      <c r="R35" s="34" t="n"/>
-      <c r="S35" s="34" t="n"/>
-      <c r="T35" s="34" t="n"/>
-      <c r="U35" s="34" t="n"/>
-      <c r="V35" s="34" t="n"/>
-      <c r="W35" s="34" t="n"/>
-      <c r="X35" s="34" t="n"/>
-      <c r="Y35" s="34" t="n"/>
-      <c r="Z35" s="34" t="n"/>
-      <c r="AA35" s="34" t="n"/>
-      <c r="AB35" s="34" t="n"/>
-      <c r="AC35" s="34" t="n"/>
-      <c r="AD35" s="34" t="n"/>
-      <c r="AE35" s="34" t="n"/>
-      <c r="AF35" s="34" t="n"/>
-      <c r="AG35" s="34" t="n"/>
-      <c r="AH35" s="35">
+      <c r="B35" s="38" t="n"/>
+      <c r="C35" s="39" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="39" t="n"/>
+      <c r="H35" s="39" t="n"/>
+      <c r="I35" s="39" t="n"/>
+      <c r="J35" s="39" t="n"/>
+      <c r="K35" s="39" t="n"/>
+      <c r="L35" s="39" t="n"/>
+      <c r="M35" s="39" t="n"/>
+      <c r="N35" s="39" t="n"/>
+      <c r="O35" s="39" t="n"/>
+      <c r="P35" s="39" t="n"/>
+      <c r="Q35" s="39" t="n"/>
+      <c r="R35" s="39" t="n"/>
+      <c r="S35" s="39" t="n"/>
+      <c r="T35" s="39" t="n"/>
+      <c r="U35" s="39" t="n"/>
+      <c r="V35" s="39" t="n"/>
+      <c r="W35" s="39" t="n"/>
+      <c r="X35" s="39" t="n"/>
+      <c r="Y35" s="39" t="n"/>
+      <c r="Z35" s="39" t="n"/>
+      <c r="AA35" s="39" t="n"/>
+      <c r="AB35" s="39" t="n"/>
+      <c r="AC35" s="39" t="n"/>
+      <c r="AD35" s="39" t="n"/>
+      <c r="AE35" s="39" t="n"/>
+      <c r="AF35" s="39" t="n"/>
+      <c r="AG35" s="39" t="n"/>
+      <c r="AH35" s="40">
         <f>COUNTIF(C35:AG35,"A")</f>
         <v/>
       </c>
-      <c r="AI35" s="35">
+      <c r="AI35" s="40">
         <f>COUNTIF(C35:AG35,"F")</f>
         <v/>
       </c>
-      <c r="AJ35" s="35">
+      <c r="AJ35" s="40">
         <f>COUNTIF(C35:AG35,"R")</f>
         <v/>
       </c>
-      <c r="AK35" s="35">
+      <c r="AK35" s="40">
         <f>COUNTIF(C35:AG35,"V")</f>
         <v/>
       </c>
-      <c r="AL35" s="35">
+      <c r="AL35" s="40">
         <f>COUNTIF(C35:AG35,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="33" t="n">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="37" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="34" t="n"/>
-      <c r="D36" s="34" t="n"/>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="34" t="n"/>
-      <c r="G36" s="34" t="n"/>
-      <c r="H36" s="34" t="n"/>
-      <c r="I36" s="34" t="n"/>
-      <c r="J36" s="34" t="n"/>
-      <c r="K36" s="34" t="n"/>
-      <c r="L36" s="34" t="n"/>
-      <c r="M36" s="34" t="n"/>
-      <c r="N36" s="34" t="n"/>
-      <c r="O36" s="34" t="n"/>
-      <c r="P36" s="34" t="n"/>
-      <c r="Q36" s="34" t="n"/>
-      <c r="R36" s="34" t="n"/>
-      <c r="S36" s="34" t="n"/>
-      <c r="T36" s="34" t="n"/>
-      <c r="U36" s="34" t="n"/>
-      <c r="V36" s="34" t="n"/>
-      <c r="W36" s="34" t="n"/>
-      <c r="X36" s="34" t="n"/>
-      <c r="Y36" s="34" t="n"/>
-      <c r="Z36" s="34" t="n"/>
-      <c r="AA36" s="34" t="n"/>
-      <c r="AB36" s="34" t="n"/>
-      <c r="AC36" s="34" t="n"/>
-      <c r="AD36" s="34" t="n"/>
-      <c r="AE36" s="34" t="n"/>
-      <c r="AF36" s="34" t="n"/>
-      <c r="AG36" s="34" t="n"/>
-      <c r="AH36" s="35">
+      <c r="B36" s="38" t="n"/>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="39" t="n"/>
+      <c r="H36" s="39" t="n"/>
+      <c r="I36" s="39" t="n"/>
+      <c r="J36" s="39" t="n"/>
+      <c r="K36" s="39" t="n"/>
+      <c r="L36" s="39" t="n"/>
+      <c r="M36" s="39" t="n"/>
+      <c r="N36" s="39" t="n"/>
+      <c r="O36" s="39" t="n"/>
+      <c r="P36" s="39" t="n"/>
+      <c r="Q36" s="39" t="n"/>
+      <c r="R36" s="39" t="n"/>
+      <c r="S36" s="39" t="n"/>
+      <c r="T36" s="39" t="n"/>
+      <c r="U36" s="39" t="n"/>
+      <c r="V36" s="39" t="n"/>
+      <c r="W36" s="39" t="n"/>
+      <c r="X36" s="39" t="n"/>
+      <c r="Y36" s="39" t="n"/>
+      <c r="Z36" s="39" t="n"/>
+      <c r="AA36" s="39" t="n"/>
+      <c r="AB36" s="39" t="n"/>
+      <c r="AC36" s="39" t="n"/>
+      <c r="AD36" s="39" t="n"/>
+      <c r="AE36" s="39" t="n"/>
+      <c r="AF36" s="39" t="n"/>
+      <c r="AG36" s="39" t="n"/>
+      <c r="AH36" s="40">
         <f>COUNTIF(C36:AG36,"A")</f>
         <v/>
       </c>
-      <c r="AI36" s="35">
+      <c r="AI36" s="40">
         <f>COUNTIF(C36:AG36,"F")</f>
         <v/>
       </c>
-      <c r="AJ36" s="35">
+      <c r="AJ36" s="40">
         <f>COUNTIF(C36:AG36,"R")</f>
         <v/>
       </c>
-      <c r="AK36" s="35">
+      <c r="AK36" s="40">
         <f>COUNTIF(C36:AG36,"V")</f>
         <v/>
       </c>
-      <c r="AL36" s="35">
+      <c r="AL36" s="40">
         <f>COUNTIF(C36:AG36,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="33" t="n">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="37" t="n">
         <v>31</v>
       </c>
-      <c r="B37" s="17" t="n"/>
-      <c r="C37" s="34" t="n"/>
-      <c r="D37" s="34" t="n"/>
-      <c r="E37" s="34" t="n"/>
-      <c r="F37" s="34" t="n"/>
-      <c r="G37" s="34" t="n"/>
-      <c r="H37" s="34" t="n"/>
-      <c r="I37" s="34" t="n"/>
-      <c r="J37" s="34" t="n"/>
-      <c r="K37" s="34" t="n"/>
-      <c r="L37" s="34" t="n"/>
-      <c r="M37" s="34" t="n"/>
-      <c r="N37" s="34" t="n"/>
-      <c r="O37" s="34" t="n"/>
-      <c r="P37" s="34" t="n"/>
-      <c r="Q37" s="34" t="n"/>
-      <c r="R37" s="34" t="n"/>
-      <c r="S37" s="34" t="n"/>
-      <c r="T37" s="34" t="n"/>
-      <c r="U37" s="34" t="n"/>
-      <c r="V37" s="34" t="n"/>
-      <c r="W37" s="34" t="n"/>
-      <c r="X37" s="34" t="n"/>
-      <c r="Y37" s="34" t="n"/>
-      <c r="Z37" s="34" t="n"/>
-      <c r="AA37" s="34" t="n"/>
-      <c r="AB37" s="34" t="n"/>
-      <c r="AC37" s="34" t="n"/>
-      <c r="AD37" s="34" t="n"/>
-      <c r="AE37" s="34" t="n"/>
-      <c r="AF37" s="34" t="n"/>
-      <c r="AG37" s="34" t="n"/>
-      <c r="AH37" s="35">
+      <c r="B37" s="38" t="n"/>
+      <c r="C37" s="39" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="39" t="n"/>
+      <c r="H37" s="39" t="n"/>
+      <c r="I37" s="39" t="n"/>
+      <c r="J37" s="39" t="n"/>
+      <c r="K37" s="39" t="n"/>
+      <c r="L37" s="39" t="n"/>
+      <c r="M37" s="39" t="n"/>
+      <c r="N37" s="39" t="n"/>
+      <c r="O37" s="39" t="n"/>
+      <c r="P37" s="39" t="n"/>
+      <c r="Q37" s="39" t="n"/>
+      <c r="R37" s="39" t="n"/>
+      <c r="S37" s="39" t="n"/>
+      <c r="T37" s="39" t="n"/>
+      <c r="U37" s="39" t="n"/>
+      <c r="V37" s="39" t="n"/>
+      <c r="W37" s="39" t="n"/>
+      <c r="X37" s="39" t="n"/>
+      <c r="Y37" s="39" t="n"/>
+      <c r="Z37" s="39" t="n"/>
+      <c r="AA37" s="39" t="n"/>
+      <c r="AB37" s="39" t="n"/>
+      <c r="AC37" s="39" t="n"/>
+      <c r="AD37" s="39" t="n"/>
+      <c r="AE37" s="39" t="n"/>
+      <c r="AF37" s="39" t="n"/>
+      <c r="AG37" s="39" t="n"/>
+      <c r="AH37" s="40">
         <f>COUNTIF(C37:AG37,"A")</f>
         <v/>
       </c>
-      <c r="AI37" s="35">
+      <c r="AI37" s="40">
         <f>COUNTIF(C37:AG37,"F")</f>
         <v/>
       </c>
-      <c r="AJ37" s="35">
+      <c r="AJ37" s="40">
         <f>COUNTIF(C37:AG37,"R")</f>
         <v/>
       </c>
-      <c r="AK37" s="35">
+      <c r="AK37" s="40">
         <f>COUNTIF(C37:AG37,"V")</f>
         <v/>
       </c>
-      <c r="AL37" s="35">
+      <c r="AL37" s="40">
         <f>COUNTIF(C37:AG37,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="33" t="n">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="37" t="n">
         <v>32</v>
       </c>
-      <c r="B38" s="17" t="n"/>
-      <c r="C38" s="34" t="n"/>
-      <c r="D38" s="34" t="n"/>
-      <c r="E38" s="34" t="n"/>
-      <c r="F38" s="34" t="n"/>
-      <c r="G38" s="34" t="n"/>
-      <c r="H38" s="34" t="n"/>
-      <c r="I38" s="34" t="n"/>
-      <c r="J38" s="34" t="n"/>
-      <c r="K38" s="34" t="n"/>
-      <c r="L38" s="34" t="n"/>
-      <c r="M38" s="34" t="n"/>
-      <c r="N38" s="34" t="n"/>
-      <c r="O38" s="34" t="n"/>
-      <c r="P38" s="34" t="n"/>
-      <c r="Q38" s="34" t="n"/>
-      <c r="R38" s="34" t="n"/>
-      <c r="S38" s="34" t="n"/>
-      <c r="T38" s="34" t="n"/>
-      <c r="U38" s="34" t="n"/>
-      <c r="V38" s="34" t="n"/>
-      <c r="W38" s="34" t="n"/>
-      <c r="X38" s="34" t="n"/>
-      <c r="Y38" s="34" t="n"/>
-      <c r="Z38" s="34" t="n"/>
-      <c r="AA38" s="34" t="n"/>
-      <c r="AB38" s="34" t="n"/>
-      <c r="AC38" s="34" t="n"/>
-      <c r="AD38" s="34" t="n"/>
-      <c r="AE38" s="34" t="n"/>
-      <c r="AF38" s="34" t="n"/>
-      <c r="AG38" s="34" t="n"/>
-      <c r="AH38" s="35">
+      <c r="B38" s="38" t="n"/>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+      <c r="G38" s="39" t="n"/>
+      <c r="H38" s="39" t="n"/>
+      <c r="I38" s="39" t="n"/>
+      <c r="J38" s="39" t="n"/>
+      <c r="K38" s="39" t="n"/>
+      <c r="L38" s="39" t="n"/>
+      <c r="M38" s="39" t="n"/>
+      <c r="N38" s="39" t="n"/>
+      <c r="O38" s="39" t="n"/>
+      <c r="P38" s="39" t="n"/>
+      <c r="Q38" s="39" t="n"/>
+      <c r="R38" s="39" t="n"/>
+      <c r="S38" s="39" t="n"/>
+      <c r="T38" s="39" t="n"/>
+      <c r="U38" s="39" t="n"/>
+      <c r="V38" s="39" t="n"/>
+      <c r="W38" s="39" t="n"/>
+      <c r="X38" s="39" t="n"/>
+      <c r="Y38" s="39" t="n"/>
+      <c r="Z38" s="39" t="n"/>
+      <c r="AA38" s="39" t="n"/>
+      <c r="AB38" s="39" t="n"/>
+      <c r="AC38" s="39" t="n"/>
+      <c r="AD38" s="39" t="n"/>
+      <c r="AE38" s="39" t="n"/>
+      <c r="AF38" s="39" t="n"/>
+      <c r="AG38" s="39" t="n"/>
+      <c r="AH38" s="40">
         <f>COUNTIF(C38:AG38,"A")</f>
         <v/>
       </c>
-      <c r="AI38" s="35">
+      <c r="AI38" s="40">
         <f>COUNTIF(C38:AG38,"F")</f>
         <v/>
       </c>
-      <c r="AJ38" s="35">
+      <c r="AJ38" s="40">
         <f>COUNTIF(C38:AG38,"R")</f>
         <v/>
       </c>
-      <c r="AK38" s="35">
+      <c r="AK38" s="40">
         <f>COUNTIF(C38:AG38,"V")</f>
         <v/>
       </c>
-      <c r="AL38" s="35">
+      <c r="AL38" s="40">
         <f>COUNTIF(C38:AG38,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="33" t="n">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="37" t="n">
         <v>33</v>
       </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="34" t="n"/>
-      <c r="D39" s="34" t="n"/>
-      <c r="E39" s="34" t="n"/>
-      <c r="F39" s="34" t="n"/>
-      <c r="G39" s="34" t="n"/>
-      <c r="H39" s="34" t="n"/>
-      <c r="I39" s="34" t="n"/>
-      <c r="J39" s="34" t="n"/>
-      <c r="K39" s="34" t="n"/>
-      <c r="L39" s="34" t="n"/>
-      <c r="M39" s="34" t="n"/>
-      <c r="N39" s="34" t="n"/>
-      <c r="O39" s="34" t="n"/>
-      <c r="P39" s="34" t="n"/>
-      <c r="Q39" s="34" t="n"/>
-      <c r="R39" s="34" t="n"/>
-      <c r="S39" s="34" t="n"/>
-      <c r="T39" s="34" t="n"/>
-      <c r="U39" s="34" t="n"/>
-      <c r="V39" s="34" t="n"/>
-      <c r="W39" s="34" t="n"/>
-      <c r="X39" s="34" t="n"/>
-      <c r="Y39" s="34" t="n"/>
-      <c r="Z39" s="34" t="n"/>
-      <c r="AA39" s="34" t="n"/>
-      <c r="AB39" s="34" t="n"/>
-      <c r="AC39" s="34" t="n"/>
-      <c r="AD39" s="34" t="n"/>
-      <c r="AE39" s="34" t="n"/>
-      <c r="AF39" s="34" t="n"/>
-      <c r="AG39" s="34" t="n"/>
-      <c r="AH39" s="35">
+      <c r="B39" s="38" t="n"/>
+      <c r="C39" s="39" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="39" t="n"/>
+      <c r="H39" s="39" t="n"/>
+      <c r="I39" s="39" t="n"/>
+      <c r="J39" s="39" t="n"/>
+      <c r="K39" s="39" t="n"/>
+      <c r="L39" s="39" t="n"/>
+      <c r="M39" s="39" t="n"/>
+      <c r="N39" s="39" t="n"/>
+      <c r="O39" s="39" t="n"/>
+      <c r="P39" s="39" t="n"/>
+      <c r="Q39" s="39" t="n"/>
+      <c r="R39" s="39" t="n"/>
+      <c r="S39" s="39" t="n"/>
+      <c r="T39" s="39" t="n"/>
+      <c r="U39" s="39" t="n"/>
+      <c r="V39" s="39" t="n"/>
+      <c r="W39" s="39" t="n"/>
+      <c r="X39" s="39" t="n"/>
+      <c r="Y39" s="39" t="n"/>
+      <c r="Z39" s="39" t="n"/>
+      <c r="AA39" s="39" t="n"/>
+      <c r="AB39" s="39" t="n"/>
+      <c r="AC39" s="39" t="n"/>
+      <c r="AD39" s="39" t="n"/>
+      <c r="AE39" s="39" t="n"/>
+      <c r="AF39" s="39" t="n"/>
+      <c r="AG39" s="39" t="n"/>
+      <c r="AH39" s="40">
         <f>COUNTIF(C39:AG39,"A")</f>
         <v/>
       </c>
-      <c r="AI39" s="35">
+      <c r="AI39" s="40">
         <f>COUNTIF(C39:AG39,"F")</f>
         <v/>
       </c>
-      <c r="AJ39" s="35">
+      <c r="AJ39" s="40">
         <f>COUNTIF(C39:AG39,"R")</f>
         <v/>
       </c>
-      <c r="AK39" s="35">
+      <c r="AK39" s="40">
         <f>COUNTIF(C39:AG39,"V")</f>
         <v/>
       </c>
-      <c r="AL39" s="35">
+      <c r="AL39" s="40">
         <f>COUNTIF(C39:AG39,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="33" t="n">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="37" t="n">
         <v>34</v>
       </c>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="34" t="n"/>
-      <c r="D40" s="34" t="n"/>
-      <c r="E40" s="34" t="n"/>
-      <c r="F40" s="34" t="n"/>
-      <c r="G40" s="34" t="n"/>
-      <c r="H40" s="34" t="n"/>
-      <c r="I40" s="34" t="n"/>
-      <c r="J40" s="34" t="n"/>
-      <c r="K40" s="34" t="n"/>
-      <c r="L40" s="34" t="n"/>
-      <c r="M40" s="34" t="n"/>
-      <c r="N40" s="34" t="n"/>
-      <c r="O40" s="34" t="n"/>
-      <c r="P40" s="34" t="n"/>
-      <c r="Q40" s="34" t="n"/>
-      <c r="R40" s="34" t="n"/>
-      <c r="S40" s="34" t="n"/>
-      <c r="T40" s="34" t="n"/>
-      <c r="U40" s="34" t="n"/>
-      <c r="V40" s="34" t="n"/>
-      <c r="W40" s="34" t="n"/>
-      <c r="X40" s="34" t="n"/>
-      <c r="Y40" s="34" t="n"/>
-      <c r="Z40" s="34" t="n"/>
-      <c r="AA40" s="34" t="n"/>
-      <c r="AB40" s="34" t="n"/>
-      <c r="AC40" s="34" t="n"/>
-      <c r="AD40" s="34" t="n"/>
-      <c r="AE40" s="34" t="n"/>
-      <c r="AF40" s="34" t="n"/>
-      <c r="AG40" s="34" t="n"/>
-      <c r="AH40" s="35">
+      <c r="B40" s="38" t="n"/>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="39" t="n"/>
+      <c r="H40" s="39" t="n"/>
+      <c r="I40" s="39" t="n"/>
+      <c r="J40" s="39" t="n"/>
+      <c r="K40" s="39" t="n"/>
+      <c r="L40" s="39" t="n"/>
+      <c r="M40" s="39" t="n"/>
+      <c r="N40" s="39" t="n"/>
+      <c r="O40" s="39" t="n"/>
+      <c r="P40" s="39" t="n"/>
+      <c r="Q40" s="39" t="n"/>
+      <c r="R40" s="39" t="n"/>
+      <c r="S40" s="39" t="n"/>
+      <c r="T40" s="39" t="n"/>
+      <c r="U40" s="39" t="n"/>
+      <c r="V40" s="39" t="n"/>
+      <c r="W40" s="39" t="n"/>
+      <c r="X40" s="39" t="n"/>
+      <c r="Y40" s="39" t="n"/>
+      <c r="Z40" s="39" t="n"/>
+      <c r="AA40" s="39" t="n"/>
+      <c r="AB40" s="39" t="n"/>
+      <c r="AC40" s="39" t="n"/>
+      <c r="AD40" s="39" t="n"/>
+      <c r="AE40" s="39" t="n"/>
+      <c r="AF40" s="39" t="n"/>
+      <c r="AG40" s="39" t="n"/>
+      <c r="AH40" s="40">
         <f>COUNTIF(C40:AG40,"A")</f>
         <v/>
       </c>
-      <c r="AI40" s="35">
+      <c r="AI40" s="40">
         <f>COUNTIF(C40:AG40,"F")</f>
         <v/>
       </c>
-      <c r="AJ40" s="35">
+      <c r="AJ40" s="40">
         <f>COUNTIF(C40:AG40,"R")</f>
         <v/>
       </c>
-      <c r="AK40" s="35">
+      <c r="AK40" s="40">
         <f>COUNTIF(C40:AG40,"V")</f>
         <v/>
       </c>
-      <c r="AL40" s="35">
+      <c r="AL40" s="40">
         <f>COUNTIF(C40:AG40,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="33" t="n">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="37" t="n">
         <v>35</v>
       </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="34" t="n"/>
-      <c r="D41" s="34" t="n"/>
-      <c r="E41" s="34" t="n"/>
-      <c r="F41" s="34" t="n"/>
-      <c r="G41" s="34" t="n"/>
-      <c r="H41" s="34" t="n"/>
-      <c r="I41" s="34" t="n"/>
-      <c r="J41" s="34" t="n"/>
-      <c r="K41" s="34" t="n"/>
-      <c r="L41" s="34" t="n"/>
-      <c r="M41" s="34" t="n"/>
-      <c r="N41" s="34" t="n"/>
-      <c r="O41" s="34" t="n"/>
-      <c r="P41" s="34" t="n"/>
-      <c r="Q41" s="34" t="n"/>
-      <c r="R41" s="34" t="n"/>
-      <c r="S41" s="34" t="n"/>
-      <c r="T41" s="34" t="n"/>
-      <c r="U41" s="34" t="n"/>
-      <c r="V41" s="34" t="n"/>
-      <c r="W41" s="34" t="n"/>
-      <c r="X41" s="34" t="n"/>
-      <c r="Y41" s="34" t="n"/>
-      <c r="Z41" s="34" t="n"/>
-      <c r="AA41" s="34" t="n"/>
-      <c r="AB41" s="34" t="n"/>
-      <c r="AC41" s="34" t="n"/>
-      <c r="AD41" s="34" t="n"/>
-      <c r="AE41" s="34" t="n"/>
-      <c r="AF41" s="34" t="n"/>
-      <c r="AG41" s="34" t="n"/>
-      <c r="AH41" s="35">
+      <c r="B41" s="38" t="n"/>
+      <c r="C41" s="39" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="39" t="n"/>
+      <c r="H41" s="39" t="n"/>
+      <c r="I41" s="39" t="n"/>
+      <c r="J41" s="39" t="n"/>
+      <c r="K41" s="39" t="n"/>
+      <c r="L41" s="39" t="n"/>
+      <c r="M41" s="39" t="n"/>
+      <c r="N41" s="39" t="n"/>
+      <c r="O41" s="39" t="n"/>
+      <c r="P41" s="39" t="n"/>
+      <c r="Q41" s="39" t="n"/>
+      <c r="R41" s="39" t="n"/>
+      <c r="S41" s="39" t="n"/>
+      <c r="T41" s="39" t="n"/>
+      <c r="U41" s="39" t="n"/>
+      <c r="V41" s="39" t="n"/>
+      <c r="W41" s="39" t="n"/>
+      <c r="X41" s="39" t="n"/>
+      <c r="Y41" s="39" t="n"/>
+      <c r="Z41" s="39" t="n"/>
+      <c r="AA41" s="39" t="n"/>
+      <c r="AB41" s="39" t="n"/>
+      <c r="AC41" s="39" t="n"/>
+      <c r="AD41" s="39" t="n"/>
+      <c r="AE41" s="39" t="n"/>
+      <c r="AF41" s="39" t="n"/>
+      <c r="AG41" s="39" t="n"/>
+      <c r="AH41" s="40">
         <f>COUNTIF(C41:AG41,"A")</f>
         <v/>
       </c>
-      <c r="AI41" s="35">
+      <c r="AI41" s="40">
         <f>COUNTIF(C41:AG41,"F")</f>
         <v/>
       </c>
-      <c r="AJ41" s="35">
+      <c r="AJ41" s="40">
         <f>COUNTIF(C41:AG41,"R")</f>
         <v/>
       </c>
-      <c r="AK41" s="35">
+      <c r="AK41" s="40">
         <f>COUNTIF(C41:AG41,"V")</f>
         <v/>
       </c>
-      <c r="AL41" s="35">
+      <c r="AL41" s="40">
         <f>COUNTIF(C41:AG41,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="33" t="n">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="37" t="n">
         <v>36</v>
       </c>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="34" t="n"/>
-      <c r="D42" s="34" t="n"/>
-      <c r="E42" s="34" t="n"/>
-      <c r="F42" s="34" t="n"/>
-      <c r="G42" s="34" t="n"/>
-      <c r="H42" s="34" t="n"/>
-      <c r="I42" s="34" t="n"/>
-      <c r="J42" s="34" t="n"/>
-      <c r="K42" s="34" t="n"/>
-      <c r="L42" s="34" t="n"/>
-      <c r="M42" s="34" t="n"/>
-      <c r="N42" s="34" t="n"/>
-      <c r="O42" s="34" t="n"/>
-      <c r="P42" s="34" t="n"/>
-      <c r="Q42" s="34" t="n"/>
-      <c r="R42" s="34" t="n"/>
-      <c r="S42" s="34" t="n"/>
-      <c r="T42" s="34" t="n"/>
-      <c r="U42" s="34" t="n"/>
-      <c r="V42" s="34" t="n"/>
-      <c r="W42" s="34" t="n"/>
-      <c r="X42" s="34" t="n"/>
-      <c r="Y42" s="34" t="n"/>
-      <c r="Z42" s="34" t="n"/>
-      <c r="AA42" s="34" t="n"/>
-      <c r="AB42" s="34" t="n"/>
-      <c r="AC42" s="34" t="n"/>
-      <c r="AD42" s="34" t="n"/>
-      <c r="AE42" s="34" t="n"/>
-      <c r="AF42" s="34" t="n"/>
-      <c r="AG42" s="34" t="n"/>
-      <c r="AH42" s="35">
+      <c r="B42" s="38" t="n"/>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="39" t="n"/>
+      <c r="H42" s="39" t="n"/>
+      <c r="I42" s="39" t="n"/>
+      <c r="J42" s="39" t="n"/>
+      <c r="K42" s="39" t="n"/>
+      <c r="L42" s="39" t="n"/>
+      <c r="M42" s="39" t="n"/>
+      <c r="N42" s="39" t="n"/>
+      <c r="O42" s="39" t="n"/>
+      <c r="P42" s="39" t="n"/>
+      <c r="Q42" s="39" t="n"/>
+      <c r="R42" s="39" t="n"/>
+      <c r="S42" s="39" t="n"/>
+      <c r="T42" s="39" t="n"/>
+      <c r="U42" s="39" t="n"/>
+      <c r="V42" s="39" t="n"/>
+      <c r="W42" s="39" t="n"/>
+      <c r="X42" s="39" t="n"/>
+      <c r="Y42" s="39" t="n"/>
+      <c r="Z42" s="39" t="n"/>
+      <c r="AA42" s="39" t="n"/>
+      <c r="AB42" s="39" t="n"/>
+      <c r="AC42" s="39" t="n"/>
+      <c r="AD42" s="39" t="n"/>
+      <c r="AE42" s="39" t="n"/>
+      <c r="AF42" s="39" t="n"/>
+      <c r="AG42" s="39" t="n"/>
+      <c r="AH42" s="40">
         <f>COUNTIF(C42:AG42,"A")</f>
         <v/>
       </c>
-      <c r="AI42" s="35">
+      <c r="AI42" s="40">
         <f>COUNTIF(C42:AG42,"F")</f>
         <v/>
       </c>
-      <c r="AJ42" s="35">
+      <c r="AJ42" s="40">
         <f>COUNTIF(C42:AG42,"R")</f>
         <v/>
       </c>
-      <c r="AK42" s="35">
+      <c r="AK42" s="40">
         <f>COUNTIF(C42:AG42,"V")</f>
         <v/>
       </c>
-      <c r="AL42" s="35">
+      <c r="AL42" s="40">
         <f>COUNTIF(C42:AG42,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="33" t="n">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="37" t="n">
         <v>37</v>
       </c>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="34" t="n"/>
-      <c r="D43" s="34" t="n"/>
-      <c r="E43" s="34" t="n"/>
-      <c r="F43" s="34" t="n"/>
-      <c r="G43" s="34" t="n"/>
-      <c r="H43" s="34" t="n"/>
-      <c r="I43" s="34" t="n"/>
-      <c r="J43" s="34" t="n"/>
-      <c r="K43" s="34" t="n"/>
-      <c r="L43" s="34" t="n"/>
-      <c r="M43" s="34" t="n"/>
-      <c r="N43" s="34" t="n"/>
-      <c r="O43" s="34" t="n"/>
-      <c r="P43" s="34" t="n"/>
-      <c r="Q43" s="34" t="n"/>
-      <c r="R43" s="34" t="n"/>
-      <c r="S43" s="34" t="n"/>
-      <c r="T43" s="34" t="n"/>
-      <c r="U43" s="34" t="n"/>
-      <c r="V43" s="34" t="n"/>
-      <c r="W43" s="34" t="n"/>
-      <c r="X43" s="34" t="n"/>
-      <c r="Y43" s="34" t="n"/>
-      <c r="Z43" s="34" t="n"/>
-      <c r="AA43" s="34" t="n"/>
-      <c r="AB43" s="34" t="n"/>
-      <c r="AC43" s="34" t="n"/>
-      <c r="AD43" s="34" t="n"/>
-      <c r="AE43" s="34" t="n"/>
-      <c r="AF43" s="34" t="n"/>
-      <c r="AG43" s="34" t="n"/>
-      <c r="AH43" s="35">
+      <c r="B43" s="38" t="n"/>
+      <c r="C43" s="39" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="39" t="n"/>
+      <c r="H43" s="39" t="n"/>
+      <c r="I43" s="39" t="n"/>
+      <c r="J43" s="39" t="n"/>
+      <c r="K43" s="39" t="n"/>
+      <c r="L43" s="39" t="n"/>
+      <c r="M43" s="39" t="n"/>
+      <c r="N43" s="39" t="n"/>
+      <c r="O43" s="39" t="n"/>
+      <c r="P43" s="39" t="n"/>
+      <c r="Q43" s="39" t="n"/>
+      <c r="R43" s="39" t="n"/>
+      <c r="S43" s="39" t="n"/>
+      <c r="T43" s="39" t="n"/>
+      <c r="U43" s="39" t="n"/>
+      <c r="V43" s="39" t="n"/>
+      <c r="W43" s="39" t="n"/>
+      <c r="X43" s="39" t="n"/>
+      <c r="Y43" s="39" t="n"/>
+      <c r="Z43" s="39" t="n"/>
+      <c r="AA43" s="39" t="n"/>
+      <c r="AB43" s="39" t="n"/>
+      <c r="AC43" s="39" t="n"/>
+      <c r="AD43" s="39" t="n"/>
+      <c r="AE43" s="39" t="n"/>
+      <c r="AF43" s="39" t="n"/>
+      <c r="AG43" s="39" t="n"/>
+      <c r="AH43" s="40">
         <f>COUNTIF(C43:AG43,"A")</f>
         <v/>
       </c>
-      <c r="AI43" s="35">
+      <c r="AI43" s="40">
         <f>COUNTIF(C43:AG43,"F")</f>
         <v/>
       </c>
-      <c r="AJ43" s="35">
+      <c r="AJ43" s="40">
         <f>COUNTIF(C43:AG43,"R")</f>
         <v/>
       </c>
-      <c r="AK43" s="35">
+      <c r="AK43" s="40">
         <f>COUNTIF(C43:AG43,"V")</f>
         <v/>
       </c>
-      <c r="AL43" s="35">
+      <c r="AL43" s="40">
         <f>COUNTIF(C43:AG43,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="33" t="n">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="37" t="n">
         <v>38</v>
       </c>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="34" t="n"/>
-      <c r="D44" s="34" t="n"/>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="34" t="n"/>
-      <c r="G44" s="34" t="n"/>
-      <c r="H44" s="34" t="n"/>
-      <c r="I44" s="34" t="n"/>
-      <c r="J44" s="34" t="n"/>
-      <c r="K44" s="34" t="n"/>
-      <c r="L44" s="34" t="n"/>
-      <c r="M44" s="34" t="n"/>
-      <c r="N44" s="34" t="n"/>
-      <c r="O44" s="34" t="n"/>
-      <c r="P44" s="34" t="n"/>
-      <c r="Q44" s="34" t="n"/>
-      <c r="R44" s="34" t="n"/>
-      <c r="S44" s="34" t="n"/>
-      <c r="T44" s="34" t="n"/>
-      <c r="U44" s="34" t="n"/>
-      <c r="V44" s="34" t="n"/>
-      <c r="W44" s="34" t="n"/>
-      <c r="X44" s="34" t="n"/>
-      <c r="Y44" s="34" t="n"/>
-      <c r="Z44" s="34" t="n"/>
-      <c r="AA44" s="34" t="n"/>
-      <c r="AB44" s="34" t="n"/>
-      <c r="AC44" s="34" t="n"/>
-      <c r="AD44" s="34" t="n"/>
-      <c r="AE44" s="34" t="n"/>
-      <c r="AF44" s="34" t="n"/>
-      <c r="AG44" s="34" t="n"/>
-      <c r="AH44" s="35">
+      <c r="B44" s="38" t="n"/>
+      <c r="C44" s="39" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="39" t="n"/>
+      <c r="H44" s="39" t="n"/>
+      <c r="I44" s="39" t="n"/>
+      <c r="J44" s="39" t="n"/>
+      <c r="K44" s="39" t="n"/>
+      <c r="L44" s="39" t="n"/>
+      <c r="M44" s="39" t="n"/>
+      <c r="N44" s="39" t="n"/>
+      <c r="O44" s="39" t="n"/>
+      <c r="P44" s="39" t="n"/>
+      <c r="Q44" s="39" t="n"/>
+      <c r="R44" s="39" t="n"/>
+      <c r="S44" s="39" t="n"/>
+      <c r="T44" s="39" t="n"/>
+      <c r="U44" s="39" t="n"/>
+      <c r="V44" s="39" t="n"/>
+      <c r="W44" s="39" t="n"/>
+      <c r="X44" s="39" t="n"/>
+      <c r="Y44" s="39" t="n"/>
+      <c r="Z44" s="39" t="n"/>
+      <c r="AA44" s="39" t="n"/>
+      <c r="AB44" s="39" t="n"/>
+      <c r="AC44" s="39" t="n"/>
+      <c r="AD44" s="39" t="n"/>
+      <c r="AE44" s="39" t="n"/>
+      <c r="AF44" s="39" t="n"/>
+      <c r="AG44" s="39" t="n"/>
+      <c r="AH44" s="40">
         <f>COUNTIF(C44:AG44,"A")</f>
         <v/>
       </c>
-      <c r="AI44" s="35">
+      <c r="AI44" s="40">
         <f>COUNTIF(C44:AG44,"F")</f>
         <v/>
       </c>
-      <c r="AJ44" s="35">
+      <c r="AJ44" s="40">
         <f>COUNTIF(C44:AG44,"R")</f>
         <v/>
       </c>
-      <c r="AK44" s="35">
+      <c r="AK44" s="40">
         <f>COUNTIF(C44:AG44,"V")</f>
         <v/>
       </c>
-      <c r="AL44" s="35">
+      <c r="AL44" s="40">
         <f>COUNTIF(C44:AG44,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="33" t="n">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="37" t="n">
         <v>39</v>
       </c>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="34" t="n"/>
-      <c r="D45" s="34" t="n"/>
-      <c r="E45" s="34" t="n"/>
-      <c r="F45" s="34" t="n"/>
-      <c r="G45" s="34" t="n"/>
-      <c r="H45" s="34" t="n"/>
-      <c r="I45" s="34" t="n"/>
-      <c r="J45" s="34" t="n"/>
-      <c r="K45" s="34" t="n"/>
-      <c r="L45" s="34" t="n"/>
-      <c r="M45" s="34" t="n"/>
-      <c r="N45" s="34" t="n"/>
-      <c r="O45" s="34" t="n"/>
-      <c r="P45" s="34" t="n"/>
-      <c r="Q45" s="34" t="n"/>
-      <c r="R45" s="34" t="n"/>
-      <c r="S45" s="34" t="n"/>
-      <c r="T45" s="34" t="n"/>
-      <c r="U45" s="34" t="n"/>
-      <c r="V45" s="34" t="n"/>
-      <c r="W45" s="34" t="n"/>
-      <c r="X45" s="34" t="n"/>
-      <c r="Y45" s="34" t="n"/>
-      <c r="Z45" s="34" t="n"/>
-      <c r="AA45" s="34" t="n"/>
-      <c r="AB45" s="34" t="n"/>
-      <c r="AC45" s="34" t="n"/>
-      <c r="AD45" s="34" t="n"/>
-      <c r="AE45" s="34" t="n"/>
-      <c r="AF45" s="34" t="n"/>
-      <c r="AG45" s="34" t="n"/>
-      <c r="AH45" s="35">
+      <c r="B45" s="38" t="n"/>
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="39" t="n"/>
+      <c r="H45" s="39" t="n"/>
+      <c r="I45" s="39" t="n"/>
+      <c r="J45" s="39" t="n"/>
+      <c r="K45" s="39" t="n"/>
+      <c r="L45" s="39" t="n"/>
+      <c r="M45" s="39" t="n"/>
+      <c r="N45" s="39" t="n"/>
+      <c r="O45" s="39" t="n"/>
+      <c r="P45" s="39" t="n"/>
+      <c r="Q45" s="39" t="n"/>
+      <c r="R45" s="39" t="n"/>
+      <c r="S45" s="39" t="n"/>
+      <c r="T45" s="39" t="n"/>
+      <c r="U45" s="39" t="n"/>
+      <c r="V45" s="39" t="n"/>
+      <c r="W45" s="39" t="n"/>
+      <c r="X45" s="39" t="n"/>
+      <c r="Y45" s="39" t="n"/>
+      <c r="Z45" s="39" t="n"/>
+      <c r="AA45" s="39" t="n"/>
+      <c r="AB45" s="39" t="n"/>
+      <c r="AC45" s="39" t="n"/>
+      <c r="AD45" s="39" t="n"/>
+      <c r="AE45" s="39" t="n"/>
+      <c r="AF45" s="39" t="n"/>
+      <c r="AG45" s="39" t="n"/>
+      <c r="AH45" s="40">
         <f>COUNTIF(C45:AG45,"A")</f>
         <v/>
       </c>
-      <c r="AI45" s="35">
+      <c r="AI45" s="40">
         <f>COUNTIF(C45:AG45,"F")</f>
         <v/>
       </c>
-      <c r="AJ45" s="35">
+      <c r="AJ45" s="40">
         <f>COUNTIF(C45:AG45,"R")</f>
         <v/>
       </c>
-      <c r="AK45" s="35">
+      <c r="AK45" s="40">
         <f>COUNTIF(C45:AG45,"V")</f>
         <v/>
       </c>
-      <c r="AL45" s="35">
+      <c r="AL45" s="40">
         <f>COUNTIF(C45:AG45,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="33" t="n">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="37" t="n">
         <v>40</v>
       </c>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="34" t="n"/>
-      <c r="D46" s="34" t="n"/>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="34" t="n"/>
-      <c r="G46" s="34" t="n"/>
-      <c r="H46" s="34" t="n"/>
-      <c r="I46" s="34" t="n"/>
-      <c r="J46" s="34" t="n"/>
-      <c r="K46" s="34" t="n"/>
-      <c r="L46" s="34" t="n"/>
-      <c r="M46" s="34" t="n"/>
-      <c r="N46" s="34" t="n"/>
-      <c r="O46" s="34" t="n"/>
-      <c r="P46" s="34" t="n"/>
-      <c r="Q46" s="34" t="n"/>
-      <c r="R46" s="34" t="n"/>
-      <c r="S46" s="34" t="n"/>
-      <c r="T46" s="34" t="n"/>
-      <c r="U46" s="34" t="n"/>
-      <c r="V46" s="34" t="n"/>
-      <c r="W46" s="34" t="n"/>
-      <c r="X46" s="34" t="n"/>
-      <c r="Y46" s="34" t="n"/>
-      <c r="Z46" s="34" t="n"/>
-      <c r="AA46" s="34" t="n"/>
-      <c r="AB46" s="34" t="n"/>
-      <c r="AC46" s="34" t="n"/>
-      <c r="AD46" s="34" t="n"/>
-      <c r="AE46" s="34" t="n"/>
-      <c r="AF46" s="34" t="n"/>
-      <c r="AG46" s="34" t="n"/>
-      <c r="AH46" s="35">
+      <c r="B46" s="38" t="n"/>
+      <c r="C46" s="39" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="39" t="n"/>
+      <c r="F46" s="39" t="n"/>
+      <c r="G46" s="39" t="n"/>
+      <c r="H46" s="39" t="n"/>
+      <c r="I46" s="39" t="n"/>
+      <c r="J46" s="39" t="n"/>
+      <c r="K46" s="39" t="n"/>
+      <c r="L46" s="39" t="n"/>
+      <c r="M46" s="39" t="n"/>
+      <c r="N46" s="39" t="n"/>
+      <c r="O46" s="39" t="n"/>
+      <c r="P46" s="39" t="n"/>
+      <c r="Q46" s="39" t="n"/>
+      <c r="R46" s="39" t="n"/>
+      <c r="S46" s="39" t="n"/>
+      <c r="T46" s="39" t="n"/>
+      <c r="U46" s="39" t="n"/>
+      <c r="V46" s="39" t="n"/>
+      <c r="W46" s="39" t="n"/>
+      <c r="X46" s="39" t="n"/>
+      <c r="Y46" s="39" t="n"/>
+      <c r="Z46" s="39" t="n"/>
+      <c r="AA46" s="39" t="n"/>
+      <c r="AB46" s="39" t="n"/>
+      <c r="AC46" s="39" t="n"/>
+      <c r="AD46" s="39" t="n"/>
+      <c r="AE46" s="39" t="n"/>
+      <c r="AF46" s="39" t="n"/>
+      <c r="AG46" s="39" t="n"/>
+      <c r="AH46" s="40">
         <f>COUNTIF(C46:AG46,"A")</f>
         <v/>
       </c>
-      <c r="AI46" s="35">
+      <c r="AI46" s="40">
         <f>COUNTIF(C46:AG46,"F")</f>
         <v/>
       </c>
-      <c r="AJ46" s="35">
+      <c r="AJ46" s="40">
         <f>COUNTIF(C46:AG46,"R")</f>
         <v/>
       </c>
-      <c r="AK46" s="35">
+      <c r="AK46" s="40">
         <f>COUNTIF(C46:AG46,"V")</f>
         <v/>
       </c>
-      <c r="AL46" s="35">
+      <c r="AL46" s="40">
         <f>COUNTIF(C46:AG46,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="33" t="n">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="37" t="n">
         <v>41</v>
       </c>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="34" t="n"/>
-      <c r="D47" s="34" t="n"/>
-      <c r="E47" s="34" t="n"/>
-      <c r="F47" s="34" t="n"/>
-      <c r="G47" s="34" t="n"/>
-      <c r="H47" s="34" t="n"/>
-      <c r="I47" s="34" t="n"/>
-      <c r="J47" s="34" t="n"/>
-      <c r="K47" s="34" t="n"/>
-      <c r="L47" s="34" t="n"/>
-      <c r="M47" s="34" t="n"/>
-      <c r="N47" s="34" t="n"/>
-      <c r="O47" s="34" t="n"/>
-      <c r="P47" s="34" t="n"/>
-      <c r="Q47" s="34" t="n"/>
-      <c r="R47" s="34" t="n"/>
-      <c r="S47" s="34" t="n"/>
-      <c r="T47" s="34" t="n"/>
-      <c r="U47" s="34" t="n"/>
-      <c r="V47" s="34" t="n"/>
-      <c r="W47" s="34" t="n"/>
-      <c r="X47" s="34" t="n"/>
-      <c r="Y47" s="34" t="n"/>
-      <c r="Z47" s="34" t="n"/>
-      <c r="AA47" s="34" t="n"/>
-      <c r="AB47" s="34" t="n"/>
-      <c r="AC47" s="34" t="n"/>
-      <c r="AD47" s="34" t="n"/>
-      <c r="AE47" s="34" t="n"/>
-      <c r="AF47" s="34" t="n"/>
-      <c r="AG47" s="34" t="n"/>
-      <c r="AH47" s="35">
+      <c r="B47" s="38" t="n"/>
+      <c r="C47" s="39" t="n"/>
+      <c r="D47" s="39" t="n"/>
+      <c r="E47" s="39" t="n"/>
+      <c r="F47" s="39" t="n"/>
+      <c r="G47" s="39" t="n"/>
+      <c r="H47" s="39" t="n"/>
+      <c r="I47" s="39" t="n"/>
+      <c r="J47" s="39" t="n"/>
+      <c r="K47" s="39" t="n"/>
+      <c r="L47" s="39" t="n"/>
+      <c r="M47" s="39" t="n"/>
+      <c r="N47" s="39" t="n"/>
+      <c r="O47" s="39" t="n"/>
+      <c r="P47" s="39" t="n"/>
+      <c r="Q47" s="39" t="n"/>
+      <c r="R47" s="39" t="n"/>
+      <c r="S47" s="39" t="n"/>
+      <c r="T47" s="39" t="n"/>
+      <c r="U47" s="39" t="n"/>
+      <c r="V47" s="39" t="n"/>
+      <c r="W47" s="39" t="n"/>
+      <c r="X47" s="39" t="n"/>
+      <c r="Y47" s="39" t="n"/>
+      <c r="Z47" s="39" t="n"/>
+      <c r="AA47" s="39" t="n"/>
+      <c r="AB47" s="39" t="n"/>
+      <c r="AC47" s="39" t="n"/>
+      <c r="AD47" s="39" t="n"/>
+      <c r="AE47" s="39" t="n"/>
+      <c r="AF47" s="39" t="n"/>
+      <c r="AG47" s="39" t="n"/>
+      <c r="AH47" s="40">
         <f>COUNTIF(C47:AG47,"A")</f>
         <v/>
       </c>
-      <c r="AI47" s="35">
+      <c r="AI47" s="40">
         <f>COUNTIF(C47:AG47,"F")</f>
         <v/>
       </c>
-      <c r="AJ47" s="35">
+      <c r="AJ47" s="40">
         <f>COUNTIF(C47:AG47,"R")</f>
         <v/>
       </c>
-      <c r="AK47" s="35">
+      <c r="AK47" s="40">
         <f>COUNTIF(C47:AG47,"V")</f>
         <v/>
       </c>
-      <c r="AL47" s="35">
+      <c r="AL47" s="40">
         <f>COUNTIF(C47:AG47,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="33" t="n">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="37" t="n">
         <v>42</v>
       </c>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="34" t="n"/>
-      <c r="D48" s="34" t="n"/>
-      <c r="E48" s="34" t="n"/>
-      <c r="F48" s="34" t="n"/>
-      <c r="G48" s="34" t="n"/>
-      <c r="H48" s="34" t="n"/>
-      <c r="I48" s="34" t="n"/>
-      <c r="J48" s="34" t="n"/>
-      <c r="K48" s="34" t="n"/>
-      <c r="L48" s="34" t="n"/>
-      <c r="M48" s="34" t="n"/>
-      <c r="N48" s="34" t="n"/>
-      <c r="O48" s="34" t="n"/>
-      <c r="P48" s="34" t="n"/>
-      <c r="Q48" s="34" t="n"/>
-      <c r="R48" s="34" t="n"/>
-      <c r="S48" s="34" t="n"/>
-      <c r="T48" s="34" t="n"/>
-      <c r="U48" s="34" t="n"/>
-      <c r="V48" s="34" t="n"/>
-      <c r="W48" s="34" t="n"/>
-      <c r="X48" s="34" t="n"/>
-      <c r="Y48" s="34" t="n"/>
-      <c r="Z48" s="34" t="n"/>
-      <c r="AA48" s="34" t="n"/>
-      <c r="AB48" s="34" t="n"/>
-      <c r="AC48" s="34" t="n"/>
-      <c r="AD48" s="34" t="n"/>
-      <c r="AE48" s="34" t="n"/>
-      <c r="AF48" s="34" t="n"/>
-      <c r="AG48" s="34" t="n"/>
-      <c r="AH48" s="35">
+      <c r="B48" s="38" t="n"/>
+      <c r="C48" s="39" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="39" t="n"/>
+      <c r="F48" s="39" t="n"/>
+      <c r="G48" s="39" t="n"/>
+      <c r="H48" s="39" t="n"/>
+      <c r="I48" s="39" t="n"/>
+      <c r="J48" s="39" t="n"/>
+      <c r="K48" s="39" t="n"/>
+      <c r="L48" s="39" t="n"/>
+      <c r="M48" s="39" t="n"/>
+      <c r="N48" s="39" t="n"/>
+      <c r="O48" s="39" t="n"/>
+      <c r="P48" s="39" t="n"/>
+      <c r="Q48" s="39" t="n"/>
+      <c r="R48" s="39" t="n"/>
+      <c r="S48" s="39" t="n"/>
+      <c r="T48" s="39" t="n"/>
+      <c r="U48" s="39" t="n"/>
+      <c r="V48" s="39" t="n"/>
+      <c r="W48" s="39" t="n"/>
+      <c r="X48" s="39" t="n"/>
+      <c r="Y48" s="39" t="n"/>
+      <c r="Z48" s="39" t="n"/>
+      <c r="AA48" s="39" t="n"/>
+      <c r="AB48" s="39" t="n"/>
+      <c r="AC48" s="39" t="n"/>
+      <c r="AD48" s="39" t="n"/>
+      <c r="AE48" s="39" t="n"/>
+      <c r="AF48" s="39" t="n"/>
+      <c r="AG48" s="39" t="n"/>
+      <c r="AH48" s="40">
         <f>COUNTIF(C48:AG48,"A")</f>
         <v/>
       </c>
-      <c r="AI48" s="35">
+      <c r="AI48" s="40">
         <f>COUNTIF(C48:AG48,"F")</f>
         <v/>
       </c>
-      <c r="AJ48" s="35">
+      <c r="AJ48" s="40">
         <f>COUNTIF(C48:AG48,"R")</f>
         <v/>
       </c>
-      <c r="AK48" s="35">
+      <c r="AK48" s="40">
         <f>COUNTIF(C48:AG48,"V")</f>
         <v/>
       </c>
-      <c r="AL48" s="35">
+      <c r="AL48" s="40">
         <f>COUNTIF(C48:AG48,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="33" t="n">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="37" t="n">
         <v>43</v>
       </c>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="34" t="n"/>
-      <c r="D49" s="34" t="n"/>
-      <c r="E49" s="34" t="n"/>
-      <c r="F49" s="34" t="n"/>
-      <c r="G49" s="34" t="n"/>
-      <c r="H49" s="34" t="n"/>
-      <c r="I49" s="34" t="n"/>
-      <c r="J49" s="34" t="n"/>
-      <c r="K49" s="34" t="n"/>
-      <c r="L49" s="34" t="n"/>
-      <c r="M49" s="34" t="n"/>
-      <c r="N49" s="34" t="n"/>
-      <c r="O49" s="34" t="n"/>
-      <c r="P49" s="34" t="n"/>
-      <c r="Q49" s="34" t="n"/>
-      <c r="R49" s="34" t="n"/>
-      <c r="S49" s="34" t="n"/>
-      <c r="T49" s="34" t="n"/>
-      <c r="U49" s="34" t="n"/>
-      <c r="V49" s="34" t="n"/>
-      <c r="W49" s="34" t="n"/>
-      <c r="X49" s="34" t="n"/>
-      <c r="Y49" s="34" t="n"/>
-      <c r="Z49" s="34" t="n"/>
-      <c r="AA49" s="34" t="n"/>
-      <c r="AB49" s="34" t="n"/>
-      <c r="AC49" s="34" t="n"/>
-      <c r="AD49" s="34" t="n"/>
-      <c r="AE49" s="34" t="n"/>
-      <c r="AF49" s="34" t="n"/>
-      <c r="AG49" s="34" t="n"/>
-      <c r="AH49" s="35">
+      <c r="B49" s="38" t="n"/>
+      <c r="C49" s="39" t="n"/>
+      <c r="D49" s="39" t="n"/>
+      <c r="E49" s="39" t="n"/>
+      <c r="F49" s="39" t="n"/>
+      <c r="G49" s="39" t="n"/>
+      <c r="H49" s="39" t="n"/>
+      <c r="I49" s="39" t="n"/>
+      <c r="J49" s="39" t="n"/>
+      <c r="K49" s="39" t="n"/>
+      <c r="L49" s="39" t="n"/>
+      <c r="M49" s="39" t="n"/>
+      <c r="N49" s="39" t="n"/>
+      <c r="O49" s="39" t="n"/>
+      <c r="P49" s="39" t="n"/>
+      <c r="Q49" s="39" t="n"/>
+      <c r="R49" s="39" t="n"/>
+      <c r="S49" s="39" t="n"/>
+      <c r="T49" s="39" t="n"/>
+      <c r="U49" s="39" t="n"/>
+      <c r="V49" s="39" t="n"/>
+      <c r="W49" s="39" t="n"/>
+      <c r="X49" s="39" t="n"/>
+      <c r="Y49" s="39" t="n"/>
+      <c r="Z49" s="39" t="n"/>
+      <c r="AA49" s="39" t="n"/>
+      <c r="AB49" s="39" t="n"/>
+      <c r="AC49" s="39" t="n"/>
+      <c r="AD49" s="39" t="n"/>
+      <c r="AE49" s="39" t="n"/>
+      <c r="AF49" s="39" t="n"/>
+      <c r="AG49" s="39" t="n"/>
+      <c r="AH49" s="40">
         <f>COUNTIF(C49:AG49,"A")</f>
         <v/>
       </c>
-      <c r="AI49" s="35">
+      <c r="AI49" s="40">
         <f>COUNTIF(C49:AG49,"F")</f>
         <v/>
       </c>
-      <c r="AJ49" s="35">
+      <c r="AJ49" s="40">
         <f>COUNTIF(C49:AG49,"R")</f>
         <v/>
       </c>
-      <c r="AK49" s="35">
+      <c r="AK49" s="40">
         <f>COUNTIF(C49:AG49,"V")</f>
         <v/>
       </c>
-      <c r="AL49" s="35">
+      <c r="AL49" s="40">
         <f>COUNTIF(C49:AG49,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="33" t="n">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="37" t="n">
         <v>44</v>
       </c>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="34" t="n"/>
-      <c r="D50" s="34" t="n"/>
-      <c r="E50" s="34" t="n"/>
-      <c r="F50" s="34" t="n"/>
-      <c r="G50" s="34" t="n"/>
-      <c r="H50" s="34" t="n"/>
-      <c r="I50" s="34" t="n"/>
-      <c r="J50" s="34" t="n"/>
-      <c r="K50" s="34" t="n"/>
-      <c r="L50" s="34" t="n"/>
-      <c r="M50" s="34" t="n"/>
-      <c r="N50" s="34" t="n"/>
-      <c r="O50" s="34" t="n"/>
-      <c r="P50" s="34" t="n"/>
-      <c r="Q50" s="34" t="n"/>
-      <c r="R50" s="34" t="n"/>
-      <c r="S50" s="34" t="n"/>
-      <c r="T50" s="34" t="n"/>
-      <c r="U50" s="34" t="n"/>
-      <c r="V50" s="34" t="n"/>
-      <c r="W50" s="34" t="n"/>
-      <c r="X50" s="34" t="n"/>
-      <c r="Y50" s="34" t="n"/>
-      <c r="Z50" s="34" t="n"/>
-      <c r="AA50" s="34" t="n"/>
-      <c r="AB50" s="34" t="n"/>
-      <c r="AC50" s="34" t="n"/>
-      <c r="AD50" s="34" t="n"/>
-      <c r="AE50" s="34" t="n"/>
-      <c r="AF50" s="34" t="n"/>
-      <c r="AG50" s="34" t="n"/>
-      <c r="AH50" s="35">
+      <c r="B50" s="38" t="n"/>
+      <c r="C50" s="39" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="39" t="n"/>
+      <c r="F50" s="39" t="n"/>
+      <c r="G50" s="39" t="n"/>
+      <c r="H50" s="39" t="n"/>
+      <c r="I50" s="39" t="n"/>
+      <c r="J50" s="39" t="n"/>
+      <c r="K50" s="39" t="n"/>
+      <c r="L50" s="39" t="n"/>
+      <c r="M50" s="39" t="n"/>
+      <c r="N50" s="39" t="n"/>
+      <c r="O50" s="39" t="n"/>
+      <c r="P50" s="39" t="n"/>
+      <c r="Q50" s="39" t="n"/>
+      <c r="R50" s="39" t="n"/>
+      <c r="S50" s="39" t="n"/>
+      <c r="T50" s="39" t="n"/>
+      <c r="U50" s="39" t="n"/>
+      <c r="V50" s="39" t="n"/>
+      <c r="W50" s="39" t="n"/>
+      <c r="X50" s="39" t="n"/>
+      <c r="Y50" s="39" t="n"/>
+      <c r="Z50" s="39" t="n"/>
+      <c r="AA50" s="39" t="n"/>
+      <c r="AB50" s="39" t="n"/>
+      <c r="AC50" s="39" t="n"/>
+      <c r="AD50" s="39" t="n"/>
+      <c r="AE50" s="39" t="n"/>
+      <c r="AF50" s="39" t="n"/>
+      <c r="AG50" s="39" t="n"/>
+      <c r="AH50" s="40">
         <f>COUNTIF(C50:AG50,"A")</f>
         <v/>
       </c>
-      <c r="AI50" s="35">
+      <c r="AI50" s="40">
         <f>COUNTIF(C50:AG50,"F")</f>
         <v/>
       </c>
-      <c r="AJ50" s="35">
+      <c r="AJ50" s="40">
         <f>COUNTIF(C50:AG50,"R")</f>
         <v/>
       </c>
-      <c r="AK50" s="35">
+      <c r="AK50" s="40">
         <f>COUNTIF(C50:AG50,"V")</f>
         <v/>
       </c>
-      <c r="AL50" s="35">
+      <c r="AL50" s="40">
         <f>COUNTIF(C50:AG50,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="33" t="n">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="37" t="n">
         <v>45</v>
       </c>
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="34" t="n"/>
-      <c r="D51" s="34" t="n"/>
-      <c r="E51" s="34" t="n"/>
-      <c r="F51" s="34" t="n"/>
-      <c r="G51" s="34" t="n"/>
-      <c r="H51" s="34" t="n"/>
-      <c r="I51" s="34" t="n"/>
-      <c r="J51" s="34" t="n"/>
-      <c r="K51" s="34" t="n"/>
-      <c r="L51" s="34" t="n"/>
-      <c r="M51" s="34" t="n"/>
-      <c r="N51" s="34" t="n"/>
-      <c r="O51" s="34" t="n"/>
-      <c r="P51" s="34" t="n"/>
-      <c r="Q51" s="34" t="n"/>
-      <c r="R51" s="34" t="n"/>
-      <c r="S51" s="34" t="n"/>
-      <c r="T51" s="34" t="n"/>
-      <c r="U51" s="34" t="n"/>
-      <c r="V51" s="34" t="n"/>
-      <c r="W51" s="34" t="n"/>
-      <c r="X51" s="34" t="n"/>
-      <c r="Y51" s="34" t="n"/>
-      <c r="Z51" s="34" t="n"/>
-      <c r="AA51" s="34" t="n"/>
-      <c r="AB51" s="34" t="n"/>
-      <c r="AC51" s="34" t="n"/>
-      <c r="AD51" s="34" t="n"/>
-      <c r="AE51" s="34" t="n"/>
-      <c r="AF51" s="34" t="n"/>
-      <c r="AG51" s="34" t="n"/>
-      <c r="AH51" s="35">
+      <c r="B51" s="38" t="n"/>
+      <c r="C51" s="39" t="n"/>
+      <c r="D51" s="39" t="n"/>
+      <c r="E51" s="39" t="n"/>
+      <c r="F51" s="39" t="n"/>
+      <c r="G51" s="39" t="n"/>
+      <c r="H51" s="39" t="n"/>
+      <c r="I51" s="39" t="n"/>
+      <c r="J51" s="39" t="n"/>
+      <c r="K51" s="39" t="n"/>
+      <c r="L51" s="39" t="n"/>
+      <c r="M51" s="39" t="n"/>
+      <c r="N51" s="39" t="n"/>
+      <c r="O51" s="39" t="n"/>
+      <c r="P51" s="39" t="n"/>
+      <c r="Q51" s="39" t="n"/>
+      <c r="R51" s="39" t="n"/>
+      <c r="S51" s="39" t="n"/>
+      <c r="T51" s="39" t="n"/>
+      <c r="U51" s="39" t="n"/>
+      <c r="V51" s="39" t="n"/>
+      <c r="W51" s="39" t="n"/>
+      <c r="X51" s="39" t="n"/>
+      <c r="Y51" s="39" t="n"/>
+      <c r="Z51" s="39" t="n"/>
+      <c r="AA51" s="39" t="n"/>
+      <c r="AB51" s="39" t="n"/>
+      <c r="AC51" s="39" t="n"/>
+      <c r="AD51" s="39" t="n"/>
+      <c r="AE51" s="39" t="n"/>
+      <c r="AF51" s="39" t="n"/>
+      <c r="AG51" s="39" t="n"/>
+      <c r="AH51" s="40">
         <f>COUNTIF(C51:AG51,"A")</f>
         <v/>
       </c>
-      <c r="AI51" s="35">
+      <c r="AI51" s="40">
         <f>COUNTIF(C51:AG51,"F")</f>
         <v/>
       </c>
-      <c r="AJ51" s="35">
+      <c r="AJ51" s="40">
         <f>COUNTIF(C51:AG51,"R")</f>
         <v/>
       </c>
-      <c r="AK51" s="35">
+      <c r="AK51" s="40">
         <f>COUNTIF(C51:AG51,"V")</f>
         <v/>
       </c>
-      <c r="AL51" s="35">
+      <c r="AL51" s="40">
         <f>COUNTIF(C51:AG51,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="33" t="n">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="37" t="n">
         <v>46</v>
       </c>
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="34" t="n"/>
-      <c r="D52" s="34" t="n"/>
-      <c r="E52" s="34" t="n"/>
-      <c r="F52" s="34" t="n"/>
-      <c r="G52" s="34" t="n"/>
-      <c r="H52" s="34" t="n"/>
-      <c r="I52" s="34" t="n"/>
-      <c r="J52" s="34" t="n"/>
-      <c r="K52" s="34" t="n"/>
-      <c r="L52" s="34" t="n"/>
-      <c r="M52" s="34" t="n"/>
-      <c r="N52" s="34" t="n"/>
-      <c r="O52" s="34" t="n"/>
-      <c r="P52" s="34" t="n"/>
-      <c r="Q52" s="34" t="n"/>
-      <c r="R52" s="34" t="n"/>
-      <c r="S52" s="34" t="n"/>
-      <c r="T52" s="34" t="n"/>
-      <c r="U52" s="34" t="n"/>
-      <c r="V52" s="34" t="n"/>
-      <c r="W52" s="34" t="n"/>
-      <c r="X52" s="34" t="n"/>
-      <c r="Y52" s="34" t="n"/>
-      <c r="Z52" s="34" t="n"/>
-      <c r="AA52" s="34" t="n"/>
-      <c r="AB52" s="34" t="n"/>
-      <c r="AC52" s="34" t="n"/>
-      <c r="AD52" s="34" t="n"/>
-      <c r="AE52" s="34" t="n"/>
-      <c r="AF52" s="34" t="n"/>
-      <c r="AG52" s="34" t="n"/>
-      <c r="AH52" s="35">
+      <c r="B52" s="38" t="n"/>
+      <c r="C52" s="39" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="39" t="n"/>
+      <c r="F52" s="39" t="n"/>
+      <c r="G52" s="39" t="n"/>
+      <c r="H52" s="39" t="n"/>
+      <c r="I52" s="39" t="n"/>
+      <c r="J52" s="39" t="n"/>
+      <c r="K52" s="39" t="n"/>
+      <c r="L52" s="39" t="n"/>
+      <c r="M52" s="39" t="n"/>
+      <c r="N52" s="39" t="n"/>
+      <c r="O52" s="39" t="n"/>
+      <c r="P52" s="39" t="n"/>
+      <c r="Q52" s="39" t="n"/>
+      <c r="R52" s="39" t="n"/>
+      <c r="S52" s="39" t="n"/>
+      <c r="T52" s="39" t="n"/>
+      <c r="U52" s="39" t="n"/>
+      <c r="V52" s="39" t="n"/>
+      <c r="W52" s="39" t="n"/>
+      <c r="X52" s="39" t="n"/>
+      <c r="Y52" s="39" t="n"/>
+      <c r="Z52" s="39" t="n"/>
+      <c r="AA52" s="39" t="n"/>
+      <c r="AB52" s="39" t="n"/>
+      <c r="AC52" s="39" t="n"/>
+      <c r="AD52" s="39" t="n"/>
+      <c r="AE52" s="39" t="n"/>
+      <c r="AF52" s="39" t="n"/>
+      <c r="AG52" s="39" t="n"/>
+      <c r="AH52" s="40">
         <f>COUNTIF(C52:AG52,"A")</f>
         <v/>
       </c>
-      <c r="AI52" s="35">
+      <c r="AI52" s="40">
         <f>COUNTIF(C52:AG52,"F")</f>
         <v/>
       </c>
-      <c r="AJ52" s="35">
+      <c r="AJ52" s="40">
         <f>COUNTIF(C52:AG52,"R")</f>
         <v/>
       </c>
-      <c r="AK52" s="35">
+      <c r="AK52" s="40">
         <f>COUNTIF(C52:AG52,"V")</f>
         <v/>
       </c>
-      <c r="AL52" s="35">
+      <c r="AL52" s="40">
         <f>COUNTIF(C52:AG52,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="33" t="n">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="37" t="n">
         <v>47</v>
       </c>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="34" t="n"/>
-      <c r="D53" s="34" t="n"/>
-      <c r="E53" s="34" t="n"/>
-      <c r="F53" s="34" t="n"/>
-      <c r="G53" s="34" t="n"/>
-      <c r="H53" s="34" t="n"/>
-      <c r="I53" s="34" t="n"/>
-      <c r="J53" s="34" t="n"/>
-      <c r="K53" s="34" t="n"/>
-      <c r="L53" s="34" t="n"/>
-      <c r="M53" s="34" t="n"/>
-      <c r="N53" s="34" t="n"/>
-      <c r="O53" s="34" t="n"/>
-      <c r="P53" s="34" t="n"/>
-      <c r="Q53" s="34" t="n"/>
-      <c r="R53" s="34" t="n"/>
-      <c r="S53" s="34" t="n"/>
-      <c r="T53" s="34" t="n"/>
-      <c r="U53" s="34" t="n"/>
-      <c r="V53" s="34" t="n"/>
-      <c r="W53" s="34" t="n"/>
-      <c r="X53" s="34" t="n"/>
-      <c r="Y53" s="34" t="n"/>
-      <c r="Z53" s="34" t="n"/>
-      <c r="AA53" s="34" t="n"/>
-      <c r="AB53" s="34" t="n"/>
-      <c r="AC53" s="34" t="n"/>
-      <c r="AD53" s="34" t="n"/>
-      <c r="AE53" s="34" t="n"/>
-      <c r="AF53" s="34" t="n"/>
-      <c r="AG53" s="34" t="n"/>
-      <c r="AH53" s="35">
+      <c r="B53" s="38" t="n"/>
+      <c r="C53" s="39" t="n"/>
+      <c r="D53" s="39" t="n"/>
+      <c r="E53" s="39" t="n"/>
+      <c r="F53" s="39" t="n"/>
+      <c r="G53" s="39" t="n"/>
+      <c r="H53" s="39" t="n"/>
+      <c r="I53" s="39" t="n"/>
+      <c r="J53" s="39" t="n"/>
+      <c r="K53" s="39" t="n"/>
+      <c r="L53" s="39" t="n"/>
+      <c r="M53" s="39" t="n"/>
+      <c r="N53" s="39" t="n"/>
+      <c r="O53" s="39" t="n"/>
+      <c r="P53" s="39" t="n"/>
+      <c r="Q53" s="39" t="n"/>
+      <c r="R53" s="39" t="n"/>
+      <c r="S53" s="39" t="n"/>
+      <c r="T53" s="39" t="n"/>
+      <c r="U53" s="39" t="n"/>
+      <c r="V53" s="39" t="n"/>
+      <c r="W53" s="39" t="n"/>
+      <c r="X53" s="39" t="n"/>
+      <c r="Y53" s="39" t="n"/>
+      <c r="Z53" s="39" t="n"/>
+      <c r="AA53" s="39" t="n"/>
+      <c r="AB53" s="39" t="n"/>
+      <c r="AC53" s="39" t="n"/>
+      <c r="AD53" s="39" t="n"/>
+      <c r="AE53" s="39" t="n"/>
+      <c r="AF53" s="39" t="n"/>
+      <c r="AG53" s="39" t="n"/>
+      <c r="AH53" s="40">
         <f>COUNTIF(C53:AG53,"A")</f>
         <v/>
       </c>
-      <c r="AI53" s="35">
+      <c r="AI53" s="40">
         <f>COUNTIF(C53:AG53,"F")</f>
         <v/>
       </c>
-      <c r="AJ53" s="35">
+      <c r="AJ53" s="40">
         <f>COUNTIF(C53:AG53,"R")</f>
         <v/>
       </c>
-      <c r="AK53" s="35">
+      <c r="AK53" s="40">
         <f>COUNTIF(C53:AG53,"V")</f>
         <v/>
       </c>
-      <c r="AL53" s="35">
+      <c r="AL53" s="40">
         <f>COUNTIF(C53:AG53,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="33" t="n">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="37" t="n">
         <v>48</v>
       </c>
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="34" t="n"/>
-      <c r="D54" s="34" t="n"/>
-      <c r="E54" s="34" t="n"/>
-      <c r="F54" s="34" t="n"/>
-      <c r="G54" s="34" t="n"/>
-      <c r="H54" s="34" t="n"/>
-      <c r="I54" s="34" t="n"/>
-      <c r="J54" s="34" t="n"/>
-      <c r="K54" s="34" t="n"/>
-      <c r="L54" s="34" t="n"/>
-      <c r="M54" s="34" t="n"/>
-      <c r="N54" s="34" t="n"/>
-      <c r="O54" s="34" t="n"/>
-      <c r="P54" s="34" t="n"/>
-      <c r="Q54" s="34" t="n"/>
-      <c r="R54" s="34" t="n"/>
-      <c r="S54" s="34" t="n"/>
-      <c r="T54" s="34" t="n"/>
-      <c r="U54" s="34" t="n"/>
-      <c r="V54" s="34" t="n"/>
-      <c r="W54" s="34" t="n"/>
-      <c r="X54" s="34" t="n"/>
-      <c r="Y54" s="34" t="n"/>
-      <c r="Z54" s="34" t="n"/>
-      <c r="AA54" s="34" t="n"/>
-      <c r="AB54" s="34" t="n"/>
-      <c r="AC54" s="34" t="n"/>
-      <c r="AD54" s="34" t="n"/>
-      <c r="AE54" s="34" t="n"/>
-      <c r="AF54" s="34" t="n"/>
-      <c r="AG54" s="34" t="n"/>
-      <c r="AH54" s="35">
+      <c r="B54" s="38" t="n"/>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="39" t="n"/>
+      <c r="F54" s="39" t="n"/>
+      <c r="G54" s="39" t="n"/>
+      <c r="H54" s="39" t="n"/>
+      <c r="I54" s="39" t="n"/>
+      <c r="J54" s="39" t="n"/>
+      <c r="K54" s="39" t="n"/>
+      <c r="L54" s="39" t="n"/>
+      <c r="M54" s="39" t="n"/>
+      <c r="N54" s="39" t="n"/>
+      <c r="O54" s="39" t="n"/>
+      <c r="P54" s="39" t="n"/>
+      <c r="Q54" s="39" t="n"/>
+      <c r="R54" s="39" t="n"/>
+      <c r="S54" s="39" t="n"/>
+      <c r="T54" s="39" t="n"/>
+      <c r="U54" s="39" t="n"/>
+      <c r="V54" s="39" t="n"/>
+      <c r="W54" s="39" t="n"/>
+      <c r="X54" s="39" t="n"/>
+      <c r="Y54" s="39" t="n"/>
+      <c r="Z54" s="39" t="n"/>
+      <c r="AA54" s="39" t="n"/>
+      <c r="AB54" s="39" t="n"/>
+      <c r="AC54" s="39" t="n"/>
+      <c r="AD54" s="39" t="n"/>
+      <c r="AE54" s="39" t="n"/>
+      <c r="AF54" s="39" t="n"/>
+      <c r="AG54" s="39" t="n"/>
+      <c r="AH54" s="40">
         <f>COUNTIF(C54:AG54,"A")</f>
         <v/>
       </c>
-      <c r="AI54" s="35">
+      <c r="AI54" s="40">
         <f>COUNTIF(C54:AG54,"F")</f>
         <v/>
       </c>
-      <c r="AJ54" s="35">
+      <c r="AJ54" s="40">
         <f>COUNTIF(C54:AG54,"R")</f>
         <v/>
       </c>
-      <c r="AK54" s="35">
+      <c r="AK54" s="40">
         <f>COUNTIF(C54:AG54,"V")</f>
         <v/>
       </c>
-      <c r="AL54" s="35">
+      <c r="AL54" s="40">
         <f>COUNTIF(C54:AG54,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="33" t="n">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="37" t="n">
         <v>49</v>
       </c>
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="34" t="n"/>
-      <c r="D55" s="34" t="n"/>
-      <c r="E55" s="34" t="n"/>
-      <c r="F55" s="34" t="n"/>
-      <c r="G55" s="34" t="n"/>
-      <c r="H55" s="34" t="n"/>
-      <c r="I55" s="34" t="n"/>
-      <c r="J55" s="34" t="n"/>
-      <c r="K55" s="34" t="n"/>
-      <c r="L55" s="34" t="n"/>
-      <c r="M55" s="34" t="n"/>
-      <c r="N55" s="34" t="n"/>
-      <c r="O55" s="34" t="n"/>
-      <c r="P55" s="34" t="n"/>
-      <c r="Q55" s="34" t="n"/>
-      <c r="R55" s="34" t="n"/>
-      <c r="S55" s="34" t="n"/>
-      <c r="T55" s="34" t="n"/>
-      <c r="U55" s="34" t="n"/>
-      <c r="V55" s="34" t="n"/>
-      <c r="W55" s="34" t="n"/>
-      <c r="X55" s="34" t="n"/>
-      <c r="Y55" s="34" t="n"/>
-      <c r="Z55" s="34" t="n"/>
-      <c r="AA55" s="34" t="n"/>
-      <c r="AB55" s="34" t="n"/>
-      <c r="AC55" s="34" t="n"/>
-      <c r="AD55" s="34" t="n"/>
-      <c r="AE55" s="34" t="n"/>
-      <c r="AF55" s="34" t="n"/>
-      <c r="AG55" s="34" t="n"/>
-      <c r="AH55" s="35">
+      <c r="B55" s="38" t="n"/>
+      <c r="C55" s="39" t="n"/>
+      <c r="D55" s="39" t="n"/>
+      <c r="E55" s="39" t="n"/>
+      <c r="F55" s="39" t="n"/>
+      <c r="G55" s="39" t="n"/>
+      <c r="H55" s="39" t="n"/>
+      <c r="I55" s="39" t="n"/>
+      <c r="J55" s="39" t="n"/>
+      <c r="K55" s="39" t="n"/>
+      <c r="L55" s="39" t="n"/>
+      <c r="M55" s="39" t="n"/>
+      <c r="N55" s="39" t="n"/>
+      <c r="O55" s="39" t="n"/>
+      <c r="P55" s="39" t="n"/>
+      <c r="Q55" s="39" t="n"/>
+      <c r="R55" s="39" t="n"/>
+      <c r="S55" s="39" t="n"/>
+      <c r="T55" s="39" t="n"/>
+      <c r="U55" s="39" t="n"/>
+      <c r="V55" s="39" t="n"/>
+      <c r="W55" s="39" t="n"/>
+      <c r="X55" s="39" t="n"/>
+      <c r="Y55" s="39" t="n"/>
+      <c r="Z55" s="39" t="n"/>
+      <c r="AA55" s="39" t="n"/>
+      <c r="AB55" s="39" t="n"/>
+      <c r="AC55" s="39" t="n"/>
+      <c r="AD55" s="39" t="n"/>
+      <c r="AE55" s="39" t="n"/>
+      <c r="AF55" s="39" t="n"/>
+      <c r="AG55" s="39" t="n"/>
+      <c r="AH55" s="40">
         <f>COUNTIF(C55:AG55,"A")</f>
         <v/>
       </c>
-      <c r="AI55" s="35">
+      <c r="AI55" s="40">
         <f>COUNTIF(C55:AG55,"F")</f>
         <v/>
       </c>
-      <c r="AJ55" s="35">
+      <c r="AJ55" s="40">
         <f>COUNTIF(C55:AG55,"R")</f>
         <v/>
       </c>
-      <c r="AK55" s="35">
+      <c r="AK55" s="40">
         <f>COUNTIF(C55:AG55,"V")</f>
         <v/>
       </c>
-      <c r="AL55" s="35">
+      <c r="AL55" s="40">
         <f>COUNTIF(C55:AG55,"I")</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="33" t="n">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="37" t="n">
         <v>50</v>
       </c>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="34" t="n"/>
-      <c r="D56" s="34" t="n"/>
-      <c r="E56" s="34" t="n"/>
-      <c r="F56" s="34" t="n"/>
-      <c r="G56" s="34" t="n"/>
-      <c r="H56" s="34" t="n"/>
-      <c r="I56" s="34" t="n"/>
-      <c r="J56" s="34" t="n"/>
-      <c r="K56" s="34" t="n"/>
-      <c r="L56" s="34" t="n"/>
-      <c r="M56" s="34" t="n"/>
-      <c r="N56" s="34" t="n"/>
-      <c r="O56" s="34" t="n"/>
-      <c r="P56" s="34" t="n"/>
-      <c r="Q56" s="34" t="n"/>
-      <c r="R56" s="34" t="n"/>
-      <c r="S56" s="34" t="n"/>
-      <c r="T56" s="34" t="n"/>
-      <c r="U56" s="34" t="n"/>
-      <c r="V56" s="34" t="n"/>
-      <c r="W56" s="34" t="n"/>
-      <c r="X56" s="34" t="n"/>
-      <c r="Y56" s="34" t="n"/>
-      <c r="Z56" s="34" t="n"/>
-      <c r="AA56" s="34" t="n"/>
-      <c r="AB56" s="34" t="n"/>
-      <c r="AC56" s="34" t="n"/>
-      <c r="AD56" s="34" t="n"/>
-      <c r="AE56" s="34" t="n"/>
-      <c r="AF56" s="34" t="n"/>
-      <c r="AG56" s="34" t="n"/>
-      <c r="AH56" s="35">
+      <c r="B56" s="38" t="n"/>
+      <c r="C56" s="39" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="39" t="n"/>
+      <c r="F56" s="39" t="n"/>
+      <c r="G56" s="39" t="n"/>
+      <c r="H56" s="39" t="n"/>
+      <c r="I56" s="39" t="n"/>
+      <c r="J56" s="39" t="n"/>
+      <c r="K56" s="39" t="n"/>
+      <c r="L56" s="39" t="n"/>
+      <c r="M56" s="39" t="n"/>
+      <c r="N56" s="39" t="n"/>
+      <c r="O56" s="39" t="n"/>
+      <c r="P56" s="39" t="n"/>
+      <c r="Q56" s="39" t="n"/>
+      <c r="R56" s="39" t="n"/>
+      <c r="S56" s="39" t="n"/>
+      <c r="T56" s="39" t="n"/>
+      <c r="U56" s="39" t="n"/>
+      <c r="V56" s="39" t="n"/>
+      <c r="W56" s="39" t="n"/>
+      <c r="X56" s="39" t="n"/>
+      <c r="Y56" s="39" t="n"/>
+      <c r="Z56" s="39" t="n"/>
+      <c r="AA56" s="39" t="n"/>
+      <c r="AB56" s="39" t="n"/>
+      <c r="AC56" s="39" t="n"/>
+      <c r="AD56" s="39" t="n"/>
+      <c r="AE56" s="39" t="n"/>
+      <c r="AF56" s="39" t="n"/>
+      <c r="AG56" s="39" t="n"/>
+      <c r="AH56" s="40">
         <f>COUNTIF(C56:AG56,"A")</f>
         <v/>
       </c>
-      <c r="AI56" s="35">
+      <c r="AI56" s="40">
         <f>COUNTIF(C56:AG56,"F")</f>
         <v/>
       </c>
-      <c r="AJ56" s="35">
+      <c r="AJ56" s="40">
         <f>COUNTIF(C56:AG56,"R")</f>
         <v/>
       </c>
-      <c r="AK56" s="35">
+      <c r="AK56" s="40">
         <f>COUNTIF(C56:AG56,"V")</f>
         <v/>
       </c>
-      <c r="AL56" s="35">
+      <c r="AL56" s="40">
         <f>COUNTIF(C56:AG56,"I")</f>
         <v/>
       </c>
@@ -4819,7 +5018,7 @@
     <mergeCell ref="C5:J5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C7:AG56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C7:AG56" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="OPCIÓN NO VÁLIDA" error="Elige una opción de la lista (puedes editarla en la hoja CATÁLOGOS)." promptTitle="SELECCIONA" prompt="Elige una opción de la lista desplegable." type="list">
       <formula1>"A,F,R,V,I,D,P"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4860,7 +5059,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>RESUMEN DE ASISTENCIA</t>
         </is>
@@ -4871,30 +5070,30 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="I1" s="24" t="n"/>
-      <c r="J1" s="25" t="n"/>
+      <c r="I1" s="28" t="n"/>
+      <c r="J1" s="29" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Asistencias, faltas y retardos del mes</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n"/>
-      <c r="C2" s="27" t="n"/>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="27" t="n"/>
-      <c r="F2" s="27" t="n"/>
-      <c r="G2" s="27" t="n"/>
-      <c r="H2" s="28" t="n"/>
-      <c r="I2" s="29" t="n"/>
-      <c r="J2" s="30" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="31" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="31" t="n"/>
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="n"/>
+      <c r="H2" s="32" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="34" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -4908,56 +5107,56 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>ASISTENCIAS</t>
         </is>
       </c>
-      <c r="C4" s="37" t="n"/>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="C4" s="42" t="n"/>
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>FALTAS</t>
         </is>
       </c>
-      <c r="E4" s="37" t="n"/>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>RETARDOS</t>
         </is>
       </c>
-      <c r="G4" s="37" t="n"/>
-      <c r="H4" s="36" t="inlineStr">
+      <c r="G4" s="42" t="n"/>
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>% ASISTENCIA</t>
         </is>
       </c>
-      <c r="I4" s="37" t="n"/>
+      <c r="I4" s="42" t="n"/>
       <c r="J4" s="4" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="38">
+      <c r="B5" s="43">
         <f>SUM(FORMATO!AH7:AH56)</f>
         <v/>
       </c>
-      <c r="C5" s="39" t="n"/>
-      <c r="D5" s="38">
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="43">
         <f>SUM(FORMATO!AI7:AI56)</f>
         <v/>
       </c>
-      <c r="E5" s="39" t="n"/>
-      <c r="F5" s="38">
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="43">
         <f>SUM(FORMATO!AJ7:AJ56)</f>
         <v/>
       </c>
-      <c r="G5" s="39" t="n"/>
-      <c r="H5" s="40">
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="45">
         <f>IFERROR(B5/(B5+D5+F5),0)</f>
         <v/>
       </c>
-      <c r="I5" s="39" t="n"/>
+      <c r="I5" s="44" t="n"/>
       <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
@@ -5190,17 +5389,17 @@
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>EMPLEADO</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>FALTAS</t>
         </is>
       </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>RETARDOS</t>
         </is>
@@ -5214,15 +5413,15 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="41">
+      <c r="B26" s="46">
         <f>IF(FORMATO!B7="","",FORMATO!B7)</f>
         <v/>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="22">
         <f>FORMATO!AI7</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="22">
         <f>FORMATO!AJ7</f>
         <v/>
       </c>
@@ -5235,15 +5434,15 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="41">
+      <c r="B27" s="46">
         <f>IF(FORMATO!B8="","",FORMATO!B8)</f>
         <v/>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="22">
         <f>FORMATO!AI8</f>
         <v/>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="22">
         <f>FORMATO!AJ8</f>
         <v/>
       </c>
@@ -5256,15 +5455,15 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="41">
+      <c r="B28" s="46">
         <f>IF(FORMATO!B9="","",FORMATO!B9)</f>
         <v/>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="22">
         <f>FORMATO!AI9</f>
         <v/>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="22">
         <f>FORMATO!AJ9</f>
         <v/>
       </c>
@@ -5277,15 +5476,15 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="41">
+      <c r="B29" s="46">
         <f>IF(FORMATO!B10="","",FORMATO!B10)</f>
         <v/>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="22">
         <f>FORMATO!AI10</f>
         <v/>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="22">
         <f>FORMATO!AJ10</f>
         <v/>
       </c>
@@ -5298,15 +5497,15 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="41">
+      <c r="B30" s="46">
         <f>IF(FORMATO!B11="","",FORMATO!B11)</f>
         <v/>
       </c>
-      <c r="C30" s="19">
+      <c r="C30" s="22">
         <f>FORMATO!AI11</f>
         <v/>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="22">
         <f>FORMATO!AJ11</f>
         <v/>
       </c>
@@ -5319,15 +5518,15 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="41">
+      <c r="B31" s="46">
         <f>IF(FORMATO!B12="","",FORMATO!B12)</f>
         <v/>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="22">
         <f>FORMATO!AI12</f>
         <v/>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="22">
         <f>FORMATO!AJ12</f>
         <v/>
       </c>
@@ -5340,15 +5539,15 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="41">
+      <c r="B32" s="46">
         <f>IF(FORMATO!B13="","",FORMATO!B13)</f>
         <v/>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="22">
         <f>FORMATO!AI13</f>
         <v/>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="22">
         <f>FORMATO!AJ13</f>
         <v/>
       </c>
@@ -5361,15 +5560,15 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="41">
+      <c r="B33" s="46">
         <f>IF(FORMATO!B14="","",FORMATO!B14)</f>
         <v/>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="22">
         <f>FORMATO!AI14</f>
         <v/>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="22">
         <f>FORMATO!AJ14</f>
         <v/>
       </c>
@@ -5382,15 +5581,15 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
-      <c r="B34" s="41">
+      <c r="B34" s="46">
         <f>IF(FORMATO!B15="","",FORMATO!B15)</f>
         <v/>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="22">
         <f>FORMATO!AI15</f>
         <v/>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="22">
         <f>FORMATO!AJ15</f>
         <v/>
       </c>
@@ -5403,15 +5602,15 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
-      <c r="B35" s="41">
+      <c r="B35" s="46">
         <f>IF(FORMATO!B16="","",FORMATO!B16)</f>
         <v/>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="22">
         <f>FORMATO!AI16</f>
         <v/>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="22">
         <f>FORMATO!AJ16</f>
         <v/>
       </c>
@@ -5424,15 +5623,15 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="41">
+      <c r="B36" s="46">
         <f>IF(FORMATO!B17="","",FORMATO!B17)</f>
         <v/>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="22">
         <f>FORMATO!AI17</f>
         <v/>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="22">
         <f>FORMATO!AJ17</f>
         <v/>
       </c>
@@ -5445,15 +5644,15 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="41">
+      <c r="B37" s="46">
         <f>IF(FORMATO!B18="","",FORMATO!B18)</f>
         <v/>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="22">
         <f>FORMATO!AI18</f>
         <v/>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="22">
         <f>FORMATO!AJ18</f>
         <v/>
       </c>
@@ -5466,15 +5665,15 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
-      <c r="B38" s="41">
+      <c r="B38" s="46">
         <f>IF(FORMATO!B19="","",FORMATO!B19)</f>
         <v/>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="22">
         <f>FORMATO!AI19</f>
         <v/>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="22">
         <f>FORMATO!AJ19</f>
         <v/>
       </c>
@@ -5487,15 +5686,15 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
-      <c r="B39" s="41">
+      <c r="B39" s="46">
         <f>IF(FORMATO!B20="","",FORMATO!B20)</f>
         <v/>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="22">
         <f>FORMATO!AI20</f>
         <v/>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="22">
         <f>FORMATO!AJ20</f>
         <v/>
       </c>
@@ -5508,15 +5707,15 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
-      <c r="B40" s="41">
+      <c r="B40" s="46">
         <f>IF(FORMATO!B21="","",FORMATO!B21)</f>
         <v/>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="22">
         <f>FORMATO!AI21</f>
         <v/>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="22">
         <f>FORMATO!AJ21</f>
         <v/>
       </c>
@@ -5576,7 +5775,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="47" t="inlineStr">
         <is>
           <t>AYUDA Y PREGUNTAS FRECUENTES</t>
         </is>
@@ -5587,7 +5786,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="48" t="inlineStr">
         <is>
           <t>CONTROL DE ASISTENCIA</t>
         </is>
@@ -5624,12 +5823,12 @@
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>¿Cómo agrego más empleados?</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>El formato incluye 50 renglones. Para más empleados duplica la hoja o usa un archivo adicional.</t>
         </is>
@@ -5639,12 +5838,12 @@
     <row r="7" ht="38" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>¿Se descuentan los días de descanso?</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>No, la clave D no cuenta como falta ni como asistencia efectiva en los totales de faltas.</t>
         </is>
@@ -5654,12 +5853,12 @@
     <row r="8" ht="53" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>¿Por qué no puedo escribir en algunas celdas?</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
         </is>
@@ -5669,12 +5868,12 @@
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>¿Cómo agrego mi logotipo?</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
         </is>
@@ -5684,12 +5883,12 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
         </is>
@@ -5699,12 +5898,12 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="44" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>¿Con qué versiones de Excel funciona?</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="50" t="inlineStr">
         <is>
           <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
         </is>
@@ -5714,14 +5913,14 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="44" t="inlineStr">
-        <is>
-          <t>¿Por qué la letra se ve diferente?</t>
-        </is>
-      </c>
-      <c r="D12" s="45" t="inlineStr">
-        <is>
-          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>¿Puedo cambiar la letra?</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Arial, disponible en Windows, Mac y Google Sheets. Si necesitas otra, selecciona todo (Ctrl+E) y cambia la fuente; no afecta el funcionamiento.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -5729,12 +5928,12 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>¿Puedo usarlo en varias empresas o por varios años?</t>
         </is>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="50" t="inlineStr">
         <is>
           <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
         </is>
@@ -5762,12 +5961,12 @@
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="52" t="inlineStr">
         <is>
           <t>Asistencia</t>
         </is>
@@ -5777,12 +5976,12 @@
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>Falta injustificada</t>
         </is>
@@ -5792,12 +5991,12 @@
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="52" t="inlineStr">
         <is>
           <t>Retardo</t>
         </is>
@@ -5807,12 +6006,12 @@
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="n"/>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="52" t="inlineStr">
         <is>
           <t>Vacaciones</t>
         </is>
@@ -5822,12 +6021,12 @@
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="4" t="n"/>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="51" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="52" t="inlineStr">
         <is>
           <t>Incapacidad</t>
         </is>
@@ -5837,12 +6036,12 @@
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="4" t="n"/>
-      <c r="C21" s="46" t="inlineStr">
+      <c r="C21" s="51" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="52" t="inlineStr">
         <is>
           <t>Descanso</t>
         </is>
@@ -5852,12 +6051,12 @@
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="n"/>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="46" t="inlineStr">
+      <c r="C22" s="51" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="52" t="inlineStr">
         <is>
           <t>Permiso</t>
         </is>
@@ -5884,12 +6083,12 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="48" t="inlineStr">
+      <c r="B25" s="53" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="C25" s="54" t="inlineStr">
         <is>
           <t>Plantilla de empleados actualizada</t>
         </is>
@@ -5899,12 +6098,12 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="48" t="inlineStr">
+      <c r="B26" s="53" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C26" s="49" t="inlineStr">
+      <c r="C26" s="54" t="inlineStr">
         <is>
           <t>Todos los días capturados</t>
         </is>
@@ -5914,12 +6113,12 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="48" t="inlineStr">
+      <c r="B27" s="53" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C27" s="49" t="inlineStr">
+      <c r="C27" s="54" t="inlineStr">
         <is>
           <t>Faltas y retardos justificados o aplicados</t>
         </is>
@@ -5929,12 +6128,12 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="48" t="inlineStr">
+      <c r="B28" s="53" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C28" s="49" t="inlineStr">
+      <c r="C28" s="54" t="inlineStr">
         <is>
           <t>Totales enviados a nómina</t>
         </is>
